--- a/drifter/Drifter_TFO_deployment_log.xlsx
+++ b/drifter/Drifter_TFO_deployment_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alaferri/GIT/sio_code/ThodeLab/drifter/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thode/Desktop/ThodeLab/drifter/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A5708E-8625-C644-9142-7C02BEBE3344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C08D5D-FCEA-F041-900E-53DD7CF9621B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="840" windowWidth="30240" windowHeight="22120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Drifter Log 2022-2025" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="150">
   <si>
     <t>Deployment</t>
   </si>
@@ -490,18 +490,20 @@
   <si>
     <t>Magnetic Declination</t>
   </si>
+  <si>
+    <t>2025_Oct_CA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\Thh:mm:ss"/>
     <numFmt numFmtId="165" formatCode="h:mm;@"/>
     <numFmt numFmtId="166" formatCode="h:mm:ss;@"/>
     <numFmt numFmtId="167" formatCode="0.00000000"/>
     <numFmt numFmtId="168" formatCode="yyyymmdd\Thhmmss"/>
-    <numFmt numFmtId="169" formatCode="hh:mm:ss"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -613,7 +615,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -650,6 +652,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -680,7 +688,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
@@ -907,9 +915,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="168" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -920,6 +925,30 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="20% - Accent3" xfId="1" builtinId="38"/>
@@ -6059,16 +6088,16 @@
       <c r="E49" s="68">
         <v>45780</v>
       </c>
-      <c r="F49" s="86">
+      <c r="F49" s="46">
         <v>0.50486111111111109</v>
       </c>
-      <c r="G49" s="87" t="s">
+      <c r="G49" s="86" t="s">
         <v>141</v>
       </c>
       <c r="H49" s="44">
         <v>20.020324074074075</v>
       </c>
-      <c r="I49" s="88">
+      <c r="I49" s="87">
         <v>-156.00538</v>
       </c>
       <c r="J49" s="45">
@@ -6101,19 +6130,19 @@
       <c r="S49" s="52">
         <v>45780.951365740744</v>
       </c>
-      <c r="T49" s="89">
+      <c r="T49" s="88">
         <v>20.032706000000001</v>
       </c>
-      <c r="U49" s="89">
+      <c r="U49" s="88">
         <v>-155.999832</v>
       </c>
       <c r="V49" s="52">
         <v>45781.875567129631</v>
       </c>
-      <c r="W49" s="89">
+      <c r="W49" s="88">
         <v>20.074359999999999</v>
       </c>
-      <c r="X49" s="89">
+      <c r="X49" s="88">
         <v>-155.953611</v>
       </c>
       <c r="Y49" s="49">
@@ -6147,16 +6176,16 @@
       <c r="E50" s="68">
         <v>45780</v>
       </c>
-      <c r="F50" s="86">
+      <c r="F50" s="46">
         <v>0.50486111111111109</v>
       </c>
-      <c r="G50" s="87" t="s">
+      <c r="G50" s="86" t="s">
         <v>141</v>
       </c>
       <c r="H50" s="44">
         <v>20.020324074074075</v>
       </c>
-      <c r="I50" s="88">
+      <c r="I50" s="87">
         <v>-156.00538</v>
       </c>
       <c r="J50" s="45">
@@ -6189,19 +6218,19 @@
       <c r="S50" s="52">
         <v>45782.028784722221</v>
       </c>
-      <c r="T50" s="89">
+      <c r="T50" s="88">
         <v>20.127566000000002</v>
       </c>
-      <c r="U50" s="89">
+      <c r="U50" s="88">
         <v>-155.93448900000001</v>
       </c>
       <c r="V50" s="52">
         <v>45782.880578703705</v>
       </c>
-      <c r="W50" s="89">
+      <c r="W50" s="88">
         <v>20.216946</v>
       </c>
-      <c r="X50" s="89">
+      <c r="X50" s="88">
         <v>-155.941529</v>
       </c>
       <c r="Y50" s="49">
@@ -6267,19 +6296,19 @@
       <c r="S51" s="74">
         <v>45784.854861111111</v>
       </c>
-      <c r="T51" s="90">
+      <c r="T51" s="89">
         <v>19.972162000000001</v>
       </c>
-      <c r="U51" s="90">
+      <c r="U51" s="89">
         <v>-156.08393000000001</v>
       </c>
       <c r="V51" s="74">
         <v>45785.979861111111</v>
       </c>
-      <c r="W51" s="90">
+      <c r="W51" s="89">
         <v>19.971561000000001</v>
       </c>
-      <c r="X51" s="90">
+      <c r="X51" s="89">
         <v>-156.05051</v>
       </c>
       <c r="Y51" s="76">
@@ -6337,19 +6366,19 @@
       <c r="S52" s="52">
         <v>45788.225694444445</v>
       </c>
-      <c r="T52" s="89">
+      <c r="T52" s="88">
         <v>19.937816000000002</v>
       </c>
-      <c r="U52" s="89">
+      <c r="U52" s="88">
         <v>-155.78363999999999</v>
       </c>
       <c r="V52" s="52">
         <v>45789.118055555555</v>
       </c>
-      <c r="W52" s="89">
+      <c r="W52" s="88">
         <v>20.028275000000001</v>
       </c>
-      <c r="X52" s="89">
+      <c r="X52" s="88">
         <v>-155.99986999999999</v>
       </c>
       <c r="Y52" s="49">
@@ -6366,10 +6395,18 @@
       <c r="AE52" s="44"/>
     </row>
     <row r="53" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="20"/>
-      <c r="B53" s="20"/>
-      <c r="C53" s="20"/>
-      <c r="D53" s="20"/>
+      <c r="A53" s="20">
+        <v>34</v>
+      </c>
+      <c r="B53" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" s="20">
+        <v>5</v>
+      </c>
+      <c r="D53" s="20">
+        <v>1</v>
+      </c>
       <c r="E53" s="21"/>
       <c r="F53" s="22"/>
       <c r="G53" s="22"/>
@@ -6399,10 +6436,18 @@
       <c r="AE53" s="20"/>
     </row>
     <row r="54" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="20"/>
-      <c r="B54" s="20"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
+      <c r="A54" s="20">
+        <v>34</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="C54" s="20">
+        <v>5</v>
+      </c>
+      <c r="D54" s="20">
+        <v>2</v>
+      </c>
       <c r="E54" s="21"/>
       <c r="F54" s="22"/>
       <c r="G54" s="22"/>
@@ -6432,10 +6477,18 @@
       <c r="AE54" s="20"/>
     </row>
     <row r="55" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="20"/>
-      <c r="B55" s="20"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="20"/>
+      <c r="A55" s="20">
+        <v>34</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" s="20">
+        <v>5</v>
+      </c>
+      <c r="D55" s="20">
+        <v>3</v>
+      </c>
       <c r="E55" s="21"/>
       <c r="F55" s="22"/>
       <c r="G55" s="22"/>
@@ -6464,104 +6517,128 @@
       <c r="AD55" s="20"/>
       <c r="AE55" s="20"/>
     </row>
-    <row r="56" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="20"/>
-      <c r="B56" s="20"/>
-      <c r="C56" s="20"/>
-      <c r="D56" s="20"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="21"/>
-      <c r="K56" s="22"/>
-      <c r="L56" s="22"/>
-      <c r="M56" s="20"/>
-      <c r="N56" s="20"/>
-      <c r="O56" s="20"/>
-      <c r="P56" s="20"/>
-      <c r="Q56" s="23"/>
-      <c r="R56" s="23"/>
-      <c r="S56" s="24"/>
-      <c r="T56" s="20"/>
-      <c r="U56" s="20"/>
-      <c r="V56" s="24"/>
-      <c r="W56" s="20"/>
-      <c r="X56" s="20"/>
-      <c r="Y56" s="25"/>
-      <c r="Z56" s="25"/>
-      <c r="AA56" s="26"/>
-      <c r="AB56" s="26"/>
-      <c r="AC56" s="20"/>
-      <c r="AD56" s="20"/>
-      <c r="AE56" s="20"/>
-    </row>
-    <row r="57" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="20"/>
-      <c r="B57" s="20"/>
-      <c r="C57" s="20"/>
-      <c r="D57" s="20"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="20"/>
-      <c r="J57" s="21"/>
-      <c r="K57" s="22"/>
-      <c r="L57" s="22"/>
-      <c r="M57" s="20"/>
-      <c r="N57" s="20"/>
-      <c r="O57" s="20"/>
-      <c r="P57" s="20"/>
-      <c r="Q57" s="23"/>
-      <c r="R57" s="23"/>
-      <c r="S57" s="24"/>
-      <c r="T57" s="20"/>
-      <c r="U57" s="20"/>
-      <c r="V57" s="24"/>
-      <c r="W57" s="20"/>
-      <c r="X57" s="20"/>
-      <c r="Y57" s="25"/>
-      <c r="Z57" s="25"/>
-      <c r="AA57" s="26"/>
-      <c r="AB57" s="26"/>
-      <c r="AC57" s="20"/>
-      <c r="AD57" s="20"/>
-      <c r="AE57" s="20"/>
-    </row>
-    <row r="58" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="20"/>
-      <c r="B58" s="20"/>
-      <c r="C58" s="20"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
-      <c r="J58" s="21"/>
-      <c r="K58" s="22"/>
-      <c r="L58" s="22"/>
-      <c r="M58" s="20"/>
-      <c r="N58" s="20"/>
-      <c r="O58" s="20"/>
-      <c r="P58" s="20"/>
-      <c r="Q58" s="23"/>
-      <c r="R58" s="23"/>
-      <c r="S58" s="24"/>
-      <c r="T58" s="20"/>
-      <c r="U58" s="20"/>
-      <c r="V58" s="24"/>
-      <c r="W58" s="20"/>
-      <c r="X58" s="20"/>
-      <c r="Y58" s="25"/>
-      <c r="Z58" s="25"/>
-      <c r="AA58" s="26"/>
-      <c r="AB58" s="26"/>
-      <c r="AC58" s="20"/>
-      <c r="AD58" s="20"/>
-      <c r="AE58" s="20"/>
+    <row r="56" spans="1:31" s="99" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="92">
+        <v>35</v>
+      </c>
+      <c r="B56" s="92" t="s">
+        <v>149</v>
+      </c>
+      <c r="C56" s="92">
+        <v>6</v>
+      </c>
+      <c r="D56" s="92">
+        <v>1</v>
+      </c>
+      <c r="E56" s="93"/>
+      <c r="F56" s="94"/>
+      <c r="G56" s="94"/>
+      <c r="H56" s="92"/>
+      <c r="I56" s="92"/>
+      <c r="J56" s="93"/>
+      <c r="K56" s="94"/>
+      <c r="L56" s="94"/>
+      <c r="M56" s="92"/>
+      <c r="N56" s="92"/>
+      <c r="O56" s="92"/>
+      <c r="P56" s="92"/>
+      <c r="Q56" s="95"/>
+      <c r="R56" s="95"/>
+      <c r="S56" s="96"/>
+      <c r="T56" s="92"/>
+      <c r="U56" s="92"/>
+      <c r="V56" s="96"/>
+      <c r="W56" s="92"/>
+      <c r="X56" s="92"/>
+      <c r="Y56" s="97"/>
+      <c r="Z56" s="97"/>
+      <c r="AA56" s="98"/>
+      <c r="AB56" s="98"/>
+      <c r="AC56" s="92"/>
+      <c r="AD56" s="92"/>
+      <c r="AE56" s="92"/>
+    </row>
+    <row r="57" spans="1:31" s="99" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="92">
+        <v>35</v>
+      </c>
+      <c r="B57" s="92" t="s">
+        <v>149</v>
+      </c>
+      <c r="C57" s="92">
+        <v>6</v>
+      </c>
+      <c r="D57" s="92">
+        <v>2</v>
+      </c>
+      <c r="E57" s="93"/>
+      <c r="F57" s="94"/>
+      <c r="G57" s="94"/>
+      <c r="H57" s="92"/>
+      <c r="I57" s="92"/>
+      <c r="J57" s="93"/>
+      <c r="K57" s="94"/>
+      <c r="L57" s="94"/>
+      <c r="M57" s="92"/>
+      <c r="N57" s="92"/>
+      <c r="O57" s="92"/>
+      <c r="P57" s="92"/>
+      <c r="Q57" s="95"/>
+      <c r="R57" s="95"/>
+      <c r="S57" s="96"/>
+      <c r="T57" s="92"/>
+      <c r="U57" s="92"/>
+      <c r="V57" s="96"/>
+      <c r="W57" s="92"/>
+      <c r="X57" s="92"/>
+      <c r="Y57" s="97"/>
+      <c r="Z57" s="97"/>
+      <c r="AA57" s="98"/>
+      <c r="AB57" s="98"/>
+      <c r="AC57" s="92"/>
+      <c r="AD57" s="92"/>
+      <c r="AE57" s="92"/>
+    </row>
+    <row r="58" spans="1:31" s="99" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="92">
+        <v>35</v>
+      </c>
+      <c r="B58" s="92" t="s">
+        <v>149</v>
+      </c>
+      <c r="C58" s="92">
+        <v>6</v>
+      </c>
+      <c r="D58" s="92">
+        <v>3</v>
+      </c>
+      <c r="E58" s="93"/>
+      <c r="F58" s="94"/>
+      <c r="G58" s="94"/>
+      <c r="H58" s="92"/>
+      <c r="I58" s="92"/>
+      <c r="J58" s="93"/>
+      <c r="K58" s="94"/>
+      <c r="L58" s="94"/>
+      <c r="M58" s="92"/>
+      <c r="N58" s="92"/>
+      <c r="O58" s="92"/>
+      <c r="P58" s="92"/>
+      <c r="Q58" s="95"/>
+      <c r="R58" s="95"/>
+      <c r="S58" s="96"/>
+      <c r="T58" s="92"/>
+      <c r="U58" s="92"/>
+      <c r="V58" s="96"/>
+      <c r="W58" s="92"/>
+      <c r="X58" s="92"/>
+      <c r="Y58" s="97"/>
+      <c r="Z58" s="97"/>
+      <c r="AA58" s="98"/>
+      <c r="AB58" s="98"/>
+      <c r="AC58" s="92"/>
+      <c r="AD58" s="92"/>
+      <c r="AE58" s="92"/>
     </row>
     <row r="59" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="20"/>
@@ -48056,11 +48133,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="96" x14ac:dyDescent="0.2">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
       <c r="D1" s="9" t="s">
         <v>53</v>
       </c>

--- a/drifter/Drifter_TFO_deployment_log.xlsx
+++ b/drifter/Drifter_TFO_deployment_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/alaferriere/GIT/ThodeLab/drifter/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thode/Desktop/ThodeLab/drifter/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21588C5B-104B-1E41-846C-0D36A4A50E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A1BB36-5A6F-994D-882B-2D451365B47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3300" yWindow="500" windowWidth="40960" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35160" yWindow="17880" windowWidth="35840" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Drifter Log 2022-2025" sheetId="1" r:id="rId1"/>
@@ -600,14 +600,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\Thh:mm:ss"/>
     <numFmt numFmtId="165" formatCode="h:mm;@"/>
     <numFmt numFmtId="166" formatCode="h:mm:ss;@"/>
     <numFmt numFmtId="167" formatCode="0.00000000"/>
     <numFmt numFmtId="168" formatCode="yyyymmdd\Thhmmss"/>
-    <numFmt numFmtId="169" formatCode="hh:mm:ss"/>
-    <numFmt numFmtId="170" formatCode="0.00000"/>
+    <numFmt numFmtId="169" formatCode="0.00000"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -824,7 +823,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
@@ -1042,35 +1041,32 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="169" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2070,12 +2066,12 @@
     <col min="3" max="4" width="14.5" style="26" customWidth="1"/>
     <col min="5" max="5" width="15.6640625" style="26" customWidth="1"/>
     <col min="6" max="6" width="17" style="26" customWidth="1"/>
-    <col min="7" max="7" width="24.83203125" style="110" customWidth="1"/>
+    <col min="7" max="7" width="24.83203125" style="109" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" style="26" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" style="26" customWidth="1"/>
     <col min="10" max="10" width="17.5" style="26" customWidth="1"/>
     <col min="11" max="11" width="17.83203125" style="26" customWidth="1"/>
-    <col min="12" max="12" width="20" style="100" customWidth="1"/>
+    <col min="12" max="12" width="20" style="99" customWidth="1"/>
     <col min="13" max="13" width="12.1640625" style="26" customWidth="1"/>
     <col min="14" max="16" width="13.5" style="26" customWidth="1"/>
     <col min="17" max="17" width="16.83203125" style="26" customWidth="1"/>
@@ -2111,7 +2107,7 @@
       <c r="F1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="102" t="s">
+      <c r="G1" s="101" t="s">
         <v>91</v>
       </c>
       <c r="H1" s="10" t="s">
@@ -2126,7 +2122,7 @@
       <c r="K1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="99" t="s">
+      <c r="L1" s="98" t="s">
         <v>92</v>
       </c>
       <c r="M1" s="10" t="s">
@@ -2206,7 +2202,7 @@
       <c r="F2" s="38">
         <v>0.55138888888888882</v>
       </c>
-      <c r="G2" s="103" t="s">
+      <c r="G2" s="102" t="s">
         <v>153</v>
       </c>
       <c r="H2" s="35">
@@ -2297,7 +2293,7 @@
       <c r="F3" s="21">
         <v>0.42638888888888887</v>
       </c>
-      <c r="G3" s="104" t="s">
+      <c r="G3" s="103" t="s">
         <v>154</v>
       </c>
       <c r="H3" s="19">
@@ -2387,7 +2383,7 @@
         <v>44822</v>
       </c>
       <c r="F4" s="38"/>
-      <c r="G4" s="105" t="s">
+      <c r="G4" s="104" t="s">
         <v>123</v>
       </c>
       <c r="H4" s="35">
@@ -2477,7 +2473,7 @@
         <v>44822</v>
       </c>
       <c r="F5" s="21"/>
-      <c r="G5" s="104" t="s">
+      <c r="G5" s="103" t="s">
         <v>125</v>
       </c>
       <c r="H5" s="19">
@@ -2565,7 +2561,7 @@
         <v>44823</v>
       </c>
       <c r="F6" s="45"/>
-      <c r="G6" s="105" t="s">
+      <c r="G6" s="104" t="s">
         <v>127</v>
       </c>
       <c r="H6" s="43">
@@ -2657,7 +2653,7 @@
       <c r="F7" s="21">
         <v>0.44444444444444442</v>
       </c>
-      <c r="G7" s="106" t="s">
+      <c r="G7" s="105" t="s">
         <v>105</v>
       </c>
       <c r="H7" s="19">
@@ -2743,7 +2739,7 @@
         <v>44983</v>
       </c>
       <c r="F8" s="45"/>
-      <c r="G8" s="105" t="s">
+      <c r="G8" s="104" t="s">
         <v>107</v>
       </c>
       <c r="H8" s="43"/>
@@ -2819,7 +2815,7 @@
         <v>44983</v>
       </c>
       <c r="F9" s="45"/>
-      <c r="G9" s="105" t="s">
+      <c r="G9" s="104" t="s">
         <v>107</v>
       </c>
       <c r="H9" s="43"/>
@@ -2895,7 +2891,7 @@
         <v>44983</v>
       </c>
       <c r="F10" s="45"/>
-      <c r="G10" s="105" t="s">
+      <c r="G10" s="104" t="s">
         <v>107</v>
       </c>
       <c r="H10" s="43"/>
@@ -2971,7 +2967,7 @@
         <v>44983</v>
       </c>
       <c r="F11" s="45"/>
-      <c r="G11" s="105" t="s">
+      <c r="G11" s="104" t="s">
         <v>107</v>
       </c>
       <c r="H11" s="43"/>
@@ -3049,7 +3045,7 @@
       <c r="F12" s="21">
         <v>0.52013888888888882</v>
       </c>
-      <c r="G12" s="106" t="s">
+      <c r="G12" s="105" t="s">
         <v>109</v>
       </c>
       <c r="H12" s="19">
@@ -3133,7 +3129,7 @@
         <v>44983</v>
       </c>
       <c r="F13" s="21"/>
-      <c r="G13" s="106" t="s">
+      <c r="G13" s="105" t="s">
         <v>109</v>
       </c>
       <c r="H13" s="19"/>
@@ -3209,7 +3205,7 @@
         <v>44985</v>
       </c>
       <c r="F14" s="45"/>
-      <c r="G14" s="105" t="s">
+      <c r="G14" s="104" t="s">
         <v>111</v>
       </c>
       <c r="H14" s="43">
@@ -3293,7 +3289,7 @@
       <c r="F15" s="21">
         <v>0.3972222222222222</v>
       </c>
-      <c r="G15" s="106" t="s">
+      <c r="G15" s="105" t="s">
         <v>103</v>
       </c>
       <c r="H15" s="19">
@@ -3383,7 +3379,7 @@
         <v>45084</v>
       </c>
       <c r="F16" s="45"/>
-      <c r="G16" s="105" t="s">
+      <c r="G16" s="104" t="s">
         <v>99</v>
       </c>
       <c r="H16" s="43"/>
@@ -3459,7 +3455,7 @@
         <v>45084</v>
       </c>
       <c r="F17" s="45"/>
-      <c r="G17" s="105" t="s">
+      <c r="G17" s="104" t="s">
         <v>99</v>
       </c>
       <c r="H17" s="43"/>
@@ -3535,7 +3531,7 @@
         <v>45084</v>
       </c>
       <c r="F18" s="21"/>
-      <c r="G18" s="106" t="s">
+      <c r="G18" s="105" t="s">
         <v>101</v>
       </c>
       <c r="H18" s="19"/>
@@ -3611,7 +3607,7 @@
         <v>45084</v>
       </c>
       <c r="F19" s="21"/>
-      <c r="G19" s="106" t="s">
+      <c r="G19" s="105" t="s">
         <v>101</v>
       </c>
       <c r="H19" s="19"/>
@@ -3689,7 +3685,7 @@
       <c r="F20" s="45">
         <v>0.37708333333333338</v>
       </c>
-      <c r="G20" s="105" t="s">
+      <c r="G20" s="104" t="s">
         <v>155</v>
       </c>
       <c r="H20" s="43">
@@ -3779,7 +3775,7 @@
       <c r="F21" s="21">
         <v>0.29722222222222222</v>
       </c>
-      <c r="G21" s="106" t="s">
+      <c r="G21" s="105" t="s">
         <v>156</v>
       </c>
       <c r="H21" s="19">
@@ -3873,7 +3869,7 @@
       <c r="F22" s="45">
         <v>0.29444444444444445</v>
       </c>
-      <c r="G22" s="105" t="s">
+      <c r="G22" s="104" t="s">
         <v>157</v>
       </c>
       <c r="H22" s="43">
@@ -3967,7 +3963,7 @@
       <c r="F23" s="45">
         <v>0.29444444444444445</v>
       </c>
-      <c r="G23" s="105" t="s">
+      <c r="G23" s="104" t="s">
         <v>157</v>
       </c>
       <c r="H23" s="43">
@@ -4015,10 +4011,10 @@
       <c r="V23" s="51">
         <v>45205.389224537037</v>
       </c>
-      <c r="W23" s="87">
+      <c r="W23" s="86">
         <v>38.930204000000003</v>
       </c>
-      <c r="X23" s="87">
+      <c r="X23" s="86">
         <v>-64.167721999999998</v>
       </c>
       <c r="Y23" s="48">
@@ -4061,7 +4057,7 @@
       <c r="F24" s="21">
         <v>0.3034722222222222</v>
       </c>
-      <c r="G24" s="106" t="s">
+      <c r="G24" s="105" t="s">
         <v>158</v>
       </c>
       <c r="H24" s="19">
@@ -4109,10 +4105,10 @@
       <c r="V24" s="27">
         <v>45204.712129629632</v>
       </c>
-      <c r="W24" s="88">
+      <c r="W24" s="87">
         <v>38.873122000000002</v>
       </c>
-      <c r="X24" s="88">
+      <c r="X24" s="87">
         <v>-64.033095000000003</v>
       </c>
       <c r="Y24" s="24">
@@ -4153,7 +4149,7 @@
       <c r="F25" s="21">
         <v>0.3034722222222222</v>
       </c>
-      <c r="G25" s="106" t="s">
+      <c r="G25" s="105" t="s">
         <v>158</v>
       </c>
       <c r="H25" s="19">
@@ -4201,10 +4197,10 @@
       <c r="V25" s="27">
         <v>45205.392685185187</v>
       </c>
-      <c r="W25" s="88">
+      <c r="W25" s="87">
         <v>38.916741999999999</v>
       </c>
-      <c r="X25" s="88">
+      <c r="X25" s="87">
         <v>-64.137314000000003</v>
       </c>
       <c r="Y25" s="24">
@@ -4245,7 +4241,7 @@
       <c r="F26" s="45">
         <v>0.92152777777777783</v>
       </c>
-      <c r="G26" s="105" t="s">
+      <c r="G26" s="104" t="s">
         <v>159</v>
       </c>
       <c r="H26" s="43">
@@ -4293,10 +4289,10 @@
       <c r="V26" s="51">
         <v>45208.63921296296</v>
       </c>
-      <c r="W26" s="89">
+      <c r="W26" s="88">
         <v>38.832385000000002</v>
       </c>
-      <c r="X26" s="89">
+      <c r="X26" s="88">
         <v>-63.796340000000001</v>
       </c>
       <c r="Y26" s="48">
@@ -4337,7 +4333,7 @@
       <c r="F27" s="45">
         <v>0.92152777777777783</v>
       </c>
-      <c r="G27" s="105" t="s">
+      <c r="G27" s="104" t="s">
         <v>159</v>
       </c>
       <c r="H27" s="43">
@@ -4385,10 +4381,10 @@
       <c r="V27" s="51">
         <v>45209.656574074077</v>
       </c>
-      <c r="W27" s="89">
+      <c r="W27" s="88">
         <v>38.923247000000003</v>
       </c>
-      <c r="X27" s="89">
+      <c r="X27" s="88">
         <v>-63.812421999999998</v>
       </c>
       <c r="Y27" s="48">
@@ -4429,7 +4425,7 @@
       <c r="F28" s="45">
         <v>0.92152777777777783</v>
       </c>
-      <c r="G28" s="105" t="s">
+      <c r="G28" s="104" t="s">
         <v>159</v>
       </c>
       <c r="H28" s="43">
@@ -4477,10 +4473,10 @@
       <c r="V28" s="51">
         <v>45210.542002314818</v>
       </c>
-      <c r="W28" s="89">
+      <c r="W28" s="88">
         <v>38.940576999999998</v>
       </c>
-      <c r="X28" s="89">
+      <c r="X28" s="88">
         <v>-63.867663</v>
       </c>
       <c r="Y28" s="48">
@@ -4521,7 +4517,7 @@
       <c r="F29" s="21">
         <v>0.9243055555555556</v>
       </c>
-      <c r="G29" s="106" t="s">
+      <c r="G29" s="105" t="s">
         <v>160</v>
       </c>
       <c r="H29" s="19">
@@ -4569,10 +4565,10 @@
       <c r="V29" s="27">
         <v>45208.687939814816</v>
       </c>
-      <c r="W29" s="90">
+      <c r="W29" s="89">
         <v>38.808157999999999</v>
       </c>
-      <c r="X29" s="90">
+      <c r="X29" s="89">
         <v>-63.765051999999997</v>
       </c>
       <c r="Y29" s="24">
@@ -4615,7 +4611,7 @@
       <c r="F30" s="21">
         <v>0.9243055555555556</v>
       </c>
-      <c r="G30" s="106" t="s">
+      <c r="G30" s="105" t="s">
         <v>160</v>
       </c>
       <c r="H30" s="19">
@@ -4663,10 +4659,10 @@
       <c r="V30" s="27">
         <v>45209.63921296296</v>
       </c>
-      <c r="W30" s="90">
+      <c r="W30" s="89">
         <v>38.928795999999998</v>
       </c>
-      <c r="X30" s="90">
+      <c r="X30" s="89">
         <v>-63.821711999999998</v>
       </c>
       <c r="Y30" s="24">
@@ -4707,7 +4703,7 @@
       <c r="F31" s="45">
         <v>0.59722222222222221</v>
       </c>
-      <c r="G31" s="105" t="s">
+      <c r="G31" s="104" t="s">
         <v>161</v>
       </c>
       <c r="H31" s="43">
@@ -4755,10 +4751,10 @@
       <c r="V31" s="47">
         <v>45209.26421296296</v>
       </c>
-      <c r="W31" s="89">
+      <c r="W31" s="88">
         <v>38.862524999999998</v>
       </c>
-      <c r="X31" s="89">
+      <c r="X31" s="88">
         <v>-63.894246000000003</v>
       </c>
       <c r="Y31" s="48">
@@ -4801,7 +4797,7 @@
       <c r="F32" s="21">
         <v>0.48333333333333334</v>
       </c>
-      <c r="G32" s="106" t="s">
+      <c r="G32" s="105" t="s">
         <v>162</v>
       </c>
       <c r="H32" s="19">
@@ -4849,10 +4845,10 @@
       <c r="V32" s="27">
         <v>45211.541979166665</v>
       </c>
-      <c r="W32" s="90">
+      <c r="W32" s="89">
         <v>38.912925999999999</v>
       </c>
-      <c r="X32" s="90">
+      <c r="X32" s="89">
         <v>-63.895589000000001</v>
       </c>
       <c r="Y32" s="24">
@@ -4895,7 +4891,7 @@
       <c r="F33" s="21">
         <v>0.48333333333333334</v>
       </c>
-      <c r="G33" s="106" t="s">
+      <c r="G33" s="105" t="s">
         <v>162</v>
       </c>
       <c r="H33" s="19">
@@ -4943,10 +4939,10 @@
       <c r="V33" s="27">
         <v>45212.556122685186</v>
       </c>
-      <c r="W33" s="90">
+      <c r="W33" s="89">
         <v>38.935225000000003</v>
       </c>
-      <c r="X33" s="90">
+      <c r="X33" s="89">
         <v>-63.928724000000003</v>
       </c>
       <c r="Y33" s="24">
@@ -4987,7 +4983,7 @@
       <c r="F34" s="45">
         <v>0.60416666666666663</v>
       </c>
-      <c r="G34" s="105" t="s">
+      <c r="G34" s="104" t="s">
         <v>163</v>
       </c>
       <c r="H34" s="43">
@@ -5035,10 +5031,10 @@
       <c r="V34" s="51">
         <v>45212.541990740741</v>
       </c>
-      <c r="W34" s="89">
+      <c r="W34" s="88">
         <v>38.884850999999998</v>
       </c>
-      <c r="X34" s="89">
+      <c r="X34" s="88">
         <v>-63.740850999999999</v>
       </c>
       <c r="Y34" s="48">
@@ -5081,7 +5077,7 @@
       <c r="F35" s="21">
         <v>0.60763888888888895</v>
       </c>
-      <c r="G35" s="106" t="s">
+      <c r="G35" s="105" t="s">
         <v>164</v>
       </c>
       <c r="H35" s="19">
@@ -5129,10 +5125,10 @@
       <c r="V35" s="27">
         <v>45212.535046296296</v>
       </c>
-      <c r="W35" s="90">
+      <c r="W35" s="89">
         <v>38.887054999999997</v>
       </c>
-      <c r="X35" s="90">
+      <c r="X35" s="89">
         <v>-63.744534000000002</v>
       </c>
       <c r="Y35" s="24">
@@ -5175,7 +5171,7 @@
       <c r="F36" s="45">
         <v>0.50972222222222219</v>
       </c>
-      <c r="G36" s="105" t="s">
+      <c r="G36" s="104" t="s">
         <v>165</v>
       </c>
       <c r="H36" s="43"/>
@@ -5215,10 +5211,10 @@
       <c r="V36" s="47">
         <v>45318.878796296296</v>
       </c>
-      <c r="W36" s="91">
+      <c r="W36" s="90">
         <v>32.999972</v>
       </c>
-      <c r="X36" s="91">
+      <c r="X36" s="90">
         <v>-117.66408699999999</v>
       </c>
       <c r="Y36" s="48">
@@ -5259,7 +5255,7 @@
       <c r="F37" s="45">
         <v>0.50972222222222219</v>
       </c>
-      <c r="G37" s="105" t="s">
+      <c r="G37" s="104" t="s">
         <v>165</v>
       </c>
       <c r="H37" s="43"/>
@@ -5299,10 +5295,10 @@
       <c r="V37" s="47">
         <v>45319.878796296296</v>
       </c>
-      <c r="W37" s="91">
+      <c r="W37" s="90">
         <v>33.117448000000003</v>
       </c>
-      <c r="X37" s="91">
+      <c r="X37" s="90">
         <v>-117.6035</v>
       </c>
       <c r="Y37" s="48">
@@ -5343,7 +5339,7 @@
       <c r="F38" s="45">
         <v>0.50972222222222219</v>
       </c>
-      <c r="G38" s="105" t="s">
+      <c r="G38" s="104" t="s">
         <v>165</v>
       </c>
       <c r="H38" s="43"/>
@@ -5383,10 +5379,10 @@
       <c r="V38" s="47">
         <v>45320.89980324074</v>
       </c>
-      <c r="W38" s="92">
+      <c r="W38" s="91">
         <v>33.200189999999999</v>
       </c>
-      <c r="X38" s="92">
+      <c r="X38" s="91">
         <v>-117.597759</v>
       </c>
       <c r="Y38" s="48">
@@ -5427,7 +5423,7 @@
       <c r="F39" s="21">
         <v>0.63472222222222219</v>
       </c>
-      <c r="G39" s="106" t="s">
+      <c r="G39" s="105" t="s">
         <v>166</v>
       </c>
       <c r="H39" s="19"/>
@@ -5467,10 +5463,10 @@
       <c r="V39" s="27">
         <v>45318.882280092592</v>
       </c>
-      <c r="W39" s="93">
+      <c r="W39" s="92">
         <v>33.012383</v>
       </c>
-      <c r="X39" s="93">
+      <c r="X39" s="92">
         <v>-117.66186500000001</v>
       </c>
       <c r="Y39" s="24">
@@ -5511,7 +5507,7 @@
       <c r="F40" s="21">
         <v>0.63472222222222219</v>
       </c>
-      <c r="G40" s="106" t="s">
+      <c r="G40" s="105" t="s">
         <v>166</v>
       </c>
       <c r="H40" s="19"/>
@@ -5551,10 +5547,10 @@
       <c r="V40" s="27">
         <v>45320.848263888889</v>
       </c>
-      <c r="W40" s="93">
+      <c r="W40" s="92">
         <v>33.115271</v>
       </c>
-      <c r="X40" s="93">
+      <c r="X40" s="92">
         <v>-117.89773700000001</v>
       </c>
       <c r="Y40" s="24">
@@ -5593,7 +5589,7 @@
         <v>45425</v>
       </c>
       <c r="F41" s="45"/>
-      <c r="G41" s="105" t="s">
+      <c r="G41" s="104" t="s">
         <v>121</v>
       </c>
       <c r="H41" s="43"/>
@@ -5621,8 +5617,8 @@
       <c r="T41" s="65"/>
       <c r="U41" s="65"/>
       <c r="V41" s="51"/>
-      <c r="W41" s="92"/>
-      <c r="X41" s="92"/>
+      <c r="W41" s="91"/>
+      <c r="X41" s="91"/>
       <c r="Y41" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5655,7 +5651,7 @@
       <c r="F42" s="70">
         <v>0.43533564814814812</v>
       </c>
-      <c r="G42" s="107" t="s">
+      <c r="G42" s="106" t="s">
         <v>115</v>
       </c>
       <c r="H42" s="63"/>
@@ -5695,10 +5691,10 @@
       <c r="V42" s="73" t="s">
         <v>117</v>
       </c>
-      <c r="W42" s="93">
+      <c r="W42" s="92">
         <v>33.001100000000001</v>
       </c>
-      <c r="X42" s="93">
+      <c r="X42" s="92">
         <v>-117.8729</v>
       </c>
       <c r="Y42" s="24" t="e">
@@ -5739,7 +5735,7 @@
       <c r="F43" s="70">
         <v>0.43533564814814812</v>
       </c>
-      <c r="G43" s="107" t="s">
+      <c r="G43" s="106" t="s">
         <v>115</v>
       </c>
       <c r="H43" s="63"/>
@@ -5779,10 +5775,10 @@
       <c r="V43" s="73" t="s">
         <v>120</v>
       </c>
-      <c r="W43" s="93">
+      <c r="W43" s="92">
         <v>33.012540000000001</v>
       </c>
-      <c r="X43" s="93">
+      <c r="X43" s="92">
         <v>-117.890097</v>
       </c>
       <c r="Y43" s="24" t="e">
@@ -5823,7 +5819,7 @@
       <c r="F44" s="45">
         <v>0.625</v>
       </c>
-      <c r="G44" s="105" t="s">
+      <c r="G44" s="104" t="s">
         <v>151</v>
       </c>
       <c r="H44">
@@ -5869,8 +5865,8 @@
       <c r="V44" s="73">
         <v>45465.117199074077</v>
       </c>
-      <c r="W44" s="91"/>
-      <c r="X44" s="91"/>
+      <c r="W44" s="90"/>
+      <c r="X44" s="90"/>
       <c r="Y44" s="24">
         <f t="shared" ref="Y44:Y58" si="2">(V44-S44)*1440/60</f>
         <v>54.165833333332557</v>
@@ -5905,7 +5901,7 @@
       <c r="F45" s="70">
         <v>0.625</v>
       </c>
-      <c r="G45" s="104" t="s">
+      <c r="G45" s="103" t="s">
         <v>151</v>
       </c>
       <c r="H45">
@@ -5953,10 +5949,10 @@
       <c r="V45" s="73">
         <v>45465.11142361111</v>
       </c>
-      <c r="W45" s="94">
+      <c r="W45" s="93">
         <v>38.406742000000001</v>
       </c>
-      <c r="X45" s="94">
+      <c r="X45" s="93">
         <v>-62.544604</v>
       </c>
       <c r="Y45" s="24">
@@ -5991,7 +5987,7 @@
       <c r="F46" s="70">
         <v>0.625</v>
       </c>
-      <c r="G46" s="104" t="s">
+      <c r="G46" s="103" t="s">
         <v>151</v>
       </c>
       <c r="H46">
@@ -6039,10 +6035,10 @@
       <c r="V46" s="27">
         <v>45466.125555555554</v>
       </c>
-      <c r="W46" s="94">
+      <c r="W46" s="93">
         <v>38.532255999999997</v>
       </c>
-      <c r="X46" s="94">
+      <c r="X46" s="93">
         <v>-62.362059000000002</v>
       </c>
       <c r="Y46" s="24">
@@ -6079,7 +6075,7 @@
       <c r="F47" s="45">
         <v>0.625</v>
       </c>
-      <c r="G47" s="105" t="s">
+      <c r="G47" s="104" t="s">
         <v>151</v>
       </c>
       <c r="H47" s="43">
@@ -6127,10 +6123,10 @@
       <c r="V47" s="51">
         <v>45463.528101851851</v>
       </c>
-      <c r="W47" s="92">
+      <c r="W47" s="91">
         <v>38.311391</v>
       </c>
-      <c r="X47" s="92">
+      <c r="X47" s="91">
         <v>-62.918548000000001</v>
       </c>
       <c r="Y47" s="24">
@@ -6165,14 +6161,14 @@
         <v>45597</v>
       </c>
       <c r="F48" s="78"/>
-      <c r="G48" s="104" t="s">
+      <c r="G48" s="103" t="s">
         <v>150</v>
       </c>
       <c r="H48" s="73"/>
       <c r="I48" s="78"/>
       <c r="J48" s="79"/>
       <c r="K48" s="70"/>
-      <c r="L48" s="98" t="s">
+      <c r="L48" s="97" t="s">
         <v>152</v>
       </c>
       <c r="M48" s="63"/>
@@ -6184,8 +6180,8 @@
       <c r="S48" s="74"/>
       <c r="T48" s="63"/>
       <c r="U48" s="63"/>
-      <c r="W48" s="95"/>
-      <c r="X48" s="95"/>
+      <c r="W48" s="94"/>
+      <c r="X48" s="94"/>
       <c r="Y48" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6213,16 +6209,16 @@
       <c r="E49" s="67">
         <v>45780</v>
       </c>
-      <c r="F49" s="83">
+      <c r="F49" s="45">
         <v>0.50486111111111109</v>
       </c>
-      <c r="G49" s="105" t="s">
+      <c r="G49" s="104" t="s">
         <v>139</v>
       </c>
       <c r="H49" s="43">
         <v>20.020324074074075</v>
       </c>
-      <c r="I49" s="84">
+      <c r="I49" s="83">
         <v>-156.00538</v>
       </c>
       <c r="J49" s="44">
@@ -6255,19 +6251,19 @@
       <c r="S49" s="51">
         <v>45780.951365740744</v>
       </c>
-      <c r="T49" s="85">
+      <c r="T49" s="84">
         <v>20.032706000000001</v>
       </c>
-      <c r="U49" s="85">
+      <c r="U49" s="84">
         <v>-155.999832</v>
       </c>
       <c r="V49" s="51">
         <v>45781.875567129631</v>
       </c>
-      <c r="W49" s="96">
+      <c r="W49" s="95">
         <v>20.074359999999999</v>
       </c>
-      <c r="X49" s="96">
+      <c r="X49" s="95">
         <v>-155.953611</v>
       </c>
       <c r="Y49" s="24">
@@ -6301,16 +6297,16 @@
       <c r="E50" s="67">
         <v>45780</v>
       </c>
-      <c r="F50" s="83">
+      <c r="F50" s="45">
         <v>0.50486111111111109</v>
       </c>
-      <c r="G50" s="105" t="s">
+      <c r="G50" s="104" t="s">
         <v>139</v>
       </c>
       <c r="H50" s="43">
         <v>20.020324074074075</v>
       </c>
-      <c r="I50" s="84">
+      <c r="I50" s="83">
         <v>-156.00538</v>
       </c>
       <c r="J50" s="44">
@@ -6343,19 +6339,19 @@
       <c r="S50" s="51">
         <v>45782.028784722221</v>
       </c>
-      <c r="T50" s="85">
+      <c r="T50" s="84">
         <v>20.127566000000002</v>
       </c>
-      <c r="U50" s="85">
+      <c r="U50" s="84">
         <v>-155.93448900000001</v>
       </c>
       <c r="V50" s="51">
         <v>45782.880578703705</v>
       </c>
-      <c r="W50" s="96">
+      <c r="W50" s="95">
         <v>20.216946</v>
       </c>
-      <c r="X50" s="96">
+      <c r="X50" s="95">
         <v>-155.941529</v>
       </c>
       <c r="Y50" s="24">
@@ -6390,7 +6386,7 @@
         <v>45784</v>
       </c>
       <c r="F51" s="70"/>
-      <c r="G51" s="107" t="s">
+      <c r="G51" s="106" t="s">
         <v>142</v>
       </c>
       <c r="H51" s="63">
@@ -6421,19 +6417,19 @@
       <c r="S51" s="73">
         <v>45784.854861111111</v>
       </c>
-      <c r="T51" s="86">
+      <c r="T51" s="85">
         <v>19.972162000000001</v>
       </c>
-      <c r="U51" s="86">
+      <c r="U51" s="85">
         <v>-156.08393000000001</v>
       </c>
       <c r="V51" s="73">
         <v>45785.979861111111</v>
       </c>
-      <c r="W51" s="97">
+      <c r="W51" s="96">
         <v>19.971561000000001</v>
       </c>
-      <c r="X51" s="97">
+      <c r="X51" s="96">
         <v>-156.05051</v>
       </c>
       <c r="Y51" s="24">
@@ -6462,20 +6458,34 @@
       <c r="D52" s="43">
         <v>1</v>
       </c>
-      <c r="E52" s="44"/>
-      <c r="F52" s="45"/>
-      <c r="G52" s="108" t="s">
+      <c r="E52" s="44">
+        <v>45788</v>
+      </c>
+      <c r="F52" s="45">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G52" s="107" t="s">
         <v>144</v>
       </c>
-      <c r="H52" s="43"/>
-      <c r="I52" s="43"/>
-      <c r="J52" s="44"/>
+      <c r="H52" s="43">
+        <v>20.025929999999999</v>
+      </c>
+      <c r="I52" s="43">
+        <v>-155.98406667</v>
+      </c>
+      <c r="J52" s="44">
+        <v>45789</v>
+      </c>
       <c r="K52" s="45"/>
       <c r="L52" s="53" t="s">
         <v>145</v>
       </c>
-      <c r="M52" s="43"/>
-      <c r="N52" s="43"/>
+      <c r="M52" s="43">
+        <v>20.043631999999999</v>
+      </c>
+      <c r="N52" s="43">
+        <v>-156.01302899999999</v>
+      </c>
       <c r="O52" s="43">
         <v>3</v>
       </c>
@@ -6491,19 +6501,19 @@
       <c r="S52" s="51">
         <v>45788.225694444445</v>
       </c>
-      <c r="T52" s="85">
+      <c r="T52" s="84">
         <v>19.937816000000002</v>
       </c>
-      <c r="U52" s="85">
+      <c r="U52" s="84">
         <v>-155.78363999999999</v>
       </c>
       <c r="V52" s="51">
         <v>45789.118055555555</v>
       </c>
-      <c r="W52" s="96">
+      <c r="W52" s="95">
         <v>20.028275000000001</v>
       </c>
-      <c r="X52" s="96">
+      <c r="X52" s="95">
         <v>-155.99986999999999</v>
       </c>
       <c r="Y52" s="24">
@@ -6538,7 +6548,7 @@
       <c r="F53" s="21">
         <v>0.45833333333333331</v>
       </c>
-      <c r="G53" s="109" t="s">
+      <c r="G53" s="108" t="s">
         <v>148</v>
       </c>
       <c r="H53" s="19"/>
@@ -6569,19 +6579,19 @@
       <c r="S53" s="73">
         <v>45926.754861111112</v>
       </c>
-      <c r="T53" s="86">
+      <c r="T53" s="85">
         <v>32.910401999999998</v>
       </c>
-      <c r="U53" s="86">
+      <c r="U53" s="85">
         <v>-117.73626</v>
       </c>
       <c r="V53" s="73">
         <v>45927.75</v>
       </c>
-      <c r="W53" s="86">
+      <c r="W53" s="85">
         <v>32.983435999999998</v>
       </c>
-      <c r="X53" s="86">
+      <c r="X53" s="85">
         <v>-117.72745999999999</v>
       </c>
       <c r="Y53" s="24">
@@ -6616,7 +6626,7 @@
       <c r="F54" s="21">
         <v>0.45833333333333331</v>
       </c>
-      <c r="G54" s="109" t="s">
+      <c r="G54" s="108" t="s">
         <v>148</v>
       </c>
       <c r="H54" s="19"/>
@@ -6647,19 +6657,19 @@
       <c r="S54" s="73">
         <v>45927.795138888891</v>
       </c>
-      <c r="T54" s="86">
+      <c r="T54" s="85">
         <v>32.988210000000002</v>
       </c>
-      <c r="U54" s="86">
+      <c r="U54" s="85">
         <v>-117.71984999999999</v>
       </c>
       <c r="V54" s="73">
         <v>45928.763888888891</v>
       </c>
-      <c r="W54" s="86">
+      <c r="W54" s="85">
         <v>33.009906999999998</v>
       </c>
-      <c r="X54" s="86">
+      <c r="X54" s="85">
         <v>-117.74563999999999</v>
       </c>
       <c r="Y54" s="24">
@@ -6694,7 +6704,7 @@
       <c r="F55" s="21">
         <v>0.45833333333333331</v>
       </c>
-      <c r="G55" s="109" t="s">
+      <c r="G55" s="108" t="s">
         <v>148</v>
       </c>
       <c r="H55" s="19"/>
@@ -6725,19 +6735,19 @@
       <c r="S55" s="73">
         <v>45928.798611111109</v>
       </c>
-      <c r="T55" s="86">
+      <c r="T55" s="85">
         <v>33.016198000000003</v>
       </c>
-      <c r="U55" s="86">
+      <c r="U55" s="85">
         <v>-117.7423</v>
       </c>
       <c r="V55" s="73">
         <v>45929.621527777781</v>
       </c>
-      <c r="W55" s="86">
+      <c r="W55" s="85">
         <v>33.048772</v>
       </c>
-      <c r="X55" s="86">
+      <c r="X55" s="85">
         <v>-117.7334</v>
       </c>
       <c r="Y55" s="24">
@@ -6772,7 +6782,7 @@
       <c r="F56" s="21">
         <v>0.57291666666666663</v>
       </c>
-      <c r="G56" s="101" t="s">
+      <c r="G56" s="100" t="s">
         <v>183</v>
       </c>
       <c r="H56" s="19"/>
@@ -6850,7 +6860,7 @@
       <c r="F57" s="21">
         <v>0.57291666666666663</v>
       </c>
-      <c r="G57" s="101" t="s">
+      <c r="G57" s="100" t="s">
         <v>183</v>
       </c>
       <c r="H57" s="19"/>
@@ -6928,7 +6938,7 @@
       <c r="F58" s="21">
         <v>0.57291666666666663</v>
       </c>
-      <c r="G58" s="101" t="s">
+      <c r="G58" s="100" t="s">
         <v>183</v>
       </c>
       <c r="H58" s="19"/>
@@ -6994,7 +7004,7 @@
       <c r="D59" s="19"/>
       <c r="E59" s="20"/>
       <c r="F59" s="21"/>
-      <c r="G59" s="101"/>
+      <c r="G59" s="100"/>
       <c r="H59" s="19"/>
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
@@ -7027,7 +7037,7 @@
       <c r="D60" s="19"/>
       <c r="E60" s="20"/>
       <c r="F60" s="21"/>
-      <c r="G60" s="101"/>
+      <c r="G60" s="100"/>
       <c r="H60" s="19"/>
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
@@ -7060,7 +7070,7 @@
       <c r="D61" s="19"/>
       <c r="E61" s="20"/>
       <c r="F61" s="21"/>
-      <c r="G61" s="101"/>
+      <c r="G61" s="100"/>
       <c r="H61" s="19"/>
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
@@ -7093,7 +7103,7 @@
       <c r="D62" s="19"/>
       <c r="E62" s="20"/>
       <c r="F62" s="21"/>
-      <c r="G62" s="101"/>
+      <c r="G62" s="100"/>
       <c r="H62" s="19"/>
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
@@ -7126,7 +7136,7 @@
       <c r="D63" s="19"/>
       <c r="E63" s="20"/>
       <c r="F63" s="21"/>
-      <c r="G63" s="101"/>
+      <c r="G63" s="100"/>
       <c r="H63" s="19"/>
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
@@ -7159,7 +7169,7 @@
       <c r="D64" s="19"/>
       <c r="E64" s="20"/>
       <c r="F64" s="21"/>
-      <c r="G64" s="101"/>
+      <c r="G64" s="100"/>
       <c r="H64" s="19"/>
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
@@ -7192,7 +7202,7 @@
       <c r="D65" s="19"/>
       <c r="E65" s="20"/>
       <c r="F65" s="21"/>
-      <c r="G65" s="101"/>
+      <c r="G65" s="100"/>
       <c r="H65" s="19"/>
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
@@ -7225,7 +7235,7 @@
       <c r="D66" s="19"/>
       <c r="E66" s="20"/>
       <c r="F66" s="21"/>
-      <c r="G66" s="101"/>
+      <c r="G66" s="100"/>
       <c r="H66" s="19"/>
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
@@ -7258,7 +7268,7 @@
       <c r="D67" s="19"/>
       <c r="E67" s="20"/>
       <c r="F67" s="21"/>
-      <c r="G67" s="101"/>
+      <c r="G67" s="100"/>
       <c r="H67" s="19"/>
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
@@ -7291,7 +7301,7 @@
       <c r="D68" s="19"/>
       <c r="E68" s="20"/>
       <c r="F68" s="21"/>
-      <c r="G68" s="101"/>
+      <c r="G68" s="100"/>
       <c r="H68" s="19"/>
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
@@ -7324,7 +7334,7 @@
       <c r="D69" s="19"/>
       <c r="E69" s="20"/>
       <c r="F69" s="21"/>
-      <c r="G69" s="101"/>
+      <c r="G69" s="100"/>
       <c r="H69" s="19"/>
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
@@ -7357,7 +7367,7 @@
       <c r="D70" s="19"/>
       <c r="E70" s="20"/>
       <c r="F70" s="21"/>
-      <c r="G70" s="101"/>
+      <c r="G70" s="100"/>
       <c r="H70" s="19"/>
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
@@ -7390,7 +7400,7 @@
       <c r="D71" s="19"/>
       <c r="E71" s="20"/>
       <c r="F71" s="21"/>
-      <c r="G71" s="101"/>
+      <c r="G71" s="100"/>
       <c r="H71" s="19"/>
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
@@ -7423,7 +7433,7 @@
       <c r="D72" s="19"/>
       <c r="E72" s="20"/>
       <c r="F72" s="21"/>
-      <c r="G72" s="101"/>
+      <c r="G72" s="100"/>
       <c r="H72" s="19"/>
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
@@ -7456,7 +7466,7 @@
       <c r="D73" s="19"/>
       <c r="E73" s="20"/>
       <c r="F73" s="21"/>
-      <c r="G73" s="101"/>
+      <c r="G73" s="100"/>
       <c r="H73" s="19"/>
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
@@ -7489,7 +7499,7 @@
       <c r="D74" s="19"/>
       <c r="E74" s="20"/>
       <c r="F74" s="21"/>
-      <c r="G74" s="101"/>
+      <c r="G74" s="100"/>
       <c r="H74" s="19"/>
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
@@ -7522,7 +7532,7 @@
       <c r="D75" s="19"/>
       <c r="E75" s="20"/>
       <c r="F75" s="21"/>
-      <c r="G75" s="101"/>
+      <c r="G75" s="100"/>
       <c r="H75" s="19"/>
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
@@ -7555,7 +7565,7 @@
       <c r="D76" s="19"/>
       <c r="E76" s="20"/>
       <c r="F76" s="21"/>
-      <c r="G76" s="101"/>
+      <c r="G76" s="100"/>
       <c r="H76" s="19"/>
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
@@ -7588,7 +7598,7 @@
       <c r="D77" s="19"/>
       <c r="E77" s="20"/>
       <c r="F77" s="21"/>
-      <c r="G77" s="101"/>
+      <c r="G77" s="100"/>
       <c r="H77" s="19"/>
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
@@ -7621,7 +7631,7 @@
       <c r="D78" s="19"/>
       <c r="E78" s="20"/>
       <c r="F78" s="21"/>
-      <c r="G78" s="101"/>
+      <c r="G78" s="100"/>
       <c r="H78" s="19"/>
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
@@ -7654,7 +7664,7 @@
       <c r="D79" s="19"/>
       <c r="E79" s="20"/>
       <c r="F79" s="21"/>
-      <c r="G79" s="101"/>
+      <c r="G79" s="100"/>
       <c r="H79" s="19"/>
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
@@ -7687,7 +7697,7 @@
       <c r="D80" s="19"/>
       <c r="E80" s="20"/>
       <c r="F80" s="21"/>
-      <c r="G80" s="101"/>
+      <c r="G80" s="100"/>
       <c r="H80" s="19"/>
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
@@ -7720,7 +7730,7 @@
       <c r="D81" s="19"/>
       <c r="E81" s="20"/>
       <c r="F81" s="21"/>
-      <c r="G81" s="101"/>
+      <c r="G81" s="100"/>
       <c r="H81" s="19"/>
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
@@ -7753,7 +7763,7 @@
       <c r="D82" s="19"/>
       <c r="E82" s="20"/>
       <c r="F82" s="21"/>
-      <c r="G82" s="101"/>
+      <c r="G82" s="100"/>
       <c r="H82" s="19"/>
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
@@ -7786,7 +7796,7 @@
       <c r="D83" s="19"/>
       <c r="E83" s="20"/>
       <c r="F83" s="21"/>
-      <c r="G83" s="101"/>
+      <c r="G83" s="100"/>
       <c r="H83" s="19"/>
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
@@ -7819,7 +7829,7 @@
       <c r="D84" s="19"/>
       <c r="E84" s="20"/>
       <c r="F84" s="21"/>
-      <c r="G84" s="101"/>
+      <c r="G84" s="100"/>
       <c r="H84" s="19"/>
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
@@ -7852,7 +7862,7 @@
       <c r="D85" s="19"/>
       <c r="E85" s="20"/>
       <c r="F85" s="21"/>
-      <c r="G85" s="101"/>
+      <c r="G85" s="100"/>
       <c r="H85" s="19"/>
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
@@ -7885,7 +7895,7 @@
       <c r="D86" s="19"/>
       <c r="E86" s="20"/>
       <c r="F86" s="21"/>
-      <c r="G86" s="101"/>
+      <c r="G86" s="100"/>
       <c r="H86" s="19"/>
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
@@ -7918,7 +7928,7 @@
       <c r="D87" s="19"/>
       <c r="E87" s="20"/>
       <c r="F87" s="21"/>
-      <c r="G87" s="101"/>
+      <c r="G87" s="100"/>
       <c r="H87" s="19"/>
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
@@ -7951,7 +7961,7 @@
       <c r="D88" s="19"/>
       <c r="E88" s="20"/>
       <c r="F88" s="21"/>
-      <c r="G88" s="101"/>
+      <c r="G88" s="100"/>
       <c r="H88" s="19"/>
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
@@ -7984,7 +7994,7 @@
       <c r="D89" s="19"/>
       <c r="E89" s="20"/>
       <c r="F89" s="21"/>
-      <c r="G89" s="101"/>
+      <c r="G89" s="100"/>
       <c r="H89" s="19"/>
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
@@ -8017,7 +8027,7 @@
       <c r="D90" s="19"/>
       <c r="E90" s="20"/>
       <c r="F90" s="21"/>
-      <c r="G90" s="101"/>
+      <c r="G90" s="100"/>
       <c r="H90" s="19"/>
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
@@ -8050,7 +8060,7 @@
       <c r="D91" s="19"/>
       <c r="E91" s="20"/>
       <c r="F91" s="21"/>
-      <c r="G91" s="101"/>
+      <c r="G91" s="100"/>
       <c r="H91" s="19"/>
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
@@ -8083,7 +8093,7 @@
       <c r="D92" s="19"/>
       <c r="E92" s="20"/>
       <c r="F92" s="21"/>
-      <c r="G92" s="101"/>
+      <c r="G92" s="100"/>
       <c r="H92" s="19"/>
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
@@ -8116,7 +8126,7 @@
       <c r="D93" s="19"/>
       <c r="E93" s="20"/>
       <c r="F93" s="21"/>
-      <c r="G93" s="101"/>
+      <c r="G93" s="100"/>
       <c r="H93" s="19"/>
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
@@ -8149,7 +8159,7 @@
       <c r="D94" s="19"/>
       <c r="E94" s="20"/>
       <c r="F94" s="21"/>
-      <c r="G94" s="101"/>
+      <c r="G94" s="100"/>
       <c r="H94" s="19"/>
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
@@ -8182,7 +8192,7 @@
       <c r="D95" s="19"/>
       <c r="E95" s="20"/>
       <c r="F95" s="21"/>
-      <c r="G95" s="101"/>
+      <c r="G95" s="100"/>
       <c r="H95" s="19"/>
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
@@ -8215,7 +8225,7 @@
       <c r="D96" s="19"/>
       <c r="E96" s="20"/>
       <c r="F96" s="21"/>
-      <c r="G96" s="101"/>
+      <c r="G96" s="100"/>
       <c r="H96" s="19"/>
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
@@ -8248,7 +8258,7 @@
       <c r="D97" s="19"/>
       <c r="E97" s="20"/>
       <c r="F97" s="21"/>
-      <c r="G97" s="101"/>
+      <c r="G97" s="100"/>
       <c r="H97" s="19"/>
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
@@ -8281,7 +8291,7 @@
       <c r="D98" s="19"/>
       <c r="E98" s="20"/>
       <c r="F98" s="21"/>
-      <c r="G98" s="101"/>
+      <c r="G98" s="100"/>
       <c r="H98" s="19"/>
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
@@ -8314,7 +8324,7 @@
       <c r="D99" s="19"/>
       <c r="E99" s="20"/>
       <c r="F99" s="21"/>
-      <c r="G99" s="101"/>
+      <c r="G99" s="100"/>
       <c r="H99" s="19"/>
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
@@ -8347,7 +8357,7 @@
       <c r="D100" s="19"/>
       <c r="E100" s="20"/>
       <c r="F100" s="21"/>
-      <c r="G100" s="101"/>
+      <c r="G100" s="100"/>
       <c r="H100" s="19"/>
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
@@ -8380,7 +8390,7 @@
       <c r="D101" s="19"/>
       <c r="E101" s="20"/>
       <c r="F101" s="21"/>
-      <c r="G101" s="101"/>
+      <c r="G101" s="100"/>
       <c r="H101" s="19"/>
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
@@ -8413,7 +8423,7 @@
       <c r="D102" s="19"/>
       <c r="E102" s="20"/>
       <c r="F102" s="21"/>
-      <c r="G102" s="101"/>
+      <c r="G102" s="100"/>
       <c r="H102" s="19"/>
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
@@ -8446,7 +8456,7 @@
       <c r="D103" s="19"/>
       <c r="E103" s="20"/>
       <c r="F103" s="21"/>
-      <c r="G103" s="101"/>
+      <c r="G103" s="100"/>
       <c r="H103" s="19"/>
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
@@ -8479,7 +8489,7 @@
       <c r="D104" s="19"/>
       <c r="E104" s="20"/>
       <c r="F104" s="21"/>
-      <c r="G104" s="101"/>
+      <c r="G104" s="100"/>
       <c r="H104" s="19"/>
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
@@ -8512,7 +8522,7 @@
       <c r="D105" s="19"/>
       <c r="E105" s="20"/>
       <c r="F105" s="21"/>
-      <c r="G105" s="101"/>
+      <c r="G105" s="100"/>
       <c r="H105" s="19"/>
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
@@ -8545,7 +8555,7 @@
       <c r="D106" s="19"/>
       <c r="E106" s="20"/>
       <c r="F106" s="21"/>
-      <c r="G106" s="101"/>
+      <c r="G106" s="100"/>
       <c r="H106" s="19"/>
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
@@ -8578,7 +8588,7 @@
       <c r="D107" s="19"/>
       <c r="E107" s="20"/>
       <c r="F107" s="21"/>
-      <c r="G107" s="101"/>
+      <c r="G107" s="100"/>
       <c r="H107" s="19"/>
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
@@ -8611,7 +8621,7 @@
       <c r="D108" s="19"/>
       <c r="E108" s="20"/>
       <c r="F108" s="21"/>
-      <c r="G108" s="101"/>
+      <c r="G108" s="100"/>
       <c r="H108" s="19"/>
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
@@ -8644,7 +8654,7 @@
       <c r="D109" s="19"/>
       <c r="E109" s="20"/>
       <c r="F109" s="21"/>
-      <c r="G109" s="101"/>
+      <c r="G109" s="100"/>
       <c r="H109" s="19"/>
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
@@ -8677,7 +8687,7 @@
       <c r="D110" s="19"/>
       <c r="E110" s="20"/>
       <c r="F110" s="21"/>
-      <c r="G110" s="101"/>
+      <c r="G110" s="100"/>
       <c r="H110" s="19"/>
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
@@ -8710,7 +8720,7 @@
       <c r="D111" s="19"/>
       <c r="E111" s="20"/>
       <c r="F111" s="21"/>
-      <c r="G111" s="101"/>
+      <c r="G111" s="100"/>
       <c r="H111" s="19"/>
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
@@ -8743,7 +8753,7 @@
       <c r="D112" s="19"/>
       <c r="E112" s="20"/>
       <c r="F112" s="21"/>
-      <c r="G112" s="101"/>
+      <c r="G112" s="100"/>
       <c r="H112" s="19"/>
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
@@ -8776,7 +8786,7 @@
       <c r="D113" s="19"/>
       <c r="E113" s="20"/>
       <c r="F113" s="21"/>
-      <c r="G113" s="101"/>
+      <c r="G113" s="100"/>
       <c r="H113" s="19"/>
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
@@ -8809,7 +8819,7 @@
       <c r="D114" s="19"/>
       <c r="E114" s="20"/>
       <c r="F114" s="21"/>
-      <c r="G114" s="101"/>
+      <c r="G114" s="100"/>
       <c r="H114" s="19"/>
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
@@ -8842,7 +8852,7 @@
       <c r="D115" s="19"/>
       <c r="E115" s="20"/>
       <c r="F115" s="21"/>
-      <c r="G115" s="101"/>
+      <c r="G115" s="100"/>
       <c r="H115" s="19"/>
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
@@ -8875,7 +8885,7 @@
       <c r="D116" s="19"/>
       <c r="E116" s="20"/>
       <c r="F116" s="21"/>
-      <c r="G116" s="101"/>
+      <c r="G116" s="100"/>
       <c r="H116" s="19"/>
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
@@ -8908,7 +8918,7 @@
       <c r="D117" s="19"/>
       <c r="E117" s="20"/>
       <c r="F117" s="21"/>
-      <c r="G117" s="101"/>
+      <c r="G117" s="100"/>
       <c r="H117" s="19"/>
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
@@ -8941,7 +8951,7 @@
       <c r="D118" s="19"/>
       <c r="E118" s="20"/>
       <c r="F118" s="21"/>
-      <c r="G118" s="101"/>
+      <c r="G118" s="100"/>
       <c r="H118" s="19"/>
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
@@ -8974,7 +8984,7 @@
       <c r="D119" s="19"/>
       <c r="E119" s="20"/>
       <c r="F119" s="21"/>
-      <c r="G119" s="101"/>
+      <c r="G119" s="100"/>
       <c r="H119" s="19"/>
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
@@ -9007,7 +9017,7 @@
       <c r="D120" s="19"/>
       <c r="E120" s="20"/>
       <c r="F120" s="21"/>
-      <c r="G120" s="101"/>
+      <c r="G120" s="100"/>
       <c r="H120" s="19"/>
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
@@ -9040,7 +9050,7 @@
       <c r="D121" s="19"/>
       <c r="E121" s="20"/>
       <c r="F121" s="21"/>
-      <c r="G121" s="101"/>
+      <c r="G121" s="100"/>
       <c r="H121" s="19"/>
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
@@ -9073,7 +9083,7 @@
       <c r="D122" s="19"/>
       <c r="E122" s="20"/>
       <c r="F122" s="21"/>
-      <c r="G122" s="101"/>
+      <c r="G122" s="100"/>
       <c r="H122" s="19"/>
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
@@ -9106,7 +9116,7 @@
       <c r="D123" s="19"/>
       <c r="E123" s="20"/>
       <c r="F123" s="21"/>
-      <c r="G123" s="101"/>
+      <c r="G123" s="100"/>
       <c r="H123" s="19"/>
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
@@ -9139,7 +9149,7 @@
       <c r="D124" s="19"/>
       <c r="E124" s="20"/>
       <c r="F124" s="21"/>
-      <c r="G124" s="101"/>
+      <c r="G124" s="100"/>
       <c r="H124" s="19"/>
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
@@ -9172,7 +9182,7 @@
       <c r="D125" s="19"/>
       <c r="E125" s="20"/>
       <c r="F125" s="21"/>
-      <c r="G125" s="101"/>
+      <c r="G125" s="100"/>
       <c r="H125" s="19"/>
       <c r="I125" s="19"/>
       <c r="J125" s="20"/>
@@ -9205,7 +9215,7 @@
       <c r="D126" s="19"/>
       <c r="E126" s="20"/>
       <c r="F126" s="21"/>
-      <c r="G126" s="101"/>
+      <c r="G126" s="100"/>
       <c r="H126" s="19"/>
       <c r="I126" s="19"/>
       <c r="J126" s="20"/>
@@ -9238,7 +9248,7 @@
       <c r="D127" s="19"/>
       <c r="E127" s="20"/>
       <c r="F127" s="21"/>
-      <c r="G127" s="101"/>
+      <c r="G127" s="100"/>
       <c r="H127" s="19"/>
       <c r="I127" s="19"/>
       <c r="J127" s="20"/>
@@ -9271,7 +9281,7 @@
       <c r="D128" s="19"/>
       <c r="E128" s="20"/>
       <c r="F128" s="21"/>
-      <c r="G128" s="101"/>
+      <c r="G128" s="100"/>
       <c r="H128" s="19"/>
       <c r="I128" s="19"/>
       <c r="J128" s="20"/>
@@ -9304,7 +9314,7 @@
       <c r="D129" s="19"/>
       <c r="E129" s="20"/>
       <c r="F129" s="21"/>
-      <c r="G129" s="101"/>
+      <c r="G129" s="100"/>
       <c r="H129" s="19"/>
       <c r="I129" s="19"/>
       <c r="J129" s="20"/>
@@ -9337,7 +9347,7 @@
       <c r="D130" s="19"/>
       <c r="E130" s="20"/>
       <c r="F130" s="21"/>
-      <c r="G130" s="101"/>
+      <c r="G130" s="100"/>
       <c r="H130" s="19"/>
       <c r="I130" s="19"/>
       <c r="J130" s="20"/>
@@ -9370,7 +9380,7 @@
       <c r="D131" s="19"/>
       <c r="E131" s="20"/>
       <c r="F131" s="21"/>
-      <c r="G131" s="101"/>
+      <c r="G131" s="100"/>
       <c r="H131" s="19"/>
       <c r="I131" s="19"/>
       <c r="J131" s="20"/>
@@ -9403,7 +9413,7 @@
       <c r="D132" s="19"/>
       <c r="E132" s="20"/>
       <c r="F132" s="21"/>
-      <c r="G132" s="101"/>
+      <c r="G132" s="100"/>
       <c r="H132" s="19"/>
       <c r="I132" s="19"/>
       <c r="J132" s="20"/>
@@ -9436,7 +9446,7 @@
       <c r="D133" s="19"/>
       <c r="E133" s="20"/>
       <c r="F133" s="21"/>
-      <c r="G133" s="101"/>
+      <c r="G133" s="100"/>
       <c r="H133" s="19"/>
       <c r="I133" s="19"/>
       <c r="J133" s="20"/>
@@ -9469,7 +9479,7 @@
       <c r="D134" s="19"/>
       <c r="E134" s="20"/>
       <c r="F134" s="21"/>
-      <c r="G134" s="101"/>
+      <c r="G134" s="100"/>
       <c r="H134" s="19"/>
       <c r="I134" s="19"/>
       <c r="J134" s="20"/>
@@ -9502,7 +9512,7 @@
       <c r="D135" s="19"/>
       <c r="E135" s="20"/>
       <c r="F135" s="21"/>
-      <c r="G135" s="101"/>
+      <c r="G135" s="100"/>
       <c r="H135" s="19"/>
       <c r="I135" s="19"/>
       <c r="J135" s="20"/>
@@ -9535,7 +9545,7 @@
       <c r="D136" s="19"/>
       <c r="E136" s="20"/>
       <c r="F136" s="21"/>
-      <c r="G136" s="101"/>
+      <c r="G136" s="100"/>
       <c r="H136" s="19"/>
       <c r="I136" s="19"/>
       <c r="J136" s="20"/>
@@ -9568,7 +9578,7 @@
       <c r="D137" s="19"/>
       <c r="E137" s="20"/>
       <c r="F137" s="21"/>
-      <c r="G137" s="101"/>
+      <c r="G137" s="100"/>
       <c r="H137" s="19"/>
       <c r="I137" s="19"/>
       <c r="J137" s="20"/>
@@ -9601,7 +9611,7 @@
       <c r="D138" s="19"/>
       <c r="E138" s="20"/>
       <c r="F138" s="21"/>
-      <c r="G138" s="101"/>
+      <c r="G138" s="100"/>
       <c r="H138" s="19"/>
       <c r="I138" s="19"/>
       <c r="J138" s="20"/>
@@ -9634,7 +9644,7 @@
       <c r="D139" s="19"/>
       <c r="E139" s="20"/>
       <c r="F139" s="21"/>
-      <c r="G139" s="101"/>
+      <c r="G139" s="100"/>
       <c r="H139" s="19"/>
       <c r="I139" s="19"/>
       <c r="J139" s="20"/>
@@ -9667,7 +9677,7 @@
       <c r="D140" s="19"/>
       <c r="E140" s="20"/>
       <c r="F140" s="21"/>
-      <c r="G140" s="101"/>
+      <c r="G140" s="100"/>
       <c r="H140" s="19"/>
       <c r="I140" s="19"/>
       <c r="J140" s="20"/>
@@ -9700,7 +9710,7 @@
       <c r="D141" s="19"/>
       <c r="E141" s="20"/>
       <c r="F141" s="21"/>
-      <c r="G141" s="101"/>
+      <c r="G141" s="100"/>
       <c r="H141" s="19"/>
       <c r="I141" s="19"/>
       <c r="J141" s="20"/>
@@ -9733,7 +9743,7 @@
       <c r="D142" s="19"/>
       <c r="E142" s="20"/>
       <c r="F142" s="21"/>
-      <c r="G142" s="101"/>
+      <c r="G142" s="100"/>
       <c r="H142" s="19"/>
       <c r="I142" s="19"/>
       <c r="J142" s="20"/>
@@ -9766,7 +9776,7 @@
       <c r="D143" s="19"/>
       <c r="E143" s="20"/>
       <c r="F143" s="21"/>
-      <c r="G143" s="101"/>
+      <c r="G143" s="100"/>
       <c r="H143" s="19"/>
       <c r="I143" s="19"/>
       <c r="J143" s="20"/>
@@ -9799,7 +9809,7 @@
       <c r="D144" s="19"/>
       <c r="E144" s="20"/>
       <c r="F144" s="21"/>
-      <c r="G144" s="101"/>
+      <c r="G144" s="100"/>
       <c r="H144" s="19"/>
       <c r="I144" s="19"/>
       <c r="J144" s="20"/>
@@ -9832,7 +9842,7 @@
       <c r="D145" s="19"/>
       <c r="E145" s="20"/>
       <c r="F145" s="21"/>
-      <c r="G145" s="101"/>
+      <c r="G145" s="100"/>
       <c r="H145" s="19"/>
       <c r="I145" s="19"/>
       <c r="J145" s="20"/>
@@ -9865,7 +9875,7 @@
       <c r="D146" s="19"/>
       <c r="E146" s="20"/>
       <c r="F146" s="21"/>
-      <c r="G146" s="101"/>
+      <c r="G146" s="100"/>
       <c r="H146" s="19"/>
       <c r="I146" s="19"/>
       <c r="J146" s="20"/>
@@ -9898,7 +9908,7 @@
       <c r="D147" s="19"/>
       <c r="E147" s="20"/>
       <c r="F147" s="21"/>
-      <c r="G147" s="101"/>
+      <c r="G147" s="100"/>
       <c r="H147" s="19"/>
       <c r="I147" s="19"/>
       <c r="J147" s="20"/>
@@ -9931,7 +9941,7 @@
       <c r="D148" s="19"/>
       <c r="E148" s="20"/>
       <c r="F148" s="21"/>
-      <c r="G148" s="101"/>
+      <c r="G148" s="100"/>
       <c r="H148" s="19"/>
       <c r="I148" s="19"/>
       <c r="J148" s="20"/>
@@ -9964,7 +9974,7 @@
       <c r="D149" s="19"/>
       <c r="E149" s="20"/>
       <c r="F149" s="21"/>
-      <c r="G149" s="101"/>
+      <c r="G149" s="100"/>
       <c r="H149" s="19"/>
       <c r="I149" s="19"/>
       <c r="J149" s="20"/>
@@ -9997,7 +10007,7 @@
       <c r="D150" s="19"/>
       <c r="E150" s="20"/>
       <c r="F150" s="21"/>
-      <c r="G150" s="101"/>
+      <c r="G150" s="100"/>
       <c r="H150" s="19"/>
       <c r="I150" s="19"/>
       <c r="J150" s="20"/>
@@ -10030,7 +10040,7 @@
       <c r="D151" s="19"/>
       <c r="E151" s="20"/>
       <c r="F151" s="21"/>
-      <c r="G151" s="101"/>
+      <c r="G151" s="100"/>
       <c r="H151" s="19"/>
       <c r="I151" s="19"/>
       <c r="J151" s="20"/>
@@ -10063,7 +10073,7 @@
       <c r="D152" s="19"/>
       <c r="E152" s="20"/>
       <c r="F152" s="21"/>
-      <c r="G152" s="101"/>
+      <c r="G152" s="100"/>
       <c r="H152" s="19"/>
       <c r="I152" s="19"/>
       <c r="J152" s="20"/>
@@ -10096,7 +10106,7 @@
       <c r="D153" s="19"/>
       <c r="E153" s="20"/>
       <c r="F153" s="21"/>
-      <c r="G153" s="101"/>
+      <c r="G153" s="100"/>
       <c r="H153" s="19"/>
       <c r="I153" s="19"/>
       <c r="J153" s="20"/>
@@ -10129,7 +10139,7 @@
       <c r="D154" s="19"/>
       <c r="E154" s="20"/>
       <c r="F154" s="21"/>
-      <c r="G154" s="101"/>
+      <c r="G154" s="100"/>
       <c r="H154" s="19"/>
       <c r="I154" s="19"/>
       <c r="J154" s="20"/>
@@ -10162,7 +10172,7 @@
       <c r="D155" s="19"/>
       <c r="E155" s="20"/>
       <c r="F155" s="21"/>
-      <c r="G155" s="101"/>
+      <c r="G155" s="100"/>
       <c r="H155" s="19"/>
       <c r="I155" s="19"/>
       <c r="J155" s="20"/>
@@ -10195,7 +10205,7 @@
       <c r="D156" s="19"/>
       <c r="E156" s="20"/>
       <c r="F156" s="21"/>
-      <c r="G156" s="101"/>
+      <c r="G156" s="100"/>
       <c r="H156" s="19"/>
       <c r="I156" s="19"/>
       <c r="J156" s="20"/>
@@ -10228,7 +10238,7 @@
       <c r="D157" s="19"/>
       <c r="E157" s="20"/>
       <c r="F157" s="21"/>
-      <c r="G157" s="101"/>
+      <c r="G157" s="100"/>
       <c r="H157" s="19"/>
       <c r="I157" s="19"/>
       <c r="J157" s="20"/>
@@ -10261,7 +10271,7 @@
       <c r="D158" s="19"/>
       <c r="E158" s="20"/>
       <c r="F158" s="21"/>
-      <c r="G158" s="101"/>
+      <c r="G158" s="100"/>
       <c r="H158" s="19"/>
       <c r="I158" s="19"/>
       <c r="J158" s="20"/>
@@ -10294,7 +10304,7 @@
       <c r="D159" s="19"/>
       <c r="E159" s="20"/>
       <c r="F159" s="21"/>
-      <c r="G159" s="101"/>
+      <c r="G159" s="100"/>
       <c r="H159" s="19"/>
       <c r="I159" s="19"/>
       <c r="J159" s="20"/>
@@ -10327,7 +10337,7 @@
       <c r="D160" s="19"/>
       <c r="E160" s="20"/>
       <c r="F160" s="21"/>
-      <c r="G160" s="101"/>
+      <c r="G160" s="100"/>
       <c r="H160" s="19"/>
       <c r="I160" s="19"/>
       <c r="J160" s="20"/>
@@ -10360,7 +10370,7 @@
       <c r="D161" s="19"/>
       <c r="E161" s="20"/>
       <c r="F161" s="21"/>
-      <c r="G161" s="101"/>
+      <c r="G161" s="100"/>
       <c r="H161" s="19"/>
       <c r="I161" s="19"/>
       <c r="J161" s="20"/>
@@ -10393,7 +10403,7 @@
       <c r="D162" s="19"/>
       <c r="E162" s="20"/>
       <c r="F162" s="21"/>
-      <c r="G162" s="101"/>
+      <c r="G162" s="100"/>
       <c r="H162" s="19"/>
       <c r="I162" s="19"/>
       <c r="J162" s="20"/>
@@ -10426,7 +10436,7 @@
       <c r="D163" s="19"/>
       <c r="E163" s="20"/>
       <c r="F163" s="21"/>
-      <c r="G163" s="101"/>
+      <c r="G163" s="100"/>
       <c r="H163" s="19"/>
       <c r="I163" s="19"/>
       <c r="J163" s="20"/>
@@ -10459,7 +10469,7 @@
       <c r="D164" s="19"/>
       <c r="E164" s="20"/>
       <c r="F164" s="21"/>
-      <c r="G164" s="101"/>
+      <c r="G164" s="100"/>
       <c r="H164" s="19"/>
       <c r="I164" s="19"/>
       <c r="J164" s="20"/>
@@ -10492,7 +10502,7 @@
       <c r="D165" s="19"/>
       <c r="E165" s="20"/>
       <c r="F165" s="21"/>
-      <c r="G165" s="101"/>
+      <c r="G165" s="100"/>
       <c r="H165" s="19"/>
       <c r="I165" s="19"/>
       <c r="J165" s="20"/>
@@ -10525,7 +10535,7 @@
       <c r="D166" s="19"/>
       <c r="E166" s="20"/>
       <c r="F166" s="21"/>
-      <c r="G166" s="101"/>
+      <c r="G166" s="100"/>
       <c r="H166" s="19"/>
       <c r="I166" s="19"/>
       <c r="J166" s="20"/>
@@ -10558,7 +10568,7 @@
       <c r="D167" s="19"/>
       <c r="E167" s="20"/>
       <c r="F167" s="21"/>
-      <c r="G167" s="101"/>
+      <c r="G167" s="100"/>
       <c r="H167" s="19"/>
       <c r="I167" s="19"/>
       <c r="J167" s="20"/>
@@ -10591,7 +10601,7 @@
       <c r="D168" s="19"/>
       <c r="E168" s="20"/>
       <c r="F168" s="21"/>
-      <c r="G168" s="101"/>
+      <c r="G168" s="100"/>
       <c r="H168" s="19"/>
       <c r="I168" s="19"/>
       <c r="J168" s="20"/>
@@ -10624,7 +10634,7 @@
       <c r="D169" s="19"/>
       <c r="E169" s="20"/>
       <c r="F169" s="21"/>
-      <c r="G169" s="101"/>
+      <c r="G169" s="100"/>
       <c r="H169" s="19"/>
       <c r="I169" s="19"/>
       <c r="J169" s="20"/>
@@ -10657,7 +10667,7 @@
       <c r="D170" s="19"/>
       <c r="E170" s="20"/>
       <c r="F170" s="21"/>
-      <c r="G170" s="101"/>
+      <c r="G170" s="100"/>
       <c r="H170" s="19"/>
       <c r="I170" s="19"/>
       <c r="J170" s="20"/>
@@ -10690,7 +10700,7 @@
       <c r="D171" s="19"/>
       <c r="E171" s="20"/>
       <c r="F171" s="21"/>
-      <c r="G171" s="101"/>
+      <c r="G171" s="100"/>
       <c r="H171" s="19"/>
       <c r="I171" s="19"/>
       <c r="J171" s="20"/>
@@ -10723,7 +10733,7 @@
       <c r="D172" s="19"/>
       <c r="E172" s="20"/>
       <c r="F172" s="21"/>
-      <c r="G172" s="101"/>
+      <c r="G172" s="100"/>
       <c r="H172" s="19"/>
       <c r="I172" s="19"/>
       <c r="J172" s="20"/>
@@ -10756,7 +10766,7 @@
       <c r="D173" s="19"/>
       <c r="E173" s="20"/>
       <c r="F173" s="21"/>
-      <c r="G173" s="101"/>
+      <c r="G173" s="100"/>
       <c r="H173" s="19"/>
       <c r="I173" s="19"/>
       <c r="J173" s="20"/>
@@ -10789,7 +10799,7 @@
       <c r="D174" s="19"/>
       <c r="E174" s="20"/>
       <c r="F174" s="21"/>
-      <c r="G174" s="101"/>
+      <c r="G174" s="100"/>
       <c r="H174" s="19"/>
       <c r="I174" s="19"/>
       <c r="J174" s="20"/>
@@ -10822,7 +10832,7 @@
       <c r="D175" s="19"/>
       <c r="E175" s="20"/>
       <c r="F175" s="21"/>
-      <c r="G175" s="101"/>
+      <c r="G175" s="100"/>
       <c r="H175" s="19"/>
       <c r="I175" s="19"/>
       <c r="J175" s="20"/>
@@ -10855,7 +10865,7 @@
       <c r="D176" s="19"/>
       <c r="E176" s="20"/>
       <c r="F176" s="21"/>
-      <c r="G176" s="101"/>
+      <c r="G176" s="100"/>
       <c r="H176" s="19"/>
       <c r="I176" s="19"/>
       <c r="J176" s="20"/>
@@ -10888,7 +10898,7 @@
       <c r="D177" s="19"/>
       <c r="E177" s="20"/>
       <c r="F177" s="21"/>
-      <c r="G177" s="101"/>
+      <c r="G177" s="100"/>
       <c r="H177" s="19"/>
       <c r="I177" s="19"/>
       <c r="J177" s="20"/>
@@ -10921,7 +10931,7 @@
       <c r="D178" s="19"/>
       <c r="E178" s="20"/>
       <c r="F178" s="21"/>
-      <c r="G178" s="101"/>
+      <c r="G178" s="100"/>
       <c r="H178" s="19"/>
       <c r="I178" s="19"/>
       <c r="J178" s="20"/>
@@ -10954,7 +10964,7 @@
       <c r="D179" s="19"/>
       <c r="E179" s="20"/>
       <c r="F179" s="21"/>
-      <c r="G179" s="101"/>
+      <c r="G179" s="100"/>
       <c r="H179" s="19"/>
       <c r="I179" s="19"/>
       <c r="J179" s="20"/>
@@ -10987,7 +10997,7 @@
       <c r="D180" s="19"/>
       <c r="E180" s="20"/>
       <c r="F180" s="21"/>
-      <c r="G180" s="101"/>
+      <c r="G180" s="100"/>
       <c r="H180" s="19"/>
       <c r="I180" s="19"/>
       <c r="J180" s="20"/>
@@ -11020,7 +11030,7 @@
       <c r="D181" s="19"/>
       <c r="E181" s="20"/>
       <c r="F181" s="21"/>
-      <c r="G181" s="101"/>
+      <c r="G181" s="100"/>
       <c r="H181" s="19"/>
       <c r="I181" s="19"/>
       <c r="J181" s="20"/>
@@ -11053,7 +11063,7 @@
       <c r="D182" s="19"/>
       <c r="E182" s="20"/>
       <c r="F182" s="21"/>
-      <c r="G182" s="101"/>
+      <c r="G182" s="100"/>
       <c r="H182" s="19"/>
       <c r="I182" s="19"/>
       <c r="J182" s="20"/>
@@ -11086,7 +11096,7 @@
       <c r="D183" s="19"/>
       <c r="E183" s="20"/>
       <c r="F183" s="21"/>
-      <c r="G183" s="101"/>
+      <c r="G183" s="100"/>
       <c r="H183" s="19"/>
       <c r="I183" s="19"/>
       <c r="J183" s="20"/>
@@ -11119,7 +11129,7 @@
       <c r="D184" s="19"/>
       <c r="E184" s="20"/>
       <c r="F184" s="21"/>
-      <c r="G184" s="101"/>
+      <c r="G184" s="100"/>
       <c r="H184" s="19"/>
       <c r="I184" s="19"/>
       <c r="J184" s="20"/>
@@ -11152,7 +11162,7 @@
       <c r="D185" s="19"/>
       <c r="E185" s="20"/>
       <c r="F185" s="21"/>
-      <c r="G185" s="101"/>
+      <c r="G185" s="100"/>
       <c r="H185" s="19"/>
       <c r="I185" s="19"/>
       <c r="J185" s="20"/>
@@ -11185,7 +11195,7 @@
       <c r="D186" s="19"/>
       <c r="E186" s="20"/>
       <c r="F186" s="21"/>
-      <c r="G186" s="101"/>
+      <c r="G186" s="100"/>
       <c r="H186" s="19"/>
       <c r="I186" s="19"/>
       <c r="J186" s="20"/>
@@ -11218,7 +11228,7 @@
       <c r="D187" s="19"/>
       <c r="E187" s="20"/>
       <c r="F187" s="21"/>
-      <c r="G187" s="101"/>
+      <c r="G187" s="100"/>
       <c r="H187" s="19"/>
       <c r="I187" s="19"/>
       <c r="J187" s="20"/>
@@ -11251,7 +11261,7 @@
       <c r="D188" s="19"/>
       <c r="E188" s="20"/>
       <c r="F188" s="21"/>
-      <c r="G188" s="101"/>
+      <c r="G188" s="100"/>
       <c r="H188" s="19"/>
       <c r="I188" s="19"/>
       <c r="J188" s="20"/>
@@ -11284,7 +11294,7 @@
       <c r="D189" s="19"/>
       <c r="E189" s="20"/>
       <c r="F189" s="21"/>
-      <c r="G189" s="101"/>
+      <c r="G189" s="100"/>
       <c r="H189" s="19"/>
       <c r="I189" s="19"/>
       <c r="J189" s="20"/>
@@ -11317,7 +11327,7 @@
       <c r="D190" s="19"/>
       <c r="E190" s="20"/>
       <c r="F190" s="21"/>
-      <c r="G190" s="101"/>
+      <c r="G190" s="100"/>
       <c r="H190" s="19"/>
       <c r="I190" s="19"/>
       <c r="J190" s="20"/>
@@ -11350,7 +11360,7 @@
       <c r="D191" s="19"/>
       <c r="E191" s="20"/>
       <c r="F191" s="21"/>
-      <c r="G191" s="101"/>
+      <c r="G191" s="100"/>
       <c r="H191" s="19"/>
       <c r="I191" s="19"/>
       <c r="J191" s="20"/>
@@ -11383,7 +11393,7 @@
       <c r="D192" s="19"/>
       <c r="E192" s="20"/>
       <c r="F192" s="21"/>
-      <c r="G192" s="101"/>
+      <c r="G192" s="100"/>
       <c r="H192" s="19"/>
       <c r="I192" s="19"/>
       <c r="J192" s="20"/>
@@ -11416,7 +11426,7 @@
       <c r="D193" s="19"/>
       <c r="E193" s="20"/>
       <c r="F193" s="21"/>
-      <c r="G193" s="101"/>
+      <c r="G193" s="100"/>
       <c r="H193" s="19"/>
       <c r="I193" s="19"/>
       <c r="J193" s="20"/>
@@ -11449,7 +11459,7 @@
       <c r="D194" s="19"/>
       <c r="E194" s="20"/>
       <c r="F194" s="21"/>
-      <c r="G194" s="101"/>
+      <c r="G194" s="100"/>
       <c r="H194" s="19"/>
       <c r="I194" s="19"/>
       <c r="J194" s="20"/>
@@ -11482,7 +11492,7 @@
       <c r="D195" s="19"/>
       <c r="E195" s="20"/>
       <c r="F195" s="21"/>
-      <c r="G195" s="101"/>
+      <c r="G195" s="100"/>
       <c r="H195" s="19"/>
       <c r="I195" s="19"/>
       <c r="J195" s="20"/>
@@ -11515,7 +11525,7 @@
       <c r="D196" s="19"/>
       <c r="E196" s="20"/>
       <c r="F196" s="21"/>
-      <c r="G196" s="101"/>
+      <c r="G196" s="100"/>
       <c r="H196" s="19"/>
       <c r="I196" s="19"/>
       <c r="J196" s="20"/>
@@ -11548,7 +11558,7 @@
       <c r="D197" s="19"/>
       <c r="E197" s="20"/>
       <c r="F197" s="21"/>
-      <c r="G197" s="101"/>
+      <c r="G197" s="100"/>
       <c r="H197" s="19"/>
       <c r="I197" s="19"/>
       <c r="J197" s="20"/>
@@ -11581,7 +11591,7 @@
       <c r="D198" s="19"/>
       <c r="E198" s="20"/>
       <c r="F198" s="21"/>
-      <c r="G198" s="101"/>
+      <c r="G198" s="100"/>
       <c r="H198" s="19"/>
       <c r="I198" s="19"/>
       <c r="J198" s="20"/>
@@ -11614,7 +11624,7 @@
       <c r="D199" s="19"/>
       <c r="E199" s="20"/>
       <c r="F199" s="21"/>
-      <c r="G199" s="101"/>
+      <c r="G199" s="100"/>
       <c r="H199" s="19"/>
       <c r="I199" s="19"/>
       <c r="J199" s="20"/>
@@ -11647,7 +11657,7 @@
       <c r="D200" s="19"/>
       <c r="E200" s="20"/>
       <c r="F200" s="21"/>
-      <c r="G200" s="101"/>
+      <c r="G200" s="100"/>
       <c r="H200" s="19"/>
       <c r="I200" s="19"/>
       <c r="J200" s="20"/>
@@ -11680,7 +11690,7 @@
       <c r="D201" s="19"/>
       <c r="E201" s="20"/>
       <c r="F201" s="21"/>
-      <c r="G201" s="101"/>
+      <c r="G201" s="100"/>
       <c r="H201" s="19"/>
       <c r="I201" s="19"/>
       <c r="J201" s="20"/>
@@ -11713,7 +11723,7 @@
       <c r="D202" s="19"/>
       <c r="E202" s="20"/>
       <c r="F202" s="21"/>
-      <c r="G202" s="101"/>
+      <c r="G202" s="100"/>
       <c r="H202" s="19"/>
       <c r="I202" s="19"/>
       <c r="J202" s="20"/>
@@ -11746,7 +11756,7 @@
       <c r="D203" s="19"/>
       <c r="E203" s="20"/>
       <c r="F203" s="21"/>
-      <c r="G203" s="101"/>
+      <c r="G203" s="100"/>
       <c r="H203" s="19"/>
       <c r="I203" s="19"/>
       <c r="J203" s="20"/>
@@ -11779,7 +11789,7 @@
       <c r="D204" s="19"/>
       <c r="E204" s="20"/>
       <c r="F204" s="21"/>
-      <c r="G204" s="101"/>
+      <c r="G204" s="100"/>
       <c r="H204" s="19"/>
       <c r="I204" s="19"/>
       <c r="J204" s="20"/>
@@ -11812,7 +11822,7 @@
       <c r="D205" s="19"/>
       <c r="E205" s="20"/>
       <c r="F205" s="21"/>
-      <c r="G205" s="101"/>
+      <c r="G205" s="100"/>
       <c r="H205" s="19"/>
       <c r="I205" s="19"/>
       <c r="J205" s="20"/>
@@ -11845,7 +11855,7 @@
       <c r="D206" s="19"/>
       <c r="E206" s="20"/>
       <c r="F206" s="21"/>
-      <c r="G206" s="101"/>
+      <c r="G206" s="100"/>
       <c r="H206" s="19"/>
       <c r="I206" s="19"/>
       <c r="J206" s="20"/>
@@ -11878,7 +11888,7 @@
       <c r="D207" s="19"/>
       <c r="E207" s="20"/>
       <c r="F207" s="21"/>
-      <c r="G207" s="101"/>
+      <c r="G207" s="100"/>
       <c r="H207" s="19"/>
       <c r="I207" s="19"/>
       <c r="J207" s="20"/>
@@ -11911,7 +11921,7 @@
       <c r="D208" s="19"/>
       <c r="E208" s="20"/>
       <c r="F208" s="21"/>
-      <c r="G208" s="101"/>
+      <c r="G208" s="100"/>
       <c r="H208" s="19"/>
       <c r="I208" s="19"/>
       <c r="J208" s="20"/>
@@ -11944,7 +11954,7 @@
       <c r="D209" s="19"/>
       <c r="E209" s="20"/>
       <c r="F209" s="21"/>
-      <c r="G209" s="101"/>
+      <c r="G209" s="100"/>
       <c r="H209" s="19"/>
       <c r="I209" s="19"/>
       <c r="J209" s="20"/>
@@ -11977,7 +11987,7 @@
       <c r="D210" s="19"/>
       <c r="E210" s="20"/>
       <c r="F210" s="21"/>
-      <c r="G210" s="101"/>
+      <c r="G210" s="100"/>
       <c r="H210" s="19"/>
       <c r="I210" s="19"/>
       <c r="J210" s="20"/>
@@ -12010,7 +12020,7 @@
       <c r="D211" s="19"/>
       <c r="E211" s="20"/>
       <c r="F211" s="21"/>
-      <c r="G211" s="101"/>
+      <c r="G211" s="100"/>
       <c r="H211" s="19"/>
       <c r="I211" s="19"/>
       <c r="J211" s="20"/>
@@ -12043,7 +12053,7 @@
       <c r="D212" s="19"/>
       <c r="E212" s="20"/>
       <c r="F212" s="21"/>
-      <c r="G212" s="101"/>
+      <c r="G212" s="100"/>
       <c r="H212" s="19"/>
       <c r="I212" s="19"/>
       <c r="J212" s="20"/>
@@ -12076,7 +12086,7 @@
       <c r="D213" s="19"/>
       <c r="E213" s="20"/>
       <c r="F213" s="21"/>
-      <c r="G213" s="101"/>
+      <c r="G213" s="100"/>
       <c r="H213" s="19"/>
       <c r="I213" s="19"/>
       <c r="J213" s="20"/>
@@ -12109,7 +12119,7 @@
       <c r="D214" s="19"/>
       <c r="E214" s="20"/>
       <c r="F214" s="21"/>
-      <c r="G214" s="101"/>
+      <c r="G214" s="100"/>
       <c r="H214" s="19"/>
       <c r="I214" s="19"/>
       <c r="J214" s="20"/>
@@ -12142,7 +12152,7 @@
       <c r="D215" s="19"/>
       <c r="E215" s="20"/>
       <c r="F215" s="21"/>
-      <c r="G215" s="101"/>
+      <c r="G215" s="100"/>
       <c r="H215" s="19"/>
       <c r="I215" s="19"/>
       <c r="J215" s="20"/>
@@ -12175,7 +12185,7 @@
       <c r="D216" s="19"/>
       <c r="E216" s="20"/>
       <c r="F216" s="21"/>
-      <c r="G216" s="101"/>
+      <c r="G216" s="100"/>
       <c r="H216" s="19"/>
       <c r="I216" s="19"/>
       <c r="J216" s="20"/>
@@ -12208,7 +12218,7 @@
       <c r="D217" s="19"/>
       <c r="E217" s="20"/>
       <c r="F217" s="21"/>
-      <c r="G217" s="101"/>
+      <c r="G217" s="100"/>
       <c r="H217" s="19"/>
       <c r="I217" s="19"/>
       <c r="J217" s="20"/>
@@ -12241,7 +12251,7 @@
       <c r="D218" s="19"/>
       <c r="E218" s="20"/>
       <c r="F218" s="21"/>
-      <c r="G218" s="101"/>
+      <c r="G218" s="100"/>
       <c r="H218" s="19"/>
       <c r="I218" s="19"/>
       <c r="J218" s="20"/>
@@ -12274,7 +12284,7 @@
       <c r="D219" s="19"/>
       <c r="E219" s="20"/>
       <c r="F219" s="21"/>
-      <c r="G219" s="101"/>
+      <c r="G219" s="100"/>
       <c r="H219" s="19"/>
       <c r="I219" s="19"/>
       <c r="J219" s="20"/>
@@ -12307,7 +12317,7 @@
       <c r="D220" s="19"/>
       <c r="E220" s="20"/>
       <c r="F220" s="21"/>
-      <c r="G220" s="101"/>
+      <c r="G220" s="100"/>
       <c r="H220" s="19"/>
       <c r="I220" s="19"/>
       <c r="J220" s="20"/>
@@ -12340,7 +12350,7 @@
       <c r="D221" s="19"/>
       <c r="E221" s="20"/>
       <c r="F221" s="21"/>
-      <c r="G221" s="101"/>
+      <c r="G221" s="100"/>
       <c r="H221" s="19"/>
       <c r="I221" s="19"/>
       <c r="J221" s="20"/>
@@ -12373,7 +12383,7 @@
       <c r="D222" s="19"/>
       <c r="E222" s="20"/>
       <c r="F222" s="21"/>
-      <c r="G222" s="101"/>
+      <c r="G222" s="100"/>
       <c r="H222" s="19"/>
       <c r="I222" s="19"/>
       <c r="J222" s="20"/>
@@ -12406,7 +12416,7 @@
       <c r="D223" s="19"/>
       <c r="E223" s="20"/>
       <c r="F223" s="21"/>
-      <c r="G223" s="101"/>
+      <c r="G223" s="100"/>
       <c r="H223" s="19"/>
       <c r="I223" s="19"/>
       <c r="J223" s="20"/>
@@ -12439,7 +12449,7 @@
       <c r="D224" s="19"/>
       <c r="E224" s="20"/>
       <c r="F224" s="21"/>
-      <c r="G224" s="101"/>
+      <c r="G224" s="100"/>
       <c r="H224" s="19"/>
       <c r="I224" s="19"/>
       <c r="J224" s="20"/>
@@ -12472,7 +12482,7 @@
       <c r="D225" s="19"/>
       <c r="E225" s="20"/>
       <c r="F225" s="21"/>
-      <c r="G225" s="101"/>
+      <c r="G225" s="100"/>
       <c r="H225" s="19"/>
       <c r="I225" s="19"/>
       <c r="J225" s="20"/>
@@ -12505,7 +12515,7 @@
       <c r="D226" s="19"/>
       <c r="E226" s="20"/>
       <c r="F226" s="21"/>
-      <c r="G226" s="101"/>
+      <c r="G226" s="100"/>
       <c r="H226" s="19"/>
       <c r="I226" s="19"/>
       <c r="J226" s="20"/>
@@ -12538,7 +12548,7 @@
       <c r="D227" s="19"/>
       <c r="E227" s="20"/>
       <c r="F227" s="21"/>
-      <c r="G227" s="101"/>
+      <c r="G227" s="100"/>
       <c r="H227" s="19"/>
       <c r="I227" s="19"/>
       <c r="J227" s="20"/>
@@ -12571,7 +12581,7 @@
       <c r="D228" s="19"/>
       <c r="E228" s="20"/>
       <c r="F228" s="21"/>
-      <c r="G228" s="101"/>
+      <c r="G228" s="100"/>
       <c r="H228" s="19"/>
       <c r="I228" s="19"/>
       <c r="J228" s="20"/>
@@ -12604,7 +12614,7 @@
       <c r="D229" s="19"/>
       <c r="E229" s="20"/>
       <c r="F229" s="21"/>
-      <c r="G229" s="101"/>
+      <c r="G229" s="100"/>
       <c r="H229" s="19"/>
       <c r="I229" s="19"/>
       <c r="J229" s="20"/>
@@ -12637,7 +12647,7 @@
       <c r="D230" s="19"/>
       <c r="E230" s="20"/>
       <c r="F230" s="21"/>
-      <c r="G230" s="101"/>
+      <c r="G230" s="100"/>
       <c r="H230" s="19"/>
       <c r="I230" s="19"/>
       <c r="J230" s="20"/>
@@ -12670,7 +12680,7 @@
       <c r="D231" s="19"/>
       <c r="E231" s="20"/>
       <c r="F231" s="21"/>
-      <c r="G231" s="101"/>
+      <c r="G231" s="100"/>
       <c r="H231" s="19"/>
       <c r="I231" s="19"/>
       <c r="J231" s="20"/>
@@ -12703,7 +12713,7 @@
       <c r="D232" s="19"/>
       <c r="E232" s="20"/>
       <c r="F232" s="21"/>
-      <c r="G232" s="101"/>
+      <c r="G232" s="100"/>
       <c r="H232" s="19"/>
       <c r="I232" s="19"/>
       <c r="J232" s="20"/>
@@ -12736,7 +12746,7 @@
       <c r="D233" s="19"/>
       <c r="E233" s="20"/>
       <c r="F233" s="21"/>
-      <c r="G233" s="101"/>
+      <c r="G233" s="100"/>
       <c r="H233" s="19"/>
       <c r="I233" s="19"/>
       <c r="J233" s="20"/>
@@ -12769,7 +12779,7 @@
       <c r="D234" s="19"/>
       <c r="E234" s="20"/>
       <c r="F234" s="21"/>
-      <c r="G234" s="101"/>
+      <c r="G234" s="100"/>
       <c r="H234" s="19"/>
       <c r="I234" s="19"/>
       <c r="J234" s="20"/>
@@ -12802,7 +12812,7 @@
       <c r="D235" s="19"/>
       <c r="E235" s="20"/>
       <c r="F235" s="21"/>
-      <c r="G235" s="101"/>
+      <c r="G235" s="100"/>
       <c r="H235" s="19"/>
       <c r="I235" s="19"/>
       <c r="J235" s="20"/>
@@ -12835,7 +12845,7 @@
       <c r="D236" s="19"/>
       <c r="E236" s="20"/>
       <c r="F236" s="21"/>
-      <c r="G236" s="101"/>
+      <c r="G236" s="100"/>
       <c r="H236" s="19"/>
       <c r="I236" s="19"/>
       <c r="J236" s="20"/>
@@ -12868,7 +12878,7 @@
       <c r="D237" s="19"/>
       <c r="E237" s="20"/>
       <c r="F237" s="21"/>
-      <c r="G237" s="101"/>
+      <c r="G237" s="100"/>
       <c r="H237" s="19"/>
       <c r="I237" s="19"/>
       <c r="J237" s="20"/>
@@ -12901,7 +12911,7 @@
       <c r="D238" s="19"/>
       <c r="E238" s="20"/>
       <c r="F238" s="21"/>
-      <c r="G238" s="101"/>
+      <c r="G238" s="100"/>
       <c r="H238" s="19"/>
       <c r="I238" s="19"/>
       <c r="J238" s="20"/>
@@ -12934,7 +12944,7 @@
       <c r="D239" s="19"/>
       <c r="E239" s="20"/>
       <c r="F239" s="21"/>
-      <c r="G239" s="101"/>
+      <c r="G239" s="100"/>
       <c r="H239" s="19"/>
       <c r="I239" s="19"/>
       <c r="J239" s="20"/>
@@ -12967,7 +12977,7 @@
       <c r="D240" s="19"/>
       <c r="E240" s="20"/>
       <c r="F240" s="21"/>
-      <c r="G240" s="101"/>
+      <c r="G240" s="100"/>
       <c r="H240" s="19"/>
       <c r="I240" s="19"/>
       <c r="J240" s="20"/>
@@ -13000,7 +13010,7 @@
       <c r="D241" s="19"/>
       <c r="E241" s="20"/>
       <c r="F241" s="21"/>
-      <c r="G241" s="101"/>
+      <c r="G241" s="100"/>
       <c r="H241" s="19"/>
       <c r="I241" s="19"/>
       <c r="J241" s="20"/>
@@ -13033,7 +13043,7 @@
       <c r="D242" s="19"/>
       <c r="E242" s="20"/>
       <c r="F242" s="21"/>
-      <c r="G242" s="101"/>
+      <c r="G242" s="100"/>
       <c r="H242" s="19"/>
       <c r="I242" s="19"/>
       <c r="J242" s="20"/>
@@ -13066,7 +13076,7 @@
       <c r="D243" s="19"/>
       <c r="E243" s="20"/>
       <c r="F243" s="21"/>
-      <c r="G243" s="101"/>
+      <c r="G243" s="100"/>
       <c r="H243" s="19"/>
       <c r="I243" s="19"/>
       <c r="J243" s="20"/>
@@ -13099,7 +13109,7 @@
       <c r="D244" s="19"/>
       <c r="E244" s="20"/>
       <c r="F244" s="21"/>
-      <c r="G244" s="101"/>
+      <c r="G244" s="100"/>
       <c r="H244" s="19"/>
       <c r="I244" s="19"/>
       <c r="J244" s="20"/>
@@ -13132,7 +13142,7 @@
       <c r="D245" s="19"/>
       <c r="E245" s="20"/>
       <c r="F245" s="21"/>
-      <c r="G245" s="101"/>
+      <c r="G245" s="100"/>
       <c r="H245" s="19"/>
       <c r="I245" s="19"/>
       <c r="J245" s="20"/>
@@ -13165,7 +13175,7 @@
       <c r="D246" s="19"/>
       <c r="E246" s="20"/>
       <c r="F246" s="21"/>
-      <c r="G246" s="101"/>
+      <c r="G246" s="100"/>
       <c r="H246" s="19"/>
       <c r="I246" s="19"/>
       <c r="J246" s="20"/>
@@ -13198,7 +13208,7 @@
       <c r="D247" s="19"/>
       <c r="E247" s="20"/>
       <c r="F247" s="21"/>
-      <c r="G247" s="101"/>
+      <c r="G247" s="100"/>
       <c r="H247" s="19"/>
       <c r="I247" s="19"/>
       <c r="J247" s="20"/>
@@ -13231,7 +13241,7 @@
       <c r="D248" s="19"/>
       <c r="E248" s="20"/>
       <c r="F248" s="21"/>
-      <c r="G248" s="101"/>
+      <c r="G248" s="100"/>
       <c r="H248" s="19"/>
       <c r="I248" s="19"/>
       <c r="J248" s="20"/>
@@ -13264,7 +13274,7 @@
       <c r="D249" s="19"/>
       <c r="E249" s="20"/>
       <c r="F249" s="21"/>
-      <c r="G249" s="101"/>
+      <c r="G249" s="100"/>
       <c r="H249" s="19"/>
       <c r="I249" s="19"/>
       <c r="J249" s="20"/>
@@ -13297,7 +13307,7 @@
       <c r="D250" s="19"/>
       <c r="E250" s="20"/>
       <c r="F250" s="21"/>
-      <c r="G250" s="101"/>
+      <c r="G250" s="100"/>
       <c r="H250" s="19"/>
       <c r="I250" s="19"/>
       <c r="J250" s="20"/>
@@ -13330,7 +13340,7 @@
       <c r="D251" s="19"/>
       <c r="E251" s="20"/>
       <c r="F251" s="21"/>
-      <c r="G251" s="101"/>
+      <c r="G251" s="100"/>
       <c r="H251" s="19"/>
       <c r="I251" s="19"/>
       <c r="J251" s="20"/>
@@ -13363,7 +13373,7 @@
       <c r="D252" s="19"/>
       <c r="E252" s="20"/>
       <c r="F252" s="21"/>
-      <c r="G252" s="101"/>
+      <c r="G252" s="100"/>
       <c r="H252" s="19"/>
       <c r="I252" s="19"/>
       <c r="J252" s="20"/>
@@ -13396,7 +13406,7 @@
       <c r="D253" s="19"/>
       <c r="E253" s="20"/>
       <c r="F253" s="21"/>
-      <c r="G253" s="101"/>
+      <c r="G253" s="100"/>
       <c r="H253" s="19"/>
       <c r="I253" s="19"/>
       <c r="J253" s="20"/>
@@ -13429,7 +13439,7 @@
       <c r="D254" s="19"/>
       <c r="E254" s="20"/>
       <c r="F254" s="21"/>
-      <c r="G254" s="101"/>
+      <c r="G254" s="100"/>
       <c r="H254" s="19"/>
       <c r="I254" s="19"/>
       <c r="J254" s="20"/>
@@ -13462,7 +13472,7 @@
       <c r="D255" s="19"/>
       <c r="E255" s="20"/>
       <c r="F255" s="21"/>
-      <c r="G255" s="101"/>
+      <c r="G255" s="100"/>
       <c r="H255" s="19"/>
       <c r="I255" s="19"/>
       <c r="J255" s="20"/>
@@ -13495,7 +13505,7 @@
       <c r="D256" s="19"/>
       <c r="E256" s="20"/>
       <c r="F256" s="21"/>
-      <c r="G256" s="101"/>
+      <c r="G256" s="100"/>
       <c r="H256" s="19"/>
       <c r="I256" s="19"/>
       <c r="J256" s="20"/>
@@ -13528,7 +13538,7 @@
       <c r="D257" s="19"/>
       <c r="E257" s="20"/>
       <c r="F257" s="21"/>
-      <c r="G257" s="101"/>
+      <c r="G257" s="100"/>
       <c r="H257" s="19"/>
       <c r="I257" s="19"/>
       <c r="J257" s="20"/>
@@ -13561,7 +13571,7 @@
       <c r="D258" s="19"/>
       <c r="E258" s="20"/>
       <c r="F258" s="21"/>
-      <c r="G258" s="101"/>
+      <c r="G258" s="100"/>
       <c r="H258" s="19"/>
       <c r="I258" s="19"/>
       <c r="J258" s="20"/>
@@ -13594,7 +13604,7 @@
       <c r="D259" s="19"/>
       <c r="E259" s="20"/>
       <c r="F259" s="21"/>
-      <c r="G259" s="101"/>
+      <c r="G259" s="100"/>
       <c r="H259" s="19"/>
       <c r="I259" s="19"/>
       <c r="J259" s="20"/>
@@ -13627,7 +13637,7 @@
       <c r="D260" s="19"/>
       <c r="E260" s="20"/>
       <c r="F260" s="21"/>
-      <c r="G260" s="101"/>
+      <c r="G260" s="100"/>
       <c r="H260" s="19"/>
       <c r="I260" s="19"/>
       <c r="J260" s="20"/>
@@ -13660,7 +13670,7 @@
       <c r="D261" s="19"/>
       <c r="E261" s="20"/>
       <c r="F261" s="21"/>
-      <c r="G261" s="101"/>
+      <c r="G261" s="100"/>
       <c r="H261" s="19"/>
       <c r="I261" s="19"/>
       <c r="J261" s="20"/>
@@ -13693,7 +13703,7 @@
       <c r="D262" s="19"/>
       <c r="E262" s="20"/>
       <c r="F262" s="21"/>
-      <c r="G262" s="101"/>
+      <c r="G262" s="100"/>
       <c r="H262" s="19"/>
       <c r="I262" s="19"/>
       <c r="J262" s="20"/>
@@ -13726,7 +13736,7 @@
       <c r="D263" s="19"/>
       <c r="E263" s="20"/>
       <c r="F263" s="21"/>
-      <c r="G263" s="101"/>
+      <c r="G263" s="100"/>
       <c r="H263" s="19"/>
       <c r="I263" s="19"/>
       <c r="J263" s="20"/>
@@ -13759,7 +13769,7 @@
       <c r="D264" s="19"/>
       <c r="E264" s="20"/>
       <c r="F264" s="21"/>
-      <c r="G264" s="101"/>
+      <c r="G264" s="100"/>
       <c r="H264" s="19"/>
       <c r="I264" s="19"/>
       <c r="J264" s="20"/>
@@ -13792,7 +13802,7 @@
       <c r="D265" s="19"/>
       <c r="E265" s="20"/>
       <c r="F265" s="21"/>
-      <c r="G265" s="101"/>
+      <c r="G265" s="100"/>
       <c r="H265" s="19"/>
       <c r="I265" s="19"/>
       <c r="J265" s="20"/>
@@ -13825,7 +13835,7 @@
       <c r="D266" s="19"/>
       <c r="E266" s="20"/>
       <c r="F266" s="21"/>
-      <c r="G266" s="101"/>
+      <c r="G266" s="100"/>
       <c r="H266" s="19"/>
       <c r="I266" s="19"/>
       <c r="J266" s="20"/>
@@ -13858,7 +13868,7 @@
       <c r="D267" s="19"/>
       <c r="E267" s="20"/>
       <c r="F267" s="21"/>
-      <c r="G267" s="101"/>
+      <c r="G267" s="100"/>
       <c r="H267" s="19"/>
       <c r="I267" s="19"/>
       <c r="J267" s="20"/>
@@ -13891,7 +13901,7 @@
       <c r="D268" s="19"/>
       <c r="E268" s="20"/>
       <c r="F268" s="21"/>
-      <c r="G268" s="101"/>
+      <c r="G268" s="100"/>
       <c r="H268" s="19"/>
       <c r="I268" s="19"/>
       <c r="J268" s="20"/>
@@ -13924,7 +13934,7 @@
       <c r="D269" s="19"/>
       <c r="E269" s="20"/>
       <c r="F269" s="21"/>
-      <c r="G269" s="101"/>
+      <c r="G269" s="100"/>
       <c r="H269" s="19"/>
       <c r="I269" s="19"/>
       <c r="J269" s="20"/>
@@ -13957,7 +13967,7 @@
       <c r="D270" s="19"/>
       <c r="E270" s="20"/>
       <c r="F270" s="21"/>
-      <c r="G270" s="101"/>
+      <c r="G270" s="100"/>
       <c r="H270" s="19"/>
       <c r="I270" s="19"/>
       <c r="J270" s="20"/>
@@ -13990,7 +14000,7 @@
       <c r="D271" s="19"/>
       <c r="E271" s="20"/>
       <c r="F271" s="21"/>
-      <c r="G271" s="101"/>
+      <c r="G271" s="100"/>
       <c r="H271" s="19"/>
       <c r="I271" s="19"/>
       <c r="J271" s="20"/>
@@ -14023,7 +14033,7 @@
       <c r="D272" s="19"/>
       <c r="E272" s="20"/>
       <c r="F272" s="21"/>
-      <c r="G272" s="101"/>
+      <c r="G272" s="100"/>
       <c r="H272" s="19"/>
       <c r="I272" s="19"/>
       <c r="J272" s="20"/>
@@ -14056,7 +14066,7 @@
       <c r="D273" s="19"/>
       <c r="E273" s="20"/>
       <c r="F273" s="21"/>
-      <c r="G273" s="101"/>
+      <c r="G273" s="100"/>
       <c r="H273" s="19"/>
       <c r="I273" s="19"/>
       <c r="J273" s="20"/>
@@ -14089,7 +14099,7 @@
       <c r="D274" s="19"/>
       <c r="E274" s="20"/>
       <c r="F274" s="21"/>
-      <c r="G274" s="101"/>
+      <c r="G274" s="100"/>
       <c r="H274" s="19"/>
       <c r="I274" s="19"/>
       <c r="J274" s="20"/>
@@ -14122,7 +14132,7 @@
       <c r="D275" s="19"/>
       <c r="E275" s="20"/>
       <c r="F275" s="21"/>
-      <c r="G275" s="101"/>
+      <c r="G275" s="100"/>
       <c r="H275" s="19"/>
       <c r="I275" s="19"/>
       <c r="J275" s="20"/>
@@ -14155,7 +14165,7 @@
       <c r="D276" s="19"/>
       <c r="E276" s="20"/>
       <c r="F276" s="21"/>
-      <c r="G276" s="101"/>
+      <c r="G276" s="100"/>
       <c r="H276" s="19"/>
       <c r="I276" s="19"/>
       <c r="J276" s="20"/>
@@ -14188,7 +14198,7 @@
       <c r="D277" s="19"/>
       <c r="E277" s="20"/>
       <c r="F277" s="21"/>
-      <c r="G277" s="101"/>
+      <c r="G277" s="100"/>
       <c r="H277" s="19"/>
       <c r="I277" s="19"/>
       <c r="J277" s="20"/>
@@ -14221,7 +14231,7 @@
       <c r="D278" s="19"/>
       <c r="E278" s="20"/>
       <c r="F278" s="21"/>
-      <c r="G278" s="101"/>
+      <c r="G278" s="100"/>
       <c r="H278" s="19"/>
       <c r="I278" s="19"/>
       <c r="J278" s="20"/>
@@ -14254,7 +14264,7 @@
       <c r="D279" s="19"/>
       <c r="E279" s="20"/>
       <c r="F279" s="21"/>
-      <c r="G279" s="101"/>
+      <c r="G279" s="100"/>
       <c r="H279" s="19"/>
       <c r="I279" s="19"/>
       <c r="J279" s="20"/>
@@ -14287,7 +14297,7 @@
       <c r="D280" s="19"/>
       <c r="E280" s="20"/>
       <c r="F280" s="21"/>
-      <c r="G280" s="101"/>
+      <c r="G280" s="100"/>
       <c r="H280" s="19"/>
       <c r="I280" s="19"/>
       <c r="J280" s="20"/>
@@ -14320,7 +14330,7 @@
       <c r="D281" s="19"/>
       <c r="E281" s="20"/>
       <c r="F281" s="21"/>
-      <c r="G281" s="101"/>
+      <c r="G281" s="100"/>
       <c r="H281" s="19"/>
       <c r="I281" s="19"/>
       <c r="J281" s="20"/>
@@ -14353,7 +14363,7 @@
       <c r="D282" s="19"/>
       <c r="E282" s="20"/>
       <c r="F282" s="21"/>
-      <c r="G282" s="101"/>
+      <c r="G282" s="100"/>
       <c r="H282" s="19"/>
       <c r="I282" s="19"/>
       <c r="J282" s="20"/>
@@ -14386,7 +14396,7 @@
       <c r="D283" s="19"/>
       <c r="E283" s="20"/>
       <c r="F283" s="21"/>
-      <c r="G283" s="101"/>
+      <c r="G283" s="100"/>
       <c r="H283" s="19"/>
       <c r="I283" s="19"/>
       <c r="J283" s="20"/>
@@ -14419,7 +14429,7 @@
       <c r="D284" s="19"/>
       <c r="E284" s="20"/>
       <c r="F284" s="21"/>
-      <c r="G284" s="101"/>
+      <c r="G284" s="100"/>
       <c r="H284" s="19"/>
       <c r="I284" s="19"/>
       <c r="J284" s="20"/>
@@ -14452,7 +14462,7 @@
       <c r="D285" s="19"/>
       <c r="E285" s="20"/>
       <c r="F285" s="21"/>
-      <c r="G285" s="101"/>
+      <c r="G285" s="100"/>
       <c r="H285" s="19"/>
       <c r="I285" s="19"/>
       <c r="J285" s="20"/>
@@ -14485,7 +14495,7 @@
       <c r="D286" s="19"/>
       <c r="E286" s="20"/>
       <c r="F286" s="21"/>
-      <c r="G286" s="101"/>
+      <c r="G286" s="100"/>
       <c r="H286" s="19"/>
       <c r="I286" s="19"/>
       <c r="J286" s="20"/>
@@ -14518,7 +14528,7 @@
       <c r="D287" s="19"/>
       <c r="E287" s="20"/>
       <c r="F287" s="21"/>
-      <c r="G287" s="101"/>
+      <c r="G287" s="100"/>
       <c r="H287" s="19"/>
       <c r="I287" s="19"/>
       <c r="J287" s="20"/>
@@ -14551,7 +14561,7 @@
       <c r="D288" s="19"/>
       <c r="E288" s="20"/>
       <c r="F288" s="21"/>
-      <c r="G288" s="101"/>
+      <c r="G288" s="100"/>
       <c r="H288" s="19"/>
       <c r="I288" s="19"/>
       <c r="J288" s="20"/>
@@ -14584,7 +14594,7 @@
       <c r="D289" s="19"/>
       <c r="E289" s="20"/>
       <c r="F289" s="21"/>
-      <c r="G289" s="101"/>
+      <c r="G289" s="100"/>
       <c r="H289" s="19"/>
       <c r="I289" s="19"/>
       <c r="J289" s="20"/>
@@ -14617,7 +14627,7 @@
       <c r="D290" s="19"/>
       <c r="E290" s="20"/>
       <c r="F290" s="21"/>
-      <c r="G290" s="101"/>
+      <c r="G290" s="100"/>
       <c r="H290" s="19"/>
       <c r="I290" s="19"/>
       <c r="J290" s="20"/>
@@ -14650,7 +14660,7 @@
       <c r="D291" s="19"/>
       <c r="E291" s="20"/>
       <c r="F291" s="21"/>
-      <c r="G291" s="101"/>
+      <c r="G291" s="100"/>
       <c r="H291" s="19"/>
       <c r="I291" s="19"/>
       <c r="J291" s="20"/>
@@ -14683,7 +14693,7 @@
       <c r="D292" s="19"/>
       <c r="E292" s="20"/>
       <c r="F292" s="21"/>
-      <c r="G292" s="101"/>
+      <c r="G292" s="100"/>
       <c r="H292" s="19"/>
       <c r="I292" s="19"/>
       <c r="J292" s="20"/>
@@ -14716,7 +14726,7 @@
       <c r="D293" s="19"/>
       <c r="E293" s="20"/>
       <c r="F293" s="21"/>
-      <c r="G293" s="101"/>
+      <c r="G293" s="100"/>
       <c r="H293" s="19"/>
       <c r="I293" s="19"/>
       <c r="J293" s="20"/>
@@ -14749,7 +14759,7 @@
       <c r="D294" s="19"/>
       <c r="E294" s="20"/>
       <c r="F294" s="21"/>
-      <c r="G294" s="101"/>
+      <c r="G294" s="100"/>
       <c r="H294" s="19"/>
       <c r="I294" s="19"/>
       <c r="J294" s="20"/>
@@ -14782,7 +14792,7 @@
       <c r="D295" s="19"/>
       <c r="E295" s="20"/>
       <c r="F295" s="21"/>
-      <c r="G295" s="101"/>
+      <c r="G295" s="100"/>
       <c r="H295" s="19"/>
       <c r="I295" s="19"/>
       <c r="J295" s="20"/>
@@ -14815,7 +14825,7 @@
       <c r="D296" s="19"/>
       <c r="E296" s="20"/>
       <c r="F296" s="21"/>
-      <c r="G296" s="101"/>
+      <c r="G296" s="100"/>
       <c r="H296" s="19"/>
       <c r="I296" s="19"/>
       <c r="J296" s="20"/>
@@ -14848,7 +14858,7 @@
       <c r="D297" s="19"/>
       <c r="E297" s="20"/>
       <c r="F297" s="21"/>
-      <c r="G297" s="101"/>
+      <c r="G297" s="100"/>
       <c r="H297" s="19"/>
       <c r="I297" s="19"/>
       <c r="J297" s="20"/>
@@ -14881,7 +14891,7 @@
       <c r="D298" s="19"/>
       <c r="E298" s="20"/>
       <c r="F298" s="21"/>
-      <c r="G298" s="101"/>
+      <c r="G298" s="100"/>
       <c r="H298" s="19"/>
       <c r="I298" s="19"/>
       <c r="J298" s="20"/>
@@ -14914,7 +14924,7 @@
       <c r="D299" s="19"/>
       <c r="E299" s="20"/>
       <c r="F299" s="21"/>
-      <c r="G299" s="101"/>
+      <c r="G299" s="100"/>
       <c r="H299" s="19"/>
       <c r="I299" s="19"/>
       <c r="J299" s="20"/>
@@ -14947,7 +14957,7 @@
       <c r="D300" s="19"/>
       <c r="E300" s="20"/>
       <c r="F300" s="21"/>
-      <c r="G300" s="101"/>
+      <c r="G300" s="100"/>
       <c r="H300" s="19"/>
       <c r="I300" s="19"/>
       <c r="J300" s="20"/>
@@ -14980,7 +14990,7 @@
       <c r="D301" s="19"/>
       <c r="E301" s="20"/>
       <c r="F301" s="21"/>
-      <c r="G301" s="101"/>
+      <c r="G301" s="100"/>
       <c r="H301" s="19"/>
       <c r="I301" s="19"/>
       <c r="J301" s="20"/>
@@ -15013,7 +15023,7 @@
       <c r="D302" s="19"/>
       <c r="E302" s="20"/>
       <c r="F302" s="21"/>
-      <c r="G302" s="101"/>
+      <c r="G302" s="100"/>
       <c r="H302" s="19"/>
       <c r="I302" s="19"/>
       <c r="J302" s="20"/>
@@ -15046,7 +15056,7 @@
       <c r="D303" s="19"/>
       <c r="E303" s="20"/>
       <c r="F303" s="21"/>
-      <c r="G303" s="101"/>
+      <c r="G303" s="100"/>
       <c r="H303" s="19"/>
       <c r="I303" s="19"/>
       <c r="J303" s="20"/>
@@ -15079,7 +15089,7 @@
       <c r="D304" s="19"/>
       <c r="E304" s="20"/>
       <c r="F304" s="21"/>
-      <c r="G304" s="101"/>
+      <c r="G304" s="100"/>
       <c r="H304" s="19"/>
       <c r="I304" s="19"/>
       <c r="J304" s="20"/>
@@ -15112,7 +15122,7 @@
       <c r="D305" s="19"/>
       <c r="E305" s="20"/>
       <c r="F305" s="21"/>
-      <c r="G305" s="101"/>
+      <c r="G305" s="100"/>
       <c r="H305" s="19"/>
       <c r="I305" s="19"/>
       <c r="J305" s="20"/>
@@ -15145,7 +15155,7 @@
       <c r="D306" s="19"/>
       <c r="E306" s="20"/>
       <c r="F306" s="21"/>
-      <c r="G306" s="101"/>
+      <c r="G306" s="100"/>
       <c r="H306" s="19"/>
       <c r="I306" s="19"/>
       <c r="J306" s="20"/>
@@ -15178,7 +15188,7 @@
       <c r="D307" s="19"/>
       <c r="E307" s="20"/>
       <c r="F307" s="21"/>
-      <c r="G307" s="101"/>
+      <c r="G307" s="100"/>
       <c r="H307" s="19"/>
       <c r="I307" s="19"/>
       <c r="J307" s="20"/>
@@ -15211,7 +15221,7 @@
       <c r="D308" s="19"/>
       <c r="E308" s="20"/>
       <c r="F308" s="21"/>
-      <c r="G308" s="101"/>
+      <c r="G308" s="100"/>
       <c r="H308" s="19"/>
       <c r="I308" s="19"/>
       <c r="J308" s="20"/>
@@ -15244,7 +15254,7 @@
       <c r="D309" s="19"/>
       <c r="E309" s="20"/>
       <c r="F309" s="21"/>
-      <c r="G309" s="101"/>
+      <c r="G309" s="100"/>
       <c r="H309" s="19"/>
       <c r="I309" s="19"/>
       <c r="J309" s="20"/>
@@ -15277,7 +15287,7 @@
       <c r="D310" s="19"/>
       <c r="E310" s="20"/>
       <c r="F310" s="21"/>
-      <c r="G310" s="101"/>
+      <c r="G310" s="100"/>
       <c r="H310" s="19"/>
       <c r="I310" s="19"/>
       <c r="J310" s="20"/>
@@ -15310,7 +15320,7 @@
       <c r="D311" s="19"/>
       <c r="E311" s="20"/>
       <c r="F311" s="21"/>
-      <c r="G311" s="101"/>
+      <c r="G311" s="100"/>
       <c r="H311" s="19"/>
       <c r="I311" s="19"/>
       <c r="J311" s="20"/>
@@ -15343,7 +15353,7 @@
       <c r="D312" s="19"/>
       <c r="E312" s="20"/>
       <c r="F312" s="21"/>
-      <c r="G312" s="101"/>
+      <c r="G312" s="100"/>
       <c r="H312" s="19"/>
       <c r="I312" s="19"/>
       <c r="J312" s="20"/>
@@ -15376,7 +15386,7 @@
       <c r="D313" s="19"/>
       <c r="E313" s="20"/>
       <c r="F313" s="21"/>
-      <c r="G313" s="101"/>
+      <c r="G313" s="100"/>
       <c r="H313" s="19"/>
       <c r="I313" s="19"/>
       <c r="J313" s="20"/>
@@ -15409,7 +15419,7 @@
       <c r="D314" s="19"/>
       <c r="E314" s="20"/>
       <c r="F314" s="21"/>
-      <c r="G314" s="101"/>
+      <c r="G314" s="100"/>
       <c r="H314" s="19"/>
       <c r="I314" s="19"/>
       <c r="J314" s="20"/>
@@ -15442,7 +15452,7 @@
       <c r="D315" s="19"/>
       <c r="E315" s="20"/>
       <c r="F315" s="21"/>
-      <c r="G315" s="101"/>
+      <c r="G315" s="100"/>
       <c r="H315" s="19"/>
       <c r="I315" s="19"/>
       <c r="J315" s="20"/>
@@ -15475,7 +15485,7 @@
       <c r="D316" s="19"/>
       <c r="E316" s="20"/>
       <c r="F316" s="21"/>
-      <c r="G316" s="101"/>
+      <c r="G316" s="100"/>
       <c r="H316" s="19"/>
       <c r="I316" s="19"/>
       <c r="J316" s="20"/>
@@ -15508,7 +15518,7 @@
       <c r="D317" s="19"/>
       <c r="E317" s="20"/>
       <c r="F317" s="21"/>
-      <c r="G317" s="101"/>
+      <c r="G317" s="100"/>
       <c r="H317" s="19"/>
       <c r="I317" s="19"/>
       <c r="J317" s="20"/>
@@ -15541,7 +15551,7 @@
       <c r="D318" s="19"/>
       <c r="E318" s="20"/>
       <c r="F318" s="21"/>
-      <c r="G318" s="101"/>
+      <c r="G318" s="100"/>
       <c r="H318" s="19"/>
       <c r="I318" s="19"/>
       <c r="J318" s="20"/>
@@ -15574,7 +15584,7 @@
       <c r="D319" s="19"/>
       <c r="E319" s="20"/>
       <c r="F319" s="21"/>
-      <c r="G319" s="101"/>
+      <c r="G319" s="100"/>
       <c r="H319" s="19"/>
       <c r="I319" s="19"/>
       <c r="J319" s="20"/>
@@ -15607,7 +15617,7 @@
       <c r="D320" s="19"/>
       <c r="E320" s="20"/>
       <c r="F320" s="21"/>
-      <c r="G320" s="101"/>
+      <c r="G320" s="100"/>
       <c r="H320" s="19"/>
       <c r="I320" s="19"/>
       <c r="J320" s="20"/>
@@ -15640,7 +15650,7 @@
       <c r="D321" s="19"/>
       <c r="E321" s="20"/>
       <c r="F321" s="21"/>
-      <c r="G321" s="101"/>
+      <c r="G321" s="100"/>
       <c r="H321" s="19"/>
       <c r="I321" s="19"/>
       <c r="J321" s="20"/>
@@ -15673,7 +15683,7 @@
       <c r="D322" s="19"/>
       <c r="E322" s="20"/>
       <c r="F322" s="21"/>
-      <c r="G322" s="101"/>
+      <c r="G322" s="100"/>
       <c r="H322" s="19"/>
       <c r="I322" s="19"/>
       <c r="J322" s="20"/>
@@ -15706,7 +15716,7 @@
       <c r="D323" s="19"/>
       <c r="E323" s="20"/>
       <c r="F323" s="21"/>
-      <c r="G323" s="101"/>
+      <c r="G323" s="100"/>
       <c r="H323" s="19"/>
       <c r="I323" s="19"/>
       <c r="J323" s="20"/>
@@ -15739,7 +15749,7 @@
       <c r="D324" s="19"/>
       <c r="E324" s="20"/>
       <c r="F324" s="21"/>
-      <c r="G324" s="101"/>
+      <c r="G324" s="100"/>
       <c r="H324" s="19"/>
       <c r="I324" s="19"/>
       <c r="J324" s="20"/>
@@ -15772,7 +15782,7 @@
       <c r="D325" s="19"/>
       <c r="E325" s="20"/>
       <c r="F325" s="21"/>
-      <c r="G325" s="101"/>
+      <c r="G325" s="100"/>
       <c r="H325" s="19"/>
       <c r="I325" s="19"/>
       <c r="J325" s="20"/>
@@ -15805,7 +15815,7 @@
       <c r="D326" s="19"/>
       <c r="E326" s="20"/>
       <c r="F326" s="21"/>
-      <c r="G326" s="101"/>
+      <c r="G326" s="100"/>
       <c r="H326" s="19"/>
       <c r="I326" s="19"/>
       <c r="J326" s="20"/>
@@ -15838,7 +15848,7 @@
       <c r="D327" s="19"/>
       <c r="E327" s="20"/>
       <c r="F327" s="21"/>
-      <c r="G327" s="101"/>
+      <c r="G327" s="100"/>
       <c r="H327" s="19"/>
       <c r="I327" s="19"/>
       <c r="J327" s="20"/>
@@ -15871,7 +15881,7 @@
       <c r="D328" s="19"/>
       <c r="E328" s="20"/>
       <c r="F328" s="21"/>
-      <c r="G328" s="101"/>
+      <c r="G328" s="100"/>
       <c r="H328" s="19"/>
       <c r="I328" s="19"/>
       <c r="J328" s="20"/>
@@ -15904,7 +15914,7 @@
       <c r="D329" s="19"/>
       <c r="E329" s="20"/>
       <c r="F329" s="21"/>
-      <c r="G329" s="101"/>
+      <c r="G329" s="100"/>
       <c r="H329" s="19"/>
       <c r="I329" s="19"/>
       <c r="J329" s="20"/>
@@ -15937,7 +15947,7 @@
       <c r="D330" s="19"/>
       <c r="E330" s="20"/>
       <c r="F330" s="21"/>
-      <c r="G330" s="101"/>
+      <c r="G330" s="100"/>
       <c r="H330" s="19"/>
       <c r="I330" s="19"/>
       <c r="J330" s="20"/>
@@ -15970,7 +15980,7 @@
       <c r="D331" s="19"/>
       <c r="E331" s="20"/>
       <c r="F331" s="21"/>
-      <c r="G331" s="101"/>
+      <c r="G331" s="100"/>
       <c r="H331" s="19"/>
       <c r="I331" s="19"/>
       <c r="J331" s="20"/>
@@ -16003,7 +16013,7 @@
       <c r="D332" s="19"/>
       <c r="E332" s="20"/>
       <c r="F332" s="21"/>
-      <c r="G332" s="101"/>
+      <c r="G332" s="100"/>
       <c r="H332" s="19"/>
       <c r="I332" s="19"/>
       <c r="J332" s="20"/>
@@ -16036,7 +16046,7 @@
       <c r="D333" s="19"/>
       <c r="E333" s="20"/>
       <c r="F333" s="21"/>
-      <c r="G333" s="101"/>
+      <c r="G333" s="100"/>
       <c r="H333" s="19"/>
       <c r="I333" s="19"/>
       <c r="J333" s="20"/>
@@ -16069,7 +16079,7 @@
       <c r="D334" s="19"/>
       <c r="E334" s="20"/>
       <c r="F334" s="21"/>
-      <c r="G334" s="101"/>
+      <c r="G334" s="100"/>
       <c r="H334" s="19"/>
       <c r="I334" s="19"/>
       <c r="J334" s="20"/>
@@ -16102,7 +16112,7 @@
       <c r="D335" s="19"/>
       <c r="E335" s="20"/>
       <c r="F335" s="21"/>
-      <c r="G335" s="101"/>
+      <c r="G335" s="100"/>
       <c r="H335" s="19"/>
       <c r="I335" s="19"/>
       <c r="J335" s="20"/>
@@ -16135,7 +16145,7 @@
       <c r="D336" s="19"/>
       <c r="E336" s="20"/>
       <c r="F336" s="21"/>
-      <c r="G336" s="101"/>
+      <c r="G336" s="100"/>
       <c r="H336" s="19"/>
       <c r="I336" s="19"/>
       <c r="J336" s="20"/>
@@ -16168,7 +16178,7 @@
       <c r="D337" s="19"/>
       <c r="E337" s="20"/>
       <c r="F337" s="21"/>
-      <c r="G337" s="101"/>
+      <c r="G337" s="100"/>
       <c r="H337" s="19"/>
       <c r="I337" s="19"/>
       <c r="J337" s="20"/>
@@ -16201,7 +16211,7 @@
       <c r="D338" s="19"/>
       <c r="E338" s="20"/>
       <c r="F338" s="21"/>
-      <c r="G338" s="101"/>
+      <c r="G338" s="100"/>
       <c r="H338" s="19"/>
       <c r="I338" s="19"/>
       <c r="J338" s="20"/>
@@ -16234,7 +16244,7 @@
       <c r="D339" s="19"/>
       <c r="E339" s="20"/>
       <c r="F339" s="21"/>
-      <c r="G339" s="101"/>
+      <c r="G339" s="100"/>
       <c r="H339" s="19"/>
       <c r="I339" s="19"/>
       <c r="J339" s="20"/>
@@ -16267,7 +16277,7 @@
       <c r="D340" s="19"/>
       <c r="E340" s="20"/>
       <c r="F340" s="21"/>
-      <c r="G340" s="101"/>
+      <c r="G340" s="100"/>
       <c r="H340" s="19"/>
       <c r="I340" s="19"/>
       <c r="J340" s="20"/>
@@ -16300,7 +16310,7 @@
       <c r="D341" s="19"/>
       <c r="E341" s="20"/>
       <c r="F341" s="21"/>
-      <c r="G341" s="101"/>
+      <c r="G341" s="100"/>
       <c r="H341" s="19"/>
       <c r="I341" s="19"/>
       <c r="J341" s="20"/>
@@ -16333,7 +16343,7 @@
       <c r="D342" s="19"/>
       <c r="E342" s="20"/>
       <c r="F342" s="21"/>
-      <c r="G342" s="101"/>
+      <c r="G342" s="100"/>
       <c r="H342" s="19"/>
       <c r="I342" s="19"/>
       <c r="J342" s="20"/>
@@ -16366,7 +16376,7 @@
       <c r="D343" s="19"/>
       <c r="E343" s="20"/>
       <c r="F343" s="21"/>
-      <c r="G343" s="101"/>
+      <c r="G343" s="100"/>
       <c r="H343" s="19"/>
       <c r="I343" s="19"/>
       <c r="J343" s="20"/>
@@ -16399,7 +16409,7 @@
       <c r="D344" s="19"/>
       <c r="E344" s="20"/>
       <c r="F344" s="21"/>
-      <c r="G344" s="101"/>
+      <c r="G344" s="100"/>
       <c r="H344" s="19"/>
       <c r="I344" s="19"/>
       <c r="J344" s="20"/>
@@ -16432,7 +16442,7 @@
       <c r="D345" s="19"/>
       <c r="E345" s="20"/>
       <c r="F345" s="21"/>
-      <c r="G345" s="101"/>
+      <c r="G345" s="100"/>
       <c r="H345" s="19"/>
       <c r="I345" s="19"/>
       <c r="J345" s="20"/>
@@ -16465,7 +16475,7 @@
       <c r="D346" s="19"/>
       <c r="E346" s="20"/>
       <c r="F346" s="21"/>
-      <c r="G346" s="101"/>
+      <c r="G346" s="100"/>
       <c r="H346" s="19"/>
       <c r="I346" s="19"/>
       <c r="J346" s="20"/>
@@ -16498,7 +16508,7 @@
       <c r="D347" s="19"/>
       <c r="E347" s="20"/>
       <c r="F347" s="21"/>
-      <c r="G347" s="101"/>
+      <c r="G347" s="100"/>
       <c r="H347" s="19"/>
       <c r="I347" s="19"/>
       <c r="J347" s="20"/>
@@ -16531,7 +16541,7 @@
       <c r="D348" s="19"/>
       <c r="E348" s="20"/>
       <c r="F348" s="21"/>
-      <c r="G348" s="101"/>
+      <c r="G348" s="100"/>
       <c r="H348" s="19"/>
       <c r="I348" s="19"/>
       <c r="J348" s="20"/>
@@ -16564,7 +16574,7 @@
       <c r="D349" s="19"/>
       <c r="E349" s="20"/>
       <c r="F349" s="21"/>
-      <c r="G349" s="101"/>
+      <c r="G349" s="100"/>
       <c r="H349" s="19"/>
       <c r="I349" s="19"/>
       <c r="J349" s="20"/>
@@ -16597,7 +16607,7 @@
       <c r="D350" s="19"/>
       <c r="E350" s="20"/>
       <c r="F350" s="21"/>
-      <c r="G350" s="101"/>
+      <c r="G350" s="100"/>
       <c r="H350" s="19"/>
       <c r="I350" s="19"/>
       <c r="J350" s="20"/>
@@ -16630,7 +16640,7 @@
       <c r="D351" s="19"/>
       <c r="E351" s="20"/>
       <c r="F351" s="21"/>
-      <c r="G351" s="101"/>
+      <c r="G351" s="100"/>
       <c r="H351" s="19"/>
       <c r="I351" s="19"/>
       <c r="J351" s="20"/>
@@ -16663,7 +16673,7 @@
       <c r="D352" s="19"/>
       <c r="E352" s="20"/>
       <c r="F352" s="21"/>
-      <c r="G352" s="101"/>
+      <c r="G352" s="100"/>
       <c r="H352" s="19"/>
       <c r="I352" s="19"/>
       <c r="J352" s="20"/>
@@ -16696,7 +16706,7 @@
       <c r="D353" s="19"/>
       <c r="E353" s="20"/>
       <c r="F353" s="21"/>
-      <c r="G353" s="101"/>
+      <c r="G353" s="100"/>
       <c r="H353" s="19"/>
       <c r="I353" s="19"/>
       <c r="J353" s="20"/>
@@ -16729,7 +16739,7 @@
       <c r="D354" s="19"/>
       <c r="E354" s="20"/>
       <c r="F354" s="21"/>
-      <c r="G354" s="101"/>
+      <c r="G354" s="100"/>
       <c r="H354" s="19"/>
       <c r="I354" s="19"/>
       <c r="J354" s="20"/>
@@ -16762,7 +16772,7 @@
       <c r="D355" s="19"/>
       <c r="E355" s="20"/>
       <c r="F355" s="21"/>
-      <c r="G355" s="101"/>
+      <c r="G355" s="100"/>
       <c r="H355" s="19"/>
       <c r="I355" s="19"/>
       <c r="J355" s="20"/>
@@ -16795,7 +16805,7 @@
       <c r="D356" s="19"/>
       <c r="E356" s="20"/>
       <c r="F356" s="21"/>
-      <c r="G356" s="101"/>
+      <c r="G356" s="100"/>
       <c r="H356" s="19"/>
       <c r="I356" s="19"/>
       <c r="J356" s="20"/>
@@ -16828,7 +16838,7 @@
       <c r="D357" s="19"/>
       <c r="E357" s="20"/>
       <c r="F357" s="21"/>
-      <c r="G357" s="101"/>
+      <c r="G357" s="100"/>
       <c r="H357" s="19"/>
       <c r="I357" s="19"/>
       <c r="J357" s="20"/>
@@ -16861,7 +16871,7 @@
       <c r="D358" s="19"/>
       <c r="E358" s="20"/>
       <c r="F358" s="21"/>
-      <c r="G358" s="101"/>
+      <c r="G358" s="100"/>
       <c r="H358" s="19"/>
       <c r="I358" s="19"/>
       <c r="J358" s="20"/>
@@ -16894,7 +16904,7 @@
       <c r="D359" s="19"/>
       <c r="E359" s="20"/>
       <c r="F359" s="21"/>
-      <c r="G359" s="101"/>
+      <c r="G359" s="100"/>
       <c r="H359" s="19"/>
       <c r="I359" s="19"/>
       <c r="J359" s="20"/>
@@ -16927,7 +16937,7 @@
       <c r="D360" s="19"/>
       <c r="E360" s="20"/>
       <c r="F360" s="21"/>
-      <c r="G360" s="101"/>
+      <c r="G360" s="100"/>
       <c r="H360" s="19"/>
       <c r="I360" s="19"/>
       <c r="J360" s="20"/>
@@ -16960,7 +16970,7 @@
       <c r="D361" s="19"/>
       <c r="E361" s="20"/>
       <c r="F361" s="21"/>
-      <c r="G361" s="101"/>
+      <c r="G361" s="100"/>
       <c r="H361" s="19"/>
       <c r="I361" s="19"/>
       <c r="J361" s="20"/>
@@ -16993,7 +17003,7 @@
       <c r="D362" s="19"/>
       <c r="E362" s="20"/>
       <c r="F362" s="21"/>
-      <c r="G362" s="101"/>
+      <c r="G362" s="100"/>
       <c r="H362" s="19"/>
       <c r="I362" s="19"/>
       <c r="J362" s="20"/>
@@ -17026,7 +17036,7 @@
       <c r="D363" s="19"/>
       <c r="E363" s="20"/>
       <c r="F363" s="21"/>
-      <c r="G363" s="101"/>
+      <c r="G363" s="100"/>
       <c r="H363" s="19"/>
       <c r="I363" s="19"/>
       <c r="J363" s="20"/>
@@ -17059,7 +17069,7 @@
       <c r="D364" s="19"/>
       <c r="E364" s="20"/>
       <c r="F364" s="21"/>
-      <c r="G364" s="101"/>
+      <c r="G364" s="100"/>
       <c r="H364" s="19"/>
       <c r="I364" s="19"/>
       <c r="J364" s="20"/>
@@ -17092,7 +17102,7 @@
       <c r="D365" s="19"/>
       <c r="E365" s="20"/>
       <c r="F365" s="21"/>
-      <c r="G365" s="101"/>
+      <c r="G365" s="100"/>
       <c r="H365" s="19"/>
       <c r="I365" s="19"/>
       <c r="J365" s="20"/>
@@ -17125,7 +17135,7 @@
       <c r="D366" s="19"/>
       <c r="E366" s="20"/>
       <c r="F366" s="21"/>
-      <c r="G366" s="101"/>
+      <c r="G366" s="100"/>
       <c r="H366" s="19"/>
       <c r="I366" s="19"/>
       <c r="J366" s="20"/>
@@ -17158,7 +17168,7 @@
       <c r="D367" s="19"/>
       <c r="E367" s="20"/>
       <c r="F367" s="21"/>
-      <c r="G367" s="101"/>
+      <c r="G367" s="100"/>
       <c r="H367" s="19"/>
       <c r="I367" s="19"/>
       <c r="J367" s="20"/>
@@ -17191,7 +17201,7 @@
       <c r="D368" s="19"/>
       <c r="E368" s="20"/>
       <c r="F368" s="21"/>
-      <c r="G368" s="101"/>
+      <c r="G368" s="100"/>
       <c r="H368" s="19"/>
       <c r="I368" s="19"/>
       <c r="J368" s="20"/>
@@ -17224,7 +17234,7 @@
       <c r="D369" s="19"/>
       <c r="E369" s="20"/>
       <c r="F369" s="21"/>
-      <c r="G369" s="101"/>
+      <c r="G369" s="100"/>
       <c r="H369" s="19"/>
       <c r="I369" s="19"/>
       <c r="J369" s="20"/>
@@ -17257,7 +17267,7 @@
       <c r="D370" s="19"/>
       <c r="E370" s="20"/>
       <c r="F370" s="21"/>
-      <c r="G370" s="101"/>
+      <c r="G370" s="100"/>
       <c r="H370" s="19"/>
       <c r="I370" s="19"/>
       <c r="J370" s="20"/>
@@ -17290,7 +17300,7 @@
       <c r="D371" s="19"/>
       <c r="E371" s="20"/>
       <c r="F371" s="21"/>
-      <c r="G371" s="101"/>
+      <c r="G371" s="100"/>
       <c r="H371" s="19"/>
       <c r="I371" s="19"/>
       <c r="J371" s="20"/>
@@ -17323,7 +17333,7 @@
       <c r="D372" s="19"/>
       <c r="E372" s="20"/>
       <c r="F372" s="21"/>
-      <c r="G372" s="101"/>
+      <c r="G372" s="100"/>
       <c r="H372" s="19"/>
       <c r="I372" s="19"/>
       <c r="J372" s="20"/>
@@ -17356,7 +17366,7 @@
       <c r="D373" s="19"/>
       <c r="E373" s="20"/>
       <c r="F373" s="21"/>
-      <c r="G373" s="101"/>
+      <c r="G373" s="100"/>
       <c r="H373" s="19"/>
       <c r="I373" s="19"/>
       <c r="J373" s="20"/>
@@ -17389,7 +17399,7 @@
       <c r="D374" s="19"/>
       <c r="E374" s="20"/>
       <c r="F374" s="21"/>
-      <c r="G374" s="101"/>
+      <c r="G374" s="100"/>
       <c r="H374" s="19"/>
       <c r="I374" s="19"/>
       <c r="J374" s="20"/>
@@ -17422,7 +17432,7 @@
       <c r="D375" s="19"/>
       <c r="E375" s="20"/>
       <c r="F375" s="21"/>
-      <c r="G375" s="101"/>
+      <c r="G375" s="100"/>
       <c r="H375" s="19"/>
       <c r="I375" s="19"/>
       <c r="J375" s="20"/>
@@ -17455,7 +17465,7 @@
       <c r="D376" s="19"/>
       <c r="E376" s="20"/>
       <c r="F376" s="21"/>
-      <c r="G376" s="101"/>
+      <c r="G376" s="100"/>
       <c r="H376" s="19"/>
       <c r="I376" s="19"/>
       <c r="J376" s="20"/>
@@ -17488,7 +17498,7 @@
       <c r="D377" s="19"/>
       <c r="E377" s="20"/>
       <c r="F377" s="21"/>
-      <c r="G377" s="101"/>
+      <c r="G377" s="100"/>
       <c r="H377" s="19"/>
       <c r="I377" s="19"/>
       <c r="J377" s="20"/>
@@ -17521,7 +17531,7 @@
       <c r="D378" s="19"/>
       <c r="E378" s="20"/>
       <c r="F378" s="21"/>
-      <c r="G378" s="101"/>
+      <c r="G378" s="100"/>
       <c r="H378" s="19"/>
       <c r="I378" s="19"/>
       <c r="J378" s="20"/>
@@ -17554,7 +17564,7 @@
       <c r="D379" s="19"/>
       <c r="E379" s="20"/>
       <c r="F379" s="21"/>
-      <c r="G379" s="101"/>
+      <c r="G379" s="100"/>
       <c r="H379" s="19"/>
       <c r="I379" s="19"/>
       <c r="J379" s="20"/>
@@ -17587,7 +17597,7 @@
       <c r="D380" s="19"/>
       <c r="E380" s="20"/>
       <c r="F380" s="21"/>
-      <c r="G380" s="101"/>
+      <c r="G380" s="100"/>
       <c r="H380" s="19"/>
       <c r="I380" s="19"/>
       <c r="J380" s="20"/>
@@ -17620,7 +17630,7 @@
       <c r="D381" s="19"/>
       <c r="E381" s="20"/>
       <c r="F381" s="21"/>
-      <c r="G381" s="101"/>
+      <c r="G381" s="100"/>
       <c r="H381" s="19"/>
       <c r="I381" s="19"/>
       <c r="J381" s="20"/>
@@ -17653,7 +17663,7 @@
       <c r="D382" s="19"/>
       <c r="E382" s="20"/>
       <c r="F382" s="21"/>
-      <c r="G382" s="101"/>
+      <c r="G382" s="100"/>
       <c r="H382" s="19"/>
       <c r="I382" s="19"/>
       <c r="J382" s="20"/>
@@ -17686,7 +17696,7 @@
       <c r="D383" s="19"/>
       <c r="E383" s="20"/>
       <c r="F383" s="21"/>
-      <c r="G383" s="101"/>
+      <c r="G383" s="100"/>
       <c r="H383" s="19"/>
       <c r="I383" s="19"/>
       <c r="J383" s="20"/>
@@ -17719,7 +17729,7 @@
       <c r="D384" s="19"/>
       <c r="E384" s="20"/>
       <c r="F384" s="21"/>
-      <c r="G384" s="101"/>
+      <c r="G384" s="100"/>
       <c r="H384" s="19"/>
       <c r="I384" s="19"/>
       <c r="J384" s="20"/>
@@ -17752,7 +17762,7 @@
       <c r="D385" s="19"/>
       <c r="E385" s="20"/>
       <c r="F385" s="21"/>
-      <c r="G385" s="101"/>
+      <c r="G385" s="100"/>
       <c r="H385" s="19"/>
       <c r="I385" s="19"/>
       <c r="J385" s="20"/>
@@ -17785,7 +17795,7 @@
       <c r="D386" s="19"/>
       <c r="E386" s="20"/>
       <c r="F386" s="21"/>
-      <c r="G386" s="101"/>
+      <c r="G386" s="100"/>
       <c r="H386" s="19"/>
       <c r="I386" s="19"/>
       <c r="J386" s="20"/>
@@ -17818,7 +17828,7 @@
       <c r="D387" s="19"/>
       <c r="E387" s="20"/>
       <c r="F387" s="21"/>
-      <c r="G387" s="101"/>
+      <c r="G387" s="100"/>
       <c r="H387" s="19"/>
       <c r="I387" s="19"/>
       <c r="J387" s="20"/>
@@ -17851,7 +17861,7 @@
       <c r="D388" s="19"/>
       <c r="E388" s="20"/>
       <c r="F388" s="21"/>
-      <c r="G388" s="101"/>
+      <c r="G388" s="100"/>
       <c r="H388" s="19"/>
       <c r="I388" s="19"/>
       <c r="J388" s="20"/>
@@ -17884,7 +17894,7 @@
       <c r="D389" s="19"/>
       <c r="E389" s="20"/>
       <c r="F389" s="21"/>
-      <c r="G389" s="101"/>
+      <c r="G389" s="100"/>
       <c r="H389" s="19"/>
       <c r="I389" s="19"/>
       <c r="J389" s="20"/>
@@ -17917,7 +17927,7 @@
       <c r="D390" s="19"/>
       <c r="E390" s="20"/>
       <c r="F390" s="21"/>
-      <c r="G390" s="101"/>
+      <c r="G390" s="100"/>
       <c r="H390" s="19"/>
       <c r="I390" s="19"/>
       <c r="J390" s="20"/>
@@ -17950,7 +17960,7 @@
       <c r="D391" s="19"/>
       <c r="E391" s="20"/>
       <c r="F391" s="21"/>
-      <c r="G391" s="101"/>
+      <c r="G391" s="100"/>
       <c r="H391" s="19"/>
       <c r="I391" s="19"/>
       <c r="J391" s="20"/>
@@ -17983,7 +17993,7 @@
       <c r="D392" s="19"/>
       <c r="E392" s="20"/>
       <c r="F392" s="21"/>
-      <c r="G392" s="101"/>
+      <c r="G392" s="100"/>
       <c r="H392" s="19"/>
       <c r="I392" s="19"/>
       <c r="J392" s="20"/>
@@ -18016,7 +18026,7 @@
       <c r="D393" s="19"/>
       <c r="E393" s="20"/>
       <c r="F393" s="21"/>
-      <c r="G393" s="101"/>
+      <c r="G393" s="100"/>
       <c r="H393" s="19"/>
       <c r="I393" s="19"/>
       <c r="J393" s="20"/>
@@ -18049,7 +18059,7 @@
       <c r="D394" s="19"/>
       <c r="E394" s="20"/>
       <c r="F394" s="21"/>
-      <c r="G394" s="101"/>
+      <c r="G394" s="100"/>
       <c r="H394" s="19"/>
       <c r="I394" s="19"/>
       <c r="J394" s="20"/>
@@ -18082,7 +18092,7 @@
       <c r="D395" s="19"/>
       <c r="E395" s="20"/>
       <c r="F395" s="21"/>
-      <c r="G395" s="101"/>
+      <c r="G395" s="100"/>
       <c r="H395" s="19"/>
       <c r="I395" s="19"/>
       <c r="J395" s="20"/>
@@ -18115,7 +18125,7 @@
       <c r="D396" s="19"/>
       <c r="E396" s="20"/>
       <c r="F396" s="21"/>
-      <c r="G396" s="101"/>
+      <c r="G396" s="100"/>
       <c r="H396" s="19"/>
       <c r="I396" s="19"/>
       <c r="J396" s="20"/>
@@ -18148,7 +18158,7 @@
       <c r="D397" s="19"/>
       <c r="E397" s="20"/>
       <c r="F397" s="21"/>
-      <c r="G397" s="101"/>
+      <c r="G397" s="100"/>
       <c r="H397" s="19"/>
       <c r="I397" s="19"/>
       <c r="J397" s="20"/>
@@ -18181,7 +18191,7 @@
       <c r="D398" s="19"/>
       <c r="E398" s="20"/>
       <c r="F398" s="21"/>
-      <c r="G398" s="101"/>
+      <c r="G398" s="100"/>
       <c r="H398" s="19"/>
       <c r="I398" s="19"/>
       <c r="J398" s="20"/>
@@ -18214,7 +18224,7 @@
       <c r="D399" s="19"/>
       <c r="E399" s="20"/>
       <c r="F399" s="21"/>
-      <c r="G399" s="101"/>
+      <c r="G399" s="100"/>
       <c r="H399" s="19"/>
       <c r="I399" s="19"/>
       <c r="J399" s="20"/>
@@ -18247,7 +18257,7 @@
       <c r="D400" s="19"/>
       <c r="E400" s="20"/>
       <c r="F400" s="21"/>
-      <c r="G400" s="101"/>
+      <c r="G400" s="100"/>
       <c r="H400" s="19"/>
       <c r="I400" s="19"/>
       <c r="J400" s="20"/>
@@ -18280,7 +18290,7 @@
       <c r="D401" s="19"/>
       <c r="E401" s="20"/>
       <c r="F401" s="21"/>
-      <c r="G401" s="101"/>
+      <c r="G401" s="100"/>
       <c r="H401" s="19"/>
       <c r="I401" s="19"/>
       <c r="J401" s="20"/>
@@ -18313,7 +18323,7 @@
       <c r="D402" s="19"/>
       <c r="E402" s="20"/>
       <c r="F402" s="21"/>
-      <c r="G402" s="101"/>
+      <c r="G402" s="100"/>
       <c r="H402" s="19"/>
       <c r="I402" s="19"/>
       <c r="J402" s="20"/>
@@ -18346,7 +18356,7 @@
       <c r="D403" s="19"/>
       <c r="E403" s="20"/>
       <c r="F403" s="21"/>
-      <c r="G403" s="101"/>
+      <c r="G403" s="100"/>
       <c r="H403" s="19"/>
       <c r="I403" s="19"/>
       <c r="J403" s="20"/>
@@ -18379,7 +18389,7 @@
       <c r="D404" s="19"/>
       <c r="E404" s="20"/>
       <c r="F404" s="21"/>
-      <c r="G404" s="101"/>
+      <c r="G404" s="100"/>
       <c r="H404" s="19"/>
       <c r="I404" s="19"/>
       <c r="J404" s="20"/>
@@ -18412,7 +18422,7 @@
       <c r="D405" s="19"/>
       <c r="E405" s="20"/>
       <c r="F405" s="21"/>
-      <c r="G405" s="101"/>
+      <c r="G405" s="100"/>
       <c r="H405" s="19"/>
       <c r="I405" s="19"/>
       <c r="J405" s="20"/>
@@ -18445,7 +18455,7 @@
       <c r="D406" s="19"/>
       <c r="E406" s="20"/>
       <c r="F406" s="21"/>
-      <c r="G406" s="101"/>
+      <c r="G406" s="100"/>
       <c r="H406" s="19"/>
       <c r="I406" s="19"/>
       <c r="J406" s="20"/>
@@ -18478,7 +18488,7 @@
       <c r="D407" s="19"/>
       <c r="E407" s="20"/>
       <c r="F407" s="21"/>
-      <c r="G407" s="101"/>
+      <c r="G407" s="100"/>
       <c r="H407" s="19"/>
       <c r="I407" s="19"/>
       <c r="J407" s="20"/>
@@ -18511,7 +18521,7 @@
       <c r="D408" s="19"/>
       <c r="E408" s="20"/>
       <c r="F408" s="21"/>
-      <c r="G408" s="101"/>
+      <c r="G408" s="100"/>
       <c r="H408" s="19"/>
       <c r="I408" s="19"/>
       <c r="J408" s="20"/>
@@ -18544,7 +18554,7 @@
       <c r="D409" s="19"/>
       <c r="E409" s="20"/>
       <c r="F409" s="21"/>
-      <c r="G409" s="101"/>
+      <c r="G409" s="100"/>
       <c r="H409" s="19"/>
       <c r="I409" s="19"/>
       <c r="J409" s="20"/>
@@ -18577,7 +18587,7 @@
       <c r="D410" s="19"/>
       <c r="E410" s="20"/>
       <c r="F410" s="21"/>
-      <c r="G410" s="101"/>
+      <c r="G410" s="100"/>
       <c r="H410" s="19"/>
       <c r="I410" s="19"/>
       <c r="J410" s="20"/>
@@ -18610,7 +18620,7 @@
       <c r="D411" s="19"/>
       <c r="E411" s="20"/>
       <c r="F411" s="21"/>
-      <c r="G411" s="101"/>
+      <c r="G411" s="100"/>
       <c r="H411" s="19"/>
       <c r="I411" s="19"/>
       <c r="J411" s="20"/>
@@ -18643,7 +18653,7 @@
       <c r="D412" s="19"/>
       <c r="E412" s="20"/>
       <c r="F412" s="21"/>
-      <c r="G412" s="101"/>
+      <c r="G412" s="100"/>
       <c r="H412" s="19"/>
       <c r="I412" s="19"/>
       <c r="J412" s="20"/>
@@ -18676,7 +18686,7 @@
       <c r="D413" s="19"/>
       <c r="E413" s="20"/>
       <c r="F413" s="21"/>
-      <c r="G413" s="101"/>
+      <c r="G413" s="100"/>
       <c r="H413" s="19"/>
       <c r="I413" s="19"/>
       <c r="J413" s="20"/>
@@ -18709,7 +18719,7 @@
       <c r="D414" s="19"/>
       <c r="E414" s="20"/>
       <c r="F414" s="21"/>
-      <c r="G414" s="101"/>
+      <c r="G414" s="100"/>
       <c r="H414" s="19"/>
       <c r="I414" s="19"/>
       <c r="J414" s="20"/>
@@ -18742,7 +18752,7 @@
       <c r="D415" s="19"/>
       <c r="E415" s="20"/>
       <c r="F415" s="21"/>
-      <c r="G415" s="101"/>
+      <c r="G415" s="100"/>
       <c r="H415" s="19"/>
       <c r="I415" s="19"/>
       <c r="J415" s="20"/>
@@ -18775,7 +18785,7 @@
       <c r="D416" s="19"/>
       <c r="E416" s="20"/>
       <c r="F416" s="21"/>
-      <c r="G416" s="101"/>
+      <c r="G416" s="100"/>
       <c r="H416" s="19"/>
       <c r="I416" s="19"/>
       <c r="J416" s="20"/>
@@ -18808,7 +18818,7 @@
       <c r="D417" s="19"/>
       <c r="E417" s="20"/>
       <c r="F417" s="21"/>
-      <c r="G417" s="101"/>
+      <c r="G417" s="100"/>
       <c r="H417" s="19"/>
       <c r="I417" s="19"/>
       <c r="J417" s="20"/>
@@ -18841,7 +18851,7 @@
       <c r="D418" s="19"/>
       <c r="E418" s="20"/>
       <c r="F418" s="21"/>
-      <c r="G418" s="101"/>
+      <c r="G418" s="100"/>
       <c r="H418" s="19"/>
       <c r="I418" s="19"/>
       <c r="J418" s="20"/>
@@ -18874,7 +18884,7 @@
       <c r="D419" s="19"/>
       <c r="E419" s="20"/>
       <c r="F419" s="21"/>
-      <c r="G419" s="101"/>
+      <c r="G419" s="100"/>
       <c r="H419" s="19"/>
       <c r="I419" s="19"/>
       <c r="J419" s="20"/>
@@ -18907,7 +18917,7 @@
       <c r="D420" s="19"/>
       <c r="E420" s="20"/>
       <c r="F420" s="21"/>
-      <c r="G420" s="101"/>
+      <c r="G420" s="100"/>
       <c r="H420" s="19"/>
       <c r="I420" s="19"/>
       <c r="J420" s="20"/>
@@ -18940,7 +18950,7 @@
       <c r="D421" s="19"/>
       <c r="E421" s="20"/>
       <c r="F421" s="21"/>
-      <c r="G421" s="101"/>
+      <c r="G421" s="100"/>
       <c r="H421" s="19"/>
       <c r="I421" s="19"/>
       <c r="J421" s="20"/>
@@ -18973,7 +18983,7 @@
       <c r="D422" s="19"/>
       <c r="E422" s="20"/>
       <c r="F422" s="21"/>
-      <c r="G422" s="101"/>
+      <c r="G422" s="100"/>
       <c r="H422" s="19"/>
       <c r="I422" s="19"/>
       <c r="J422" s="20"/>
@@ -19006,7 +19016,7 @@
       <c r="D423" s="19"/>
       <c r="E423" s="20"/>
       <c r="F423" s="21"/>
-      <c r="G423" s="101"/>
+      <c r="G423" s="100"/>
       <c r="H423" s="19"/>
       <c r="I423" s="19"/>
       <c r="J423" s="20"/>
@@ -19039,7 +19049,7 @@
       <c r="D424" s="19"/>
       <c r="E424" s="20"/>
       <c r="F424" s="21"/>
-      <c r="G424" s="101"/>
+      <c r="G424" s="100"/>
       <c r="H424" s="19"/>
       <c r="I424" s="19"/>
       <c r="J424" s="20"/>
@@ -19072,7 +19082,7 @@
       <c r="D425" s="19"/>
       <c r="E425" s="20"/>
       <c r="F425" s="21"/>
-      <c r="G425" s="101"/>
+      <c r="G425" s="100"/>
       <c r="H425" s="19"/>
       <c r="I425" s="19"/>
       <c r="J425" s="20"/>
@@ -19105,7 +19115,7 @@
       <c r="D426" s="19"/>
       <c r="E426" s="20"/>
       <c r="F426" s="21"/>
-      <c r="G426" s="101"/>
+      <c r="G426" s="100"/>
       <c r="H426" s="19"/>
       <c r="I426" s="19"/>
       <c r="J426" s="20"/>
@@ -19138,7 +19148,7 @@
       <c r="D427" s="19"/>
       <c r="E427" s="20"/>
       <c r="F427" s="21"/>
-      <c r="G427" s="101"/>
+      <c r="G427" s="100"/>
       <c r="H427" s="19"/>
       <c r="I427" s="19"/>
       <c r="J427" s="20"/>
@@ -19171,7 +19181,7 @@
       <c r="D428" s="19"/>
       <c r="E428" s="20"/>
       <c r="F428" s="21"/>
-      <c r="G428" s="101"/>
+      <c r="G428" s="100"/>
       <c r="H428" s="19"/>
       <c r="I428" s="19"/>
       <c r="J428" s="20"/>
@@ -19204,7 +19214,7 @@
       <c r="D429" s="19"/>
       <c r="E429" s="20"/>
       <c r="F429" s="21"/>
-      <c r="G429" s="101"/>
+      <c r="G429" s="100"/>
       <c r="H429" s="19"/>
       <c r="I429" s="19"/>
       <c r="J429" s="20"/>
@@ -19237,7 +19247,7 @@
       <c r="D430" s="19"/>
       <c r="E430" s="20"/>
       <c r="F430" s="21"/>
-      <c r="G430" s="101"/>
+      <c r="G430" s="100"/>
       <c r="H430" s="19"/>
       <c r="I430" s="19"/>
       <c r="J430" s="20"/>
@@ -19270,7 +19280,7 @@
       <c r="D431" s="19"/>
       <c r="E431" s="20"/>
       <c r="F431" s="21"/>
-      <c r="G431" s="101"/>
+      <c r="G431" s="100"/>
       <c r="H431" s="19"/>
       <c r="I431" s="19"/>
       <c r="J431" s="20"/>
@@ -19303,7 +19313,7 @@
       <c r="D432" s="19"/>
       <c r="E432" s="20"/>
       <c r="F432" s="21"/>
-      <c r="G432" s="101"/>
+      <c r="G432" s="100"/>
       <c r="H432" s="19"/>
       <c r="I432" s="19"/>
       <c r="J432" s="20"/>
@@ -19336,7 +19346,7 @@
       <c r="D433" s="19"/>
       <c r="E433" s="20"/>
       <c r="F433" s="21"/>
-      <c r="G433" s="101"/>
+      <c r="G433" s="100"/>
       <c r="H433" s="19"/>
       <c r="I433" s="19"/>
       <c r="J433" s="20"/>
@@ -19369,7 +19379,7 @@
       <c r="D434" s="19"/>
       <c r="E434" s="20"/>
       <c r="F434" s="21"/>
-      <c r="G434" s="101"/>
+      <c r="G434" s="100"/>
       <c r="H434" s="19"/>
       <c r="I434" s="19"/>
       <c r="J434" s="20"/>
@@ -19402,7 +19412,7 @@
       <c r="D435" s="19"/>
       <c r="E435" s="20"/>
       <c r="F435" s="21"/>
-      <c r="G435" s="101"/>
+      <c r="G435" s="100"/>
       <c r="H435" s="19"/>
       <c r="I435" s="19"/>
       <c r="J435" s="20"/>
@@ -19435,7 +19445,7 @@
       <c r="D436" s="19"/>
       <c r="E436" s="20"/>
       <c r="F436" s="21"/>
-      <c r="G436" s="101"/>
+      <c r="G436" s="100"/>
       <c r="H436" s="19"/>
       <c r="I436" s="19"/>
       <c r="J436" s="20"/>
@@ -19468,7 +19478,7 @@
       <c r="D437" s="19"/>
       <c r="E437" s="20"/>
       <c r="F437" s="21"/>
-      <c r="G437" s="101"/>
+      <c r="G437" s="100"/>
       <c r="H437" s="19"/>
       <c r="I437" s="19"/>
       <c r="J437" s="20"/>
@@ -19501,7 +19511,7 @@
       <c r="D438" s="19"/>
       <c r="E438" s="20"/>
       <c r="F438" s="21"/>
-      <c r="G438" s="101"/>
+      <c r="G438" s="100"/>
       <c r="H438" s="19"/>
       <c r="I438" s="19"/>
       <c r="J438" s="20"/>
@@ -19534,7 +19544,7 @@
       <c r="D439" s="19"/>
       <c r="E439" s="20"/>
       <c r="F439" s="21"/>
-      <c r="G439" s="101"/>
+      <c r="G439" s="100"/>
       <c r="H439" s="19"/>
       <c r="I439" s="19"/>
       <c r="J439" s="20"/>
@@ -19567,7 +19577,7 @@
       <c r="D440" s="19"/>
       <c r="E440" s="20"/>
       <c r="F440" s="21"/>
-      <c r="G440" s="101"/>
+      <c r="G440" s="100"/>
       <c r="H440" s="19"/>
       <c r="I440" s="19"/>
       <c r="J440" s="20"/>
@@ -19600,7 +19610,7 @@
       <c r="D441" s="19"/>
       <c r="E441" s="20"/>
       <c r="F441" s="21"/>
-      <c r="G441" s="101"/>
+      <c r="G441" s="100"/>
       <c r="H441" s="19"/>
       <c r="I441" s="19"/>
       <c r="J441" s="20"/>
@@ -19633,7 +19643,7 @@
       <c r="D442" s="19"/>
       <c r="E442" s="20"/>
       <c r="F442" s="21"/>
-      <c r="G442" s="101"/>
+      <c r="G442" s="100"/>
       <c r="H442" s="19"/>
       <c r="I442" s="19"/>
       <c r="J442" s="20"/>
@@ -19666,7 +19676,7 @@
       <c r="D443" s="19"/>
       <c r="E443" s="20"/>
       <c r="F443" s="21"/>
-      <c r="G443" s="101"/>
+      <c r="G443" s="100"/>
       <c r="H443" s="19"/>
       <c r="I443" s="19"/>
       <c r="J443" s="20"/>
@@ -19699,7 +19709,7 @@
       <c r="D444" s="19"/>
       <c r="E444" s="20"/>
       <c r="F444" s="21"/>
-      <c r="G444" s="101"/>
+      <c r="G444" s="100"/>
       <c r="H444" s="19"/>
       <c r="I444" s="19"/>
       <c r="J444" s="20"/>
@@ -19732,7 +19742,7 @@
       <c r="D445" s="19"/>
       <c r="E445" s="20"/>
       <c r="F445" s="21"/>
-      <c r="G445" s="101"/>
+      <c r="G445" s="100"/>
       <c r="H445" s="19"/>
       <c r="I445" s="19"/>
       <c r="J445" s="20"/>
@@ -19765,7 +19775,7 @@
       <c r="D446" s="19"/>
       <c r="E446" s="20"/>
       <c r="F446" s="21"/>
-      <c r="G446" s="101"/>
+      <c r="G446" s="100"/>
       <c r="H446" s="19"/>
       <c r="I446" s="19"/>
       <c r="J446" s="20"/>
@@ -19798,7 +19808,7 @@
       <c r="D447" s="19"/>
       <c r="E447" s="20"/>
       <c r="F447" s="21"/>
-      <c r="G447" s="101"/>
+      <c r="G447" s="100"/>
       <c r="H447" s="19"/>
       <c r="I447" s="19"/>
       <c r="J447" s="20"/>
@@ -19831,7 +19841,7 @@
       <c r="D448" s="19"/>
       <c r="E448" s="20"/>
       <c r="F448" s="21"/>
-      <c r="G448" s="101"/>
+      <c r="G448" s="100"/>
       <c r="H448" s="19"/>
       <c r="I448" s="19"/>
       <c r="J448" s="20"/>
@@ -19864,7 +19874,7 @@
       <c r="D449" s="19"/>
       <c r="E449" s="20"/>
       <c r="F449" s="21"/>
-      <c r="G449" s="101"/>
+      <c r="G449" s="100"/>
       <c r="H449" s="19"/>
       <c r="I449" s="19"/>
       <c r="J449" s="20"/>
@@ -19897,7 +19907,7 @@
       <c r="D450" s="19"/>
       <c r="E450" s="20"/>
       <c r="F450" s="21"/>
-      <c r="G450" s="101"/>
+      <c r="G450" s="100"/>
       <c r="H450" s="19"/>
       <c r="I450" s="19"/>
       <c r="J450" s="20"/>
@@ -19930,7 +19940,7 @@
       <c r="D451" s="19"/>
       <c r="E451" s="20"/>
       <c r="F451" s="21"/>
-      <c r="G451" s="101"/>
+      <c r="G451" s="100"/>
       <c r="H451" s="19"/>
       <c r="I451" s="19"/>
       <c r="J451" s="20"/>
@@ -19963,7 +19973,7 @@
       <c r="D452" s="19"/>
       <c r="E452" s="20"/>
       <c r="F452" s="21"/>
-      <c r="G452" s="101"/>
+      <c r="G452" s="100"/>
       <c r="H452" s="19"/>
       <c r="I452" s="19"/>
       <c r="J452" s="20"/>
@@ -19996,7 +20006,7 @@
       <c r="D453" s="19"/>
       <c r="E453" s="20"/>
       <c r="F453" s="21"/>
-      <c r="G453" s="101"/>
+      <c r="G453" s="100"/>
       <c r="H453" s="19"/>
       <c r="I453" s="19"/>
       <c r="J453" s="20"/>
@@ -20029,7 +20039,7 @@
       <c r="D454" s="19"/>
       <c r="E454" s="20"/>
       <c r="F454" s="21"/>
-      <c r="G454" s="101"/>
+      <c r="G454" s="100"/>
       <c r="H454" s="19"/>
       <c r="I454" s="19"/>
       <c r="J454" s="20"/>
@@ -20062,7 +20072,7 @@
       <c r="D455" s="19"/>
       <c r="E455" s="20"/>
       <c r="F455" s="21"/>
-      <c r="G455" s="101"/>
+      <c r="G455" s="100"/>
       <c r="H455" s="19"/>
       <c r="I455" s="19"/>
       <c r="J455" s="20"/>
@@ -20095,7 +20105,7 @@
       <c r="D456" s="19"/>
       <c r="E456" s="20"/>
       <c r="F456" s="21"/>
-      <c r="G456" s="101"/>
+      <c r="G456" s="100"/>
       <c r="H456" s="19"/>
       <c r="I456" s="19"/>
       <c r="J456" s="20"/>
@@ -20128,7 +20138,7 @@
       <c r="D457" s="19"/>
       <c r="E457" s="20"/>
       <c r="F457" s="21"/>
-      <c r="G457" s="101"/>
+      <c r="G457" s="100"/>
       <c r="H457" s="19"/>
       <c r="I457" s="19"/>
       <c r="J457" s="20"/>
@@ -20161,7 +20171,7 @@
       <c r="D458" s="19"/>
       <c r="E458" s="20"/>
       <c r="F458" s="21"/>
-      <c r="G458" s="101"/>
+      <c r="G458" s="100"/>
       <c r="H458" s="19"/>
       <c r="I458" s="19"/>
       <c r="J458" s="20"/>
@@ -20194,7 +20204,7 @@
       <c r="D459" s="19"/>
       <c r="E459" s="20"/>
       <c r="F459" s="21"/>
-      <c r="G459" s="101"/>
+      <c r="G459" s="100"/>
       <c r="H459" s="19"/>
       <c r="I459" s="19"/>
       <c r="J459" s="20"/>
@@ -20227,7 +20237,7 @@
       <c r="D460" s="19"/>
       <c r="E460" s="20"/>
       <c r="F460" s="21"/>
-      <c r="G460" s="101"/>
+      <c r="G460" s="100"/>
       <c r="H460" s="19"/>
       <c r="I460" s="19"/>
       <c r="J460" s="20"/>
@@ -20260,7 +20270,7 @@
       <c r="D461" s="19"/>
       <c r="E461" s="20"/>
       <c r="F461" s="21"/>
-      <c r="G461" s="101"/>
+      <c r="G461" s="100"/>
       <c r="H461" s="19"/>
       <c r="I461" s="19"/>
       <c r="J461" s="20"/>
@@ -20293,7 +20303,7 @@
       <c r="D462" s="19"/>
       <c r="E462" s="20"/>
       <c r="F462" s="21"/>
-      <c r="G462" s="101"/>
+      <c r="G462" s="100"/>
       <c r="H462" s="19"/>
       <c r="I462" s="19"/>
       <c r="J462" s="20"/>
@@ -20326,7 +20336,7 @@
       <c r="D463" s="19"/>
       <c r="E463" s="20"/>
       <c r="F463" s="21"/>
-      <c r="G463" s="101"/>
+      <c r="G463" s="100"/>
       <c r="H463" s="19"/>
       <c r="I463" s="19"/>
       <c r="J463" s="20"/>
@@ -20359,7 +20369,7 @@
       <c r="D464" s="19"/>
       <c r="E464" s="20"/>
       <c r="F464" s="21"/>
-      <c r="G464" s="101"/>
+      <c r="G464" s="100"/>
       <c r="H464" s="19"/>
       <c r="I464" s="19"/>
       <c r="J464" s="20"/>
@@ -20392,7 +20402,7 @@
       <c r="D465" s="19"/>
       <c r="E465" s="20"/>
       <c r="F465" s="21"/>
-      <c r="G465" s="101"/>
+      <c r="G465" s="100"/>
       <c r="H465" s="19"/>
       <c r="I465" s="19"/>
       <c r="J465" s="20"/>
@@ -20425,7 +20435,7 @@
       <c r="D466" s="19"/>
       <c r="E466" s="20"/>
       <c r="F466" s="21"/>
-      <c r="G466" s="101"/>
+      <c r="G466" s="100"/>
       <c r="H466" s="19"/>
       <c r="I466" s="19"/>
       <c r="J466" s="20"/>
@@ -20458,7 +20468,7 @@
       <c r="D467" s="19"/>
       <c r="E467" s="20"/>
       <c r="F467" s="21"/>
-      <c r="G467" s="101"/>
+      <c r="G467" s="100"/>
       <c r="H467" s="19"/>
       <c r="I467" s="19"/>
       <c r="J467" s="20"/>
@@ -20491,7 +20501,7 @@
       <c r="D468" s="19"/>
       <c r="E468" s="20"/>
       <c r="F468" s="21"/>
-      <c r="G468" s="101"/>
+      <c r="G468" s="100"/>
       <c r="H468" s="19"/>
       <c r="I468" s="19"/>
       <c r="J468" s="20"/>
@@ -20524,7 +20534,7 @@
       <c r="D469" s="19"/>
       <c r="E469" s="20"/>
       <c r="F469" s="21"/>
-      <c r="G469" s="101"/>
+      <c r="G469" s="100"/>
       <c r="H469" s="19"/>
       <c r="I469" s="19"/>
       <c r="J469" s="20"/>
@@ -20557,7 +20567,7 @@
       <c r="D470" s="19"/>
       <c r="E470" s="20"/>
       <c r="F470" s="21"/>
-      <c r="G470" s="101"/>
+      <c r="G470" s="100"/>
       <c r="H470" s="19"/>
       <c r="I470" s="19"/>
       <c r="J470" s="20"/>
@@ -20590,7 +20600,7 @@
       <c r="D471" s="19"/>
       <c r="E471" s="20"/>
       <c r="F471" s="21"/>
-      <c r="G471" s="101"/>
+      <c r="G471" s="100"/>
       <c r="H471" s="19"/>
       <c r="I471" s="19"/>
       <c r="J471" s="20"/>
@@ -20623,7 +20633,7 @@
       <c r="D472" s="19"/>
       <c r="E472" s="20"/>
       <c r="F472" s="21"/>
-      <c r="G472" s="101"/>
+      <c r="G472" s="100"/>
       <c r="H472" s="19"/>
       <c r="I472" s="19"/>
       <c r="J472" s="20"/>
@@ -20656,7 +20666,7 @@
       <c r="D473" s="19"/>
       <c r="E473" s="20"/>
       <c r="F473" s="21"/>
-      <c r="G473" s="101"/>
+      <c r="G473" s="100"/>
       <c r="H473" s="19"/>
       <c r="I473" s="19"/>
       <c r="J473" s="20"/>
@@ -20689,7 +20699,7 @@
       <c r="D474" s="19"/>
       <c r="E474" s="20"/>
       <c r="F474" s="21"/>
-      <c r="G474" s="101"/>
+      <c r="G474" s="100"/>
       <c r="H474" s="19"/>
       <c r="I474" s="19"/>
       <c r="J474" s="20"/>
@@ -20722,7 +20732,7 @@
       <c r="D475" s="19"/>
       <c r="E475" s="20"/>
       <c r="F475" s="21"/>
-      <c r="G475" s="101"/>
+      <c r="G475" s="100"/>
       <c r="H475" s="19"/>
       <c r="I475" s="19"/>
       <c r="J475" s="20"/>
@@ -20755,7 +20765,7 @@
       <c r="D476" s="19"/>
       <c r="E476" s="20"/>
       <c r="F476" s="21"/>
-      <c r="G476" s="101"/>
+      <c r="G476" s="100"/>
       <c r="H476" s="19"/>
       <c r="I476" s="19"/>
       <c r="J476" s="20"/>
@@ -20788,7 +20798,7 @@
       <c r="D477" s="19"/>
       <c r="E477" s="20"/>
       <c r="F477" s="21"/>
-      <c r="G477" s="101"/>
+      <c r="G477" s="100"/>
       <c r="H477" s="19"/>
       <c r="I477" s="19"/>
       <c r="J477" s="20"/>
@@ -20821,7 +20831,7 @@
       <c r="D478" s="19"/>
       <c r="E478" s="20"/>
       <c r="F478" s="21"/>
-      <c r="G478" s="101"/>
+      <c r="G478" s="100"/>
       <c r="H478" s="19"/>
       <c r="I478" s="19"/>
       <c r="J478" s="20"/>
@@ -20854,7 +20864,7 @@
       <c r="D479" s="19"/>
       <c r="E479" s="20"/>
       <c r="F479" s="21"/>
-      <c r="G479" s="101"/>
+      <c r="G479" s="100"/>
       <c r="H479" s="19"/>
       <c r="I479" s="19"/>
       <c r="J479" s="20"/>
@@ -20887,7 +20897,7 @@
       <c r="D480" s="19"/>
       <c r="E480" s="20"/>
       <c r="F480" s="21"/>
-      <c r="G480" s="101"/>
+      <c r="G480" s="100"/>
       <c r="H480" s="19"/>
       <c r="I480" s="19"/>
       <c r="J480" s="20"/>
@@ -20920,7 +20930,7 @@
       <c r="D481" s="19"/>
       <c r="E481" s="20"/>
       <c r="F481" s="21"/>
-      <c r="G481" s="101"/>
+      <c r="G481" s="100"/>
       <c r="H481" s="19"/>
       <c r="I481" s="19"/>
       <c r="J481" s="20"/>
@@ -20953,7 +20963,7 @@
       <c r="D482" s="19"/>
       <c r="E482" s="20"/>
       <c r="F482" s="21"/>
-      <c r="G482" s="101"/>
+      <c r="G482" s="100"/>
       <c r="H482" s="19"/>
       <c r="I482" s="19"/>
       <c r="J482" s="20"/>
@@ -20986,7 +20996,7 @@
       <c r="D483" s="19"/>
       <c r="E483" s="20"/>
       <c r="F483" s="21"/>
-      <c r="G483" s="101"/>
+      <c r="G483" s="100"/>
       <c r="H483" s="19"/>
       <c r="I483" s="19"/>
       <c r="J483" s="20"/>
@@ -21019,7 +21029,7 @@
       <c r="D484" s="19"/>
       <c r="E484" s="20"/>
       <c r="F484" s="21"/>
-      <c r="G484" s="101"/>
+      <c r="G484" s="100"/>
       <c r="H484" s="19"/>
       <c r="I484" s="19"/>
       <c r="J484" s="20"/>
@@ -21052,7 +21062,7 @@
       <c r="D485" s="19"/>
       <c r="E485" s="20"/>
       <c r="F485" s="21"/>
-      <c r="G485" s="101"/>
+      <c r="G485" s="100"/>
       <c r="H485" s="19"/>
       <c r="I485" s="19"/>
       <c r="J485" s="20"/>
@@ -21085,7 +21095,7 @@
       <c r="D486" s="19"/>
       <c r="E486" s="20"/>
       <c r="F486" s="21"/>
-      <c r="G486" s="101"/>
+      <c r="G486" s="100"/>
       <c r="H486" s="19"/>
       <c r="I486" s="19"/>
       <c r="J486" s="20"/>
@@ -21118,7 +21128,7 @@
       <c r="D487" s="19"/>
       <c r="E487" s="20"/>
       <c r="F487" s="21"/>
-      <c r="G487" s="101"/>
+      <c r="G487" s="100"/>
       <c r="H487" s="19"/>
       <c r="I487" s="19"/>
       <c r="J487" s="20"/>
@@ -21151,7 +21161,7 @@
       <c r="D488" s="19"/>
       <c r="E488" s="20"/>
       <c r="F488" s="21"/>
-      <c r="G488" s="101"/>
+      <c r="G488" s="100"/>
       <c r="H488" s="19"/>
       <c r="I488" s="19"/>
       <c r="J488" s="20"/>
@@ -21184,7 +21194,7 @@
       <c r="D489" s="19"/>
       <c r="E489" s="20"/>
       <c r="F489" s="21"/>
-      <c r="G489" s="101"/>
+      <c r="G489" s="100"/>
       <c r="H489" s="19"/>
       <c r="I489" s="19"/>
       <c r="J489" s="20"/>
@@ -21217,7 +21227,7 @@
       <c r="D490" s="19"/>
       <c r="E490" s="20"/>
       <c r="F490" s="21"/>
-      <c r="G490" s="101"/>
+      <c r="G490" s="100"/>
       <c r="H490" s="19"/>
       <c r="I490" s="19"/>
       <c r="J490" s="20"/>
@@ -21250,7 +21260,7 @@
       <c r="D491" s="19"/>
       <c r="E491" s="20"/>
       <c r="F491" s="21"/>
-      <c r="G491" s="101"/>
+      <c r="G491" s="100"/>
       <c r="H491" s="19"/>
       <c r="I491" s="19"/>
       <c r="J491" s="20"/>
@@ -21283,7 +21293,7 @@
       <c r="D492" s="19"/>
       <c r="E492" s="20"/>
       <c r="F492" s="21"/>
-      <c r="G492" s="101"/>
+      <c r="G492" s="100"/>
       <c r="H492" s="19"/>
       <c r="I492" s="19"/>
       <c r="J492" s="20"/>
@@ -21316,7 +21326,7 @@
       <c r="D493" s="19"/>
       <c r="E493" s="20"/>
       <c r="F493" s="21"/>
-      <c r="G493" s="101"/>
+      <c r="G493" s="100"/>
       <c r="H493" s="19"/>
       <c r="I493" s="19"/>
       <c r="J493" s="20"/>
@@ -21349,7 +21359,7 @@
       <c r="D494" s="19"/>
       <c r="E494" s="20"/>
       <c r="F494" s="21"/>
-      <c r="G494" s="101"/>
+      <c r="G494" s="100"/>
       <c r="H494" s="19"/>
       <c r="I494" s="19"/>
       <c r="J494" s="20"/>
@@ -21382,7 +21392,7 @@
       <c r="D495" s="19"/>
       <c r="E495" s="20"/>
       <c r="F495" s="21"/>
-      <c r="G495" s="101"/>
+      <c r="G495" s="100"/>
       <c r="H495" s="19"/>
       <c r="I495" s="19"/>
       <c r="J495" s="20"/>
@@ -21415,7 +21425,7 @@
       <c r="D496" s="19"/>
       <c r="E496" s="20"/>
       <c r="F496" s="21"/>
-      <c r="G496" s="101"/>
+      <c r="G496" s="100"/>
       <c r="H496" s="19"/>
       <c r="I496" s="19"/>
       <c r="J496" s="20"/>
@@ -21448,7 +21458,7 @@
       <c r="D497" s="19"/>
       <c r="E497" s="20"/>
       <c r="F497" s="21"/>
-      <c r="G497" s="101"/>
+      <c r="G497" s="100"/>
       <c r="H497" s="19"/>
       <c r="I497" s="19"/>
       <c r="J497" s="20"/>
@@ -21481,7 +21491,7 @@
       <c r="D498" s="19"/>
       <c r="E498" s="20"/>
       <c r="F498" s="21"/>
-      <c r="G498" s="101"/>
+      <c r="G498" s="100"/>
       <c r="H498" s="19"/>
       <c r="I498" s="19"/>
       <c r="J498" s="20"/>
@@ -21514,7 +21524,7 @@
       <c r="D499" s="19"/>
       <c r="E499" s="20"/>
       <c r="F499" s="21"/>
-      <c r="G499" s="101"/>
+      <c r="G499" s="100"/>
       <c r="H499" s="19"/>
       <c r="I499" s="19"/>
       <c r="J499" s="20"/>
@@ -21547,7 +21557,7 @@
       <c r="D500" s="19"/>
       <c r="E500" s="20"/>
       <c r="F500" s="21"/>
-      <c r="G500" s="101"/>
+      <c r="G500" s="100"/>
       <c r="H500" s="19"/>
       <c r="I500" s="19"/>
       <c r="J500" s="20"/>
@@ -21580,7 +21590,7 @@
       <c r="D501" s="19"/>
       <c r="E501" s="20"/>
       <c r="F501" s="21"/>
-      <c r="G501" s="101"/>
+      <c r="G501" s="100"/>
       <c r="H501" s="19"/>
       <c r="I501" s="19"/>
       <c r="J501" s="20"/>
@@ -21613,7 +21623,7 @@
       <c r="D502" s="19"/>
       <c r="E502" s="20"/>
       <c r="F502" s="21"/>
-      <c r="G502" s="101"/>
+      <c r="G502" s="100"/>
       <c r="H502" s="19"/>
       <c r="I502" s="19"/>
       <c r="J502" s="20"/>
@@ -21646,7 +21656,7 @@
       <c r="D503" s="19"/>
       <c r="E503" s="20"/>
       <c r="F503" s="21"/>
-      <c r="G503" s="101"/>
+      <c r="G503" s="100"/>
       <c r="H503" s="19"/>
       <c r="I503" s="19"/>
       <c r="J503" s="20"/>
@@ -21679,7 +21689,7 @@
       <c r="D504" s="19"/>
       <c r="E504" s="20"/>
       <c r="F504" s="21"/>
-      <c r="G504" s="101"/>
+      <c r="G504" s="100"/>
       <c r="H504" s="19"/>
       <c r="I504" s="19"/>
       <c r="J504" s="20"/>
@@ -21712,7 +21722,7 @@
       <c r="D505" s="19"/>
       <c r="E505" s="20"/>
       <c r="F505" s="21"/>
-      <c r="G505" s="101"/>
+      <c r="G505" s="100"/>
       <c r="H505" s="19"/>
       <c r="I505" s="19"/>
       <c r="J505" s="20"/>
@@ -21745,7 +21755,7 @@
       <c r="D506" s="19"/>
       <c r="E506" s="20"/>
       <c r="F506" s="21"/>
-      <c r="G506" s="101"/>
+      <c r="G506" s="100"/>
       <c r="H506" s="19"/>
       <c r="I506" s="19"/>
       <c r="J506" s="20"/>
@@ -21778,7 +21788,7 @@
       <c r="D507" s="19"/>
       <c r="E507" s="20"/>
       <c r="F507" s="21"/>
-      <c r="G507" s="101"/>
+      <c r="G507" s="100"/>
       <c r="H507" s="19"/>
       <c r="I507" s="19"/>
       <c r="J507" s="20"/>
@@ -21811,7 +21821,7 @@
       <c r="D508" s="19"/>
       <c r="E508" s="20"/>
       <c r="F508" s="21"/>
-      <c r="G508" s="101"/>
+      <c r="G508" s="100"/>
       <c r="H508" s="19"/>
       <c r="I508" s="19"/>
       <c r="J508" s="20"/>
@@ -21844,7 +21854,7 @@
       <c r="D509" s="19"/>
       <c r="E509" s="20"/>
       <c r="F509" s="21"/>
-      <c r="G509" s="101"/>
+      <c r="G509" s="100"/>
       <c r="H509" s="19"/>
       <c r="I509" s="19"/>
       <c r="J509" s="20"/>
@@ -21877,7 +21887,7 @@
       <c r="D510" s="19"/>
       <c r="E510" s="20"/>
       <c r="F510" s="21"/>
-      <c r="G510" s="101"/>
+      <c r="G510" s="100"/>
       <c r="H510" s="19"/>
       <c r="I510" s="19"/>
       <c r="J510" s="20"/>
@@ -21910,7 +21920,7 @@
       <c r="D511" s="19"/>
       <c r="E511" s="20"/>
       <c r="F511" s="21"/>
-      <c r="G511" s="101"/>
+      <c r="G511" s="100"/>
       <c r="H511" s="19"/>
       <c r="I511" s="19"/>
       <c r="J511" s="20"/>
@@ -21943,7 +21953,7 @@
       <c r="D512" s="19"/>
       <c r="E512" s="20"/>
       <c r="F512" s="21"/>
-      <c r="G512" s="101"/>
+      <c r="G512" s="100"/>
       <c r="H512" s="19"/>
       <c r="I512" s="19"/>
       <c r="J512" s="20"/>
@@ -21976,7 +21986,7 @@
       <c r="D513" s="19"/>
       <c r="E513" s="20"/>
       <c r="F513" s="21"/>
-      <c r="G513" s="101"/>
+      <c r="G513" s="100"/>
       <c r="H513" s="19"/>
       <c r="I513" s="19"/>
       <c r="J513" s="20"/>
@@ -22009,7 +22019,7 @@
       <c r="D514" s="19"/>
       <c r="E514" s="20"/>
       <c r="F514" s="21"/>
-      <c r="G514" s="101"/>
+      <c r="G514" s="100"/>
       <c r="H514" s="19"/>
       <c r="I514" s="19"/>
       <c r="J514" s="20"/>
@@ -22042,7 +22052,7 @@
       <c r="D515" s="19"/>
       <c r="E515" s="20"/>
       <c r="F515" s="21"/>
-      <c r="G515" s="101"/>
+      <c r="G515" s="100"/>
       <c r="H515" s="19"/>
       <c r="I515" s="19"/>
       <c r="J515" s="20"/>
@@ -22075,7 +22085,7 @@
       <c r="D516" s="19"/>
       <c r="E516" s="20"/>
       <c r="F516" s="21"/>
-      <c r="G516" s="101"/>
+      <c r="G516" s="100"/>
       <c r="H516" s="19"/>
       <c r="I516" s="19"/>
       <c r="J516" s="20"/>
@@ -22108,7 +22118,7 @@
       <c r="D517" s="19"/>
       <c r="E517" s="20"/>
       <c r="F517" s="21"/>
-      <c r="G517" s="101"/>
+      <c r="G517" s="100"/>
       <c r="H517" s="19"/>
       <c r="I517" s="19"/>
       <c r="J517" s="20"/>
@@ -22141,7 +22151,7 @@
       <c r="D518" s="19"/>
       <c r="E518" s="20"/>
       <c r="F518" s="21"/>
-      <c r="G518" s="101"/>
+      <c r="G518" s="100"/>
       <c r="H518" s="19"/>
       <c r="I518" s="19"/>
       <c r="J518" s="20"/>
@@ -22174,7 +22184,7 @@
       <c r="D519" s="19"/>
       <c r="E519" s="20"/>
       <c r="F519" s="21"/>
-      <c r="G519" s="101"/>
+      <c r="G519" s="100"/>
       <c r="H519" s="19"/>
       <c r="I519" s="19"/>
       <c r="J519" s="20"/>
@@ -22207,7 +22217,7 @@
       <c r="D520" s="19"/>
       <c r="E520" s="20"/>
       <c r="F520" s="21"/>
-      <c r="G520" s="101"/>
+      <c r="G520" s="100"/>
       <c r="H520" s="19"/>
       <c r="I520" s="19"/>
       <c r="J520" s="20"/>
@@ -22240,7 +22250,7 @@
       <c r="D521" s="19"/>
       <c r="E521" s="20"/>
       <c r="F521" s="21"/>
-      <c r="G521" s="101"/>
+      <c r="G521" s="100"/>
       <c r="H521" s="19"/>
       <c r="I521" s="19"/>
       <c r="J521" s="20"/>
@@ -22273,7 +22283,7 @@
       <c r="D522" s="19"/>
       <c r="E522" s="20"/>
       <c r="F522" s="21"/>
-      <c r="G522" s="101"/>
+      <c r="G522" s="100"/>
       <c r="H522" s="19"/>
       <c r="I522" s="19"/>
       <c r="J522" s="20"/>
@@ -22306,7 +22316,7 @@
       <c r="D523" s="19"/>
       <c r="E523" s="20"/>
       <c r="F523" s="21"/>
-      <c r="G523" s="101"/>
+      <c r="G523" s="100"/>
       <c r="H523" s="19"/>
       <c r="I523" s="19"/>
       <c r="J523" s="20"/>
@@ -22339,7 +22349,7 @@
       <c r="D524" s="19"/>
       <c r="E524" s="20"/>
       <c r="F524" s="21"/>
-      <c r="G524" s="101"/>
+      <c r="G524" s="100"/>
       <c r="H524" s="19"/>
       <c r="I524" s="19"/>
       <c r="J524" s="20"/>
@@ -22372,7 +22382,7 @@
       <c r="D525" s="19"/>
       <c r="E525" s="20"/>
       <c r="F525" s="21"/>
-      <c r="G525" s="101"/>
+      <c r="G525" s="100"/>
       <c r="H525" s="19"/>
       <c r="I525" s="19"/>
       <c r="J525" s="20"/>
@@ -22405,7 +22415,7 @@
       <c r="D526" s="19"/>
       <c r="E526" s="20"/>
       <c r="F526" s="21"/>
-      <c r="G526" s="101"/>
+      <c r="G526" s="100"/>
       <c r="H526" s="19"/>
       <c r="I526" s="19"/>
       <c r="J526" s="20"/>
@@ -22438,7 +22448,7 @@
       <c r="D527" s="19"/>
       <c r="E527" s="20"/>
       <c r="F527" s="21"/>
-      <c r="G527" s="101"/>
+      <c r="G527" s="100"/>
       <c r="H527" s="19"/>
       <c r="I527" s="19"/>
       <c r="J527" s="20"/>
@@ -22471,7 +22481,7 @@
       <c r="D528" s="19"/>
       <c r="E528" s="20"/>
       <c r="F528" s="21"/>
-      <c r="G528" s="101"/>
+      <c r="G528" s="100"/>
       <c r="H528" s="19"/>
       <c r="I528" s="19"/>
       <c r="J528" s="20"/>
@@ -22504,7 +22514,7 @@
       <c r="D529" s="19"/>
       <c r="E529" s="20"/>
       <c r="F529" s="21"/>
-      <c r="G529" s="101"/>
+      <c r="G529" s="100"/>
       <c r="H529" s="19"/>
       <c r="I529" s="19"/>
       <c r="J529" s="20"/>
@@ -22537,7 +22547,7 @@
       <c r="D530" s="19"/>
       <c r="E530" s="20"/>
       <c r="F530" s="21"/>
-      <c r="G530" s="101"/>
+      <c r="G530" s="100"/>
       <c r="H530" s="19"/>
       <c r="I530" s="19"/>
       <c r="J530" s="20"/>
@@ -22570,7 +22580,7 @@
       <c r="D531" s="19"/>
       <c r="E531" s="20"/>
       <c r="F531" s="21"/>
-      <c r="G531" s="101"/>
+      <c r="G531" s="100"/>
       <c r="H531" s="19"/>
       <c r="I531" s="19"/>
       <c r="J531" s="20"/>
@@ -22603,7 +22613,7 @@
       <c r="D532" s="19"/>
       <c r="E532" s="20"/>
       <c r="F532" s="21"/>
-      <c r="G532" s="101"/>
+      <c r="G532" s="100"/>
       <c r="H532" s="19"/>
       <c r="I532" s="19"/>
       <c r="J532" s="20"/>
@@ -22636,7 +22646,7 @@
       <c r="D533" s="19"/>
       <c r="E533" s="20"/>
       <c r="F533" s="21"/>
-      <c r="G533" s="101"/>
+      <c r="G533" s="100"/>
       <c r="H533" s="19"/>
       <c r="I533" s="19"/>
       <c r="J533" s="20"/>
@@ -22669,7 +22679,7 @@
       <c r="D534" s="19"/>
       <c r="E534" s="20"/>
       <c r="F534" s="21"/>
-      <c r="G534" s="101"/>
+      <c r="G534" s="100"/>
       <c r="H534" s="19"/>
       <c r="I534" s="19"/>
       <c r="J534" s="20"/>
@@ -22702,7 +22712,7 @@
       <c r="D535" s="19"/>
       <c r="E535" s="20"/>
       <c r="F535" s="21"/>
-      <c r="G535" s="101"/>
+      <c r="G535" s="100"/>
       <c r="H535" s="19"/>
       <c r="I535" s="19"/>
       <c r="J535" s="20"/>
@@ -22735,7 +22745,7 @@
       <c r="D536" s="19"/>
       <c r="E536" s="20"/>
       <c r="F536" s="21"/>
-      <c r="G536" s="101"/>
+      <c r="G536" s="100"/>
       <c r="H536" s="19"/>
       <c r="I536" s="19"/>
       <c r="J536" s="20"/>
@@ -22768,7 +22778,7 @@
       <c r="D537" s="19"/>
       <c r="E537" s="20"/>
       <c r="F537" s="21"/>
-      <c r="G537" s="101"/>
+      <c r="G537" s="100"/>
       <c r="H537" s="19"/>
       <c r="I537" s="19"/>
       <c r="J537" s="20"/>
@@ -22801,7 +22811,7 @@
       <c r="D538" s="19"/>
       <c r="E538" s="20"/>
       <c r="F538" s="21"/>
-      <c r="G538" s="101"/>
+      <c r="G538" s="100"/>
       <c r="H538" s="19"/>
       <c r="I538" s="19"/>
       <c r="J538" s="20"/>
@@ -22834,7 +22844,7 @@
       <c r="D539" s="19"/>
       <c r="E539" s="20"/>
       <c r="F539" s="21"/>
-      <c r="G539" s="101"/>
+      <c r="G539" s="100"/>
       <c r="H539" s="19"/>
       <c r="I539" s="19"/>
       <c r="J539" s="20"/>
@@ -22867,7 +22877,7 @@
       <c r="D540" s="19"/>
       <c r="E540" s="20"/>
       <c r="F540" s="21"/>
-      <c r="G540" s="101"/>
+      <c r="G540" s="100"/>
       <c r="H540" s="19"/>
       <c r="I540" s="19"/>
       <c r="J540" s="20"/>
@@ -22900,7 +22910,7 @@
       <c r="D541" s="19"/>
       <c r="E541" s="20"/>
       <c r="F541" s="21"/>
-      <c r="G541" s="101"/>
+      <c r="G541" s="100"/>
       <c r="H541" s="19"/>
       <c r="I541" s="19"/>
       <c r="J541" s="20"/>
@@ -22933,7 +22943,7 @@
       <c r="D542" s="19"/>
       <c r="E542" s="20"/>
       <c r="F542" s="21"/>
-      <c r="G542" s="101"/>
+      <c r="G542" s="100"/>
       <c r="H542" s="19"/>
       <c r="I542" s="19"/>
       <c r="J542" s="20"/>
@@ -22966,7 +22976,7 @@
       <c r="D543" s="19"/>
       <c r="E543" s="20"/>
       <c r="F543" s="21"/>
-      <c r="G543" s="101"/>
+      <c r="G543" s="100"/>
       <c r="H543" s="19"/>
       <c r="I543" s="19"/>
       <c r="J543" s="20"/>
@@ -22999,7 +23009,7 @@
       <c r="D544" s="19"/>
       <c r="E544" s="20"/>
       <c r="F544" s="21"/>
-      <c r="G544" s="101"/>
+      <c r="G544" s="100"/>
       <c r="H544" s="19"/>
       <c r="I544" s="19"/>
       <c r="J544" s="20"/>
@@ -23032,7 +23042,7 @@
       <c r="D545" s="19"/>
       <c r="E545" s="20"/>
       <c r="F545" s="21"/>
-      <c r="G545" s="101"/>
+      <c r="G545" s="100"/>
       <c r="H545" s="19"/>
       <c r="I545" s="19"/>
       <c r="J545" s="20"/>
@@ -23065,7 +23075,7 @@
       <c r="D546" s="19"/>
       <c r="E546" s="20"/>
       <c r="F546" s="21"/>
-      <c r="G546" s="101"/>
+      <c r="G546" s="100"/>
       <c r="H546" s="19"/>
       <c r="I546" s="19"/>
       <c r="J546" s="20"/>
@@ -23098,7 +23108,7 @@
       <c r="D547" s="19"/>
       <c r="E547" s="20"/>
       <c r="F547" s="21"/>
-      <c r="G547" s="101"/>
+      <c r="G547" s="100"/>
       <c r="H547" s="19"/>
       <c r="I547" s="19"/>
       <c r="J547" s="20"/>
@@ -23131,7 +23141,7 @@
       <c r="D548" s="19"/>
       <c r="E548" s="20"/>
       <c r="F548" s="21"/>
-      <c r="G548" s="101"/>
+      <c r="G548" s="100"/>
       <c r="H548" s="19"/>
       <c r="I548" s="19"/>
       <c r="J548" s="20"/>
@@ -23164,7 +23174,7 @@
       <c r="D549" s="19"/>
       <c r="E549" s="20"/>
       <c r="F549" s="21"/>
-      <c r="G549" s="101"/>
+      <c r="G549" s="100"/>
       <c r="H549" s="19"/>
       <c r="I549" s="19"/>
       <c r="J549" s="20"/>
@@ -23197,7 +23207,7 @@
       <c r="D550" s="19"/>
       <c r="E550" s="20"/>
       <c r="F550" s="21"/>
-      <c r="G550" s="101"/>
+      <c r="G550" s="100"/>
       <c r="H550" s="19"/>
       <c r="I550" s="19"/>
       <c r="J550" s="20"/>
@@ -23230,7 +23240,7 @@
       <c r="D551" s="19"/>
       <c r="E551" s="20"/>
       <c r="F551" s="21"/>
-      <c r="G551" s="101"/>
+      <c r="G551" s="100"/>
       <c r="H551" s="19"/>
       <c r="I551" s="19"/>
       <c r="J551" s="20"/>
@@ -23263,7 +23273,7 @@
       <c r="D552" s="19"/>
       <c r="E552" s="20"/>
       <c r="F552" s="21"/>
-      <c r="G552" s="101"/>
+      <c r="G552" s="100"/>
       <c r="H552" s="19"/>
       <c r="I552" s="19"/>
       <c r="J552" s="20"/>
@@ -23296,7 +23306,7 @@
       <c r="D553" s="19"/>
       <c r="E553" s="20"/>
       <c r="F553" s="21"/>
-      <c r="G553" s="101"/>
+      <c r="G553" s="100"/>
       <c r="H553" s="19"/>
       <c r="I553" s="19"/>
       <c r="J553" s="20"/>
@@ -23329,7 +23339,7 @@
       <c r="D554" s="19"/>
       <c r="E554" s="20"/>
       <c r="F554" s="21"/>
-      <c r="G554" s="101"/>
+      <c r="G554" s="100"/>
       <c r="H554" s="19"/>
       <c r="I554" s="19"/>
       <c r="J554" s="20"/>
@@ -23362,7 +23372,7 @@
       <c r="D555" s="19"/>
       <c r="E555" s="20"/>
       <c r="F555" s="21"/>
-      <c r="G555" s="101"/>
+      <c r="G555" s="100"/>
       <c r="H555" s="19"/>
       <c r="I555" s="19"/>
       <c r="J555" s="20"/>
@@ -23395,7 +23405,7 @@
       <c r="D556" s="19"/>
       <c r="E556" s="20"/>
       <c r="F556" s="21"/>
-      <c r="G556" s="101"/>
+      <c r="G556" s="100"/>
       <c r="H556" s="19"/>
       <c r="I556" s="19"/>
       <c r="J556" s="20"/>
@@ -23428,7 +23438,7 @@
       <c r="D557" s="19"/>
       <c r="E557" s="20"/>
       <c r="F557" s="21"/>
-      <c r="G557" s="101"/>
+      <c r="G557" s="100"/>
       <c r="H557" s="19"/>
       <c r="I557" s="19"/>
       <c r="J557" s="20"/>
@@ -23461,7 +23471,7 @@
       <c r="D558" s="19"/>
       <c r="E558" s="20"/>
       <c r="F558" s="21"/>
-      <c r="G558" s="101"/>
+      <c r="G558" s="100"/>
       <c r="H558" s="19"/>
       <c r="I558" s="19"/>
       <c r="J558" s="20"/>
@@ -23494,7 +23504,7 @@
       <c r="D559" s="19"/>
       <c r="E559" s="20"/>
       <c r="F559" s="21"/>
-      <c r="G559" s="101"/>
+      <c r="G559" s="100"/>
       <c r="H559" s="19"/>
       <c r="I559" s="19"/>
       <c r="J559" s="20"/>
@@ -23527,7 +23537,7 @@
       <c r="D560" s="19"/>
       <c r="E560" s="20"/>
       <c r="F560" s="21"/>
-      <c r="G560" s="101"/>
+      <c r="G560" s="100"/>
       <c r="H560" s="19"/>
       <c r="I560" s="19"/>
       <c r="J560" s="20"/>
@@ -23560,7 +23570,7 @@
       <c r="D561" s="19"/>
       <c r="E561" s="20"/>
       <c r="F561" s="21"/>
-      <c r="G561" s="101"/>
+      <c r="G561" s="100"/>
       <c r="H561" s="19"/>
       <c r="I561" s="19"/>
       <c r="J561" s="20"/>
@@ -23593,7 +23603,7 @@
       <c r="D562" s="19"/>
       <c r="E562" s="20"/>
       <c r="F562" s="21"/>
-      <c r="G562" s="101"/>
+      <c r="G562" s="100"/>
       <c r="H562" s="19"/>
       <c r="I562" s="19"/>
       <c r="J562" s="20"/>
@@ -23626,7 +23636,7 @@
       <c r="D563" s="19"/>
       <c r="E563" s="20"/>
       <c r="F563" s="21"/>
-      <c r="G563" s="101"/>
+      <c r="G563" s="100"/>
       <c r="H563" s="19"/>
       <c r="I563" s="19"/>
       <c r="J563" s="20"/>
@@ -23659,7 +23669,7 @@
       <c r="D564" s="19"/>
       <c r="E564" s="20"/>
       <c r="F564" s="21"/>
-      <c r="G564" s="101"/>
+      <c r="G564" s="100"/>
       <c r="H564" s="19"/>
       <c r="I564" s="19"/>
       <c r="J564" s="20"/>
@@ -23692,7 +23702,7 @@
       <c r="D565" s="19"/>
       <c r="E565" s="20"/>
       <c r="F565" s="21"/>
-      <c r="G565" s="101"/>
+      <c r="G565" s="100"/>
       <c r="H565" s="19"/>
       <c r="I565" s="19"/>
       <c r="J565" s="20"/>
@@ -23725,7 +23735,7 @@
       <c r="D566" s="19"/>
       <c r="E566" s="20"/>
       <c r="F566" s="21"/>
-      <c r="G566" s="101"/>
+      <c r="G566" s="100"/>
       <c r="H566" s="19"/>
       <c r="I566" s="19"/>
       <c r="J566" s="20"/>
@@ -23758,7 +23768,7 @@
       <c r="D567" s="19"/>
       <c r="E567" s="20"/>
       <c r="F567" s="21"/>
-      <c r="G567" s="101"/>
+      <c r="G567" s="100"/>
       <c r="H567" s="19"/>
       <c r="I567" s="19"/>
       <c r="J567" s="20"/>
@@ -23791,7 +23801,7 @@
       <c r="D568" s="19"/>
       <c r="E568" s="20"/>
       <c r="F568" s="21"/>
-      <c r="G568" s="101"/>
+      <c r="G568" s="100"/>
       <c r="H568" s="19"/>
       <c r="I568" s="19"/>
       <c r="J568" s="20"/>
@@ -23824,7 +23834,7 @@
       <c r="D569" s="19"/>
       <c r="E569" s="20"/>
       <c r="F569" s="21"/>
-      <c r="G569" s="101"/>
+      <c r="G569" s="100"/>
       <c r="H569" s="19"/>
       <c r="I569" s="19"/>
       <c r="J569" s="20"/>
@@ -23857,7 +23867,7 @@
       <c r="D570" s="19"/>
       <c r="E570" s="20"/>
       <c r="F570" s="21"/>
-      <c r="G570" s="101"/>
+      <c r="G570" s="100"/>
       <c r="H570" s="19"/>
       <c r="I570" s="19"/>
       <c r="J570" s="20"/>
@@ -23890,7 +23900,7 @@
       <c r="D571" s="19"/>
       <c r="E571" s="20"/>
       <c r="F571" s="21"/>
-      <c r="G571" s="101"/>
+      <c r="G571" s="100"/>
       <c r="H571" s="19"/>
       <c r="I571" s="19"/>
       <c r="J571" s="20"/>
@@ -23923,7 +23933,7 @@
       <c r="D572" s="19"/>
       <c r="E572" s="20"/>
       <c r="F572" s="21"/>
-      <c r="G572" s="101"/>
+      <c r="G572" s="100"/>
       <c r="H572" s="19"/>
       <c r="I572" s="19"/>
       <c r="J572" s="20"/>
@@ -23956,7 +23966,7 @@
       <c r="D573" s="19"/>
       <c r="E573" s="20"/>
       <c r="F573" s="21"/>
-      <c r="G573" s="101"/>
+      <c r="G573" s="100"/>
       <c r="H573" s="19"/>
       <c r="I573" s="19"/>
       <c r="J573" s="20"/>
@@ -23989,7 +23999,7 @@
       <c r="D574" s="19"/>
       <c r="E574" s="20"/>
       <c r="F574" s="21"/>
-      <c r="G574" s="101"/>
+      <c r="G574" s="100"/>
       <c r="H574" s="19"/>
       <c r="I574" s="19"/>
       <c r="J574" s="20"/>
@@ -24022,7 +24032,7 @@
       <c r="D575" s="19"/>
       <c r="E575" s="20"/>
       <c r="F575" s="21"/>
-      <c r="G575" s="101"/>
+      <c r="G575" s="100"/>
       <c r="H575" s="19"/>
       <c r="I575" s="19"/>
       <c r="J575" s="20"/>
@@ -24055,7 +24065,7 @@
       <c r="D576" s="19"/>
       <c r="E576" s="20"/>
       <c r="F576" s="21"/>
-      <c r="G576" s="101"/>
+      <c r="G576" s="100"/>
       <c r="H576" s="19"/>
       <c r="I576" s="19"/>
       <c r="J576" s="20"/>
@@ -24088,7 +24098,7 @@
       <c r="D577" s="19"/>
       <c r="E577" s="20"/>
       <c r="F577" s="21"/>
-      <c r="G577" s="101"/>
+      <c r="G577" s="100"/>
       <c r="H577" s="19"/>
       <c r="I577" s="19"/>
       <c r="J577" s="20"/>
@@ -24121,7 +24131,7 @@
       <c r="D578" s="19"/>
       <c r="E578" s="20"/>
       <c r="F578" s="21"/>
-      <c r="G578" s="101"/>
+      <c r="G578" s="100"/>
       <c r="H578" s="19"/>
       <c r="I578" s="19"/>
       <c r="J578" s="20"/>
@@ -24154,7 +24164,7 @@
       <c r="D579" s="19"/>
       <c r="E579" s="20"/>
       <c r="F579" s="21"/>
-      <c r="G579" s="101"/>
+      <c r="G579" s="100"/>
       <c r="H579" s="19"/>
       <c r="I579" s="19"/>
       <c r="J579" s="20"/>
@@ -24187,7 +24197,7 @@
       <c r="D580" s="19"/>
       <c r="E580" s="20"/>
       <c r="F580" s="21"/>
-      <c r="G580" s="101"/>
+      <c r="G580" s="100"/>
       <c r="H580" s="19"/>
       <c r="I580" s="19"/>
       <c r="J580" s="20"/>
@@ -24220,7 +24230,7 @@
       <c r="D581" s="19"/>
       <c r="E581" s="20"/>
       <c r="F581" s="21"/>
-      <c r="G581" s="101"/>
+      <c r="G581" s="100"/>
       <c r="H581" s="19"/>
       <c r="I581" s="19"/>
       <c r="J581" s="20"/>
@@ -24253,7 +24263,7 @@
       <c r="D582" s="19"/>
       <c r="E582" s="20"/>
       <c r="F582" s="21"/>
-      <c r="G582" s="101"/>
+      <c r="G582" s="100"/>
       <c r="H582" s="19"/>
       <c r="I582" s="19"/>
       <c r="J582" s="20"/>
@@ -24286,7 +24296,7 @@
       <c r="D583" s="19"/>
       <c r="E583" s="20"/>
       <c r="F583" s="21"/>
-      <c r="G583" s="101"/>
+      <c r="G583" s="100"/>
       <c r="H583" s="19"/>
       <c r="I583" s="19"/>
       <c r="J583" s="20"/>
@@ -24319,7 +24329,7 @@
       <c r="D584" s="19"/>
       <c r="E584" s="20"/>
       <c r="F584" s="21"/>
-      <c r="G584" s="101"/>
+      <c r="G584" s="100"/>
       <c r="H584" s="19"/>
       <c r="I584" s="19"/>
       <c r="J584" s="20"/>
@@ -24352,7 +24362,7 @@
       <c r="D585" s="19"/>
       <c r="E585" s="20"/>
       <c r="F585" s="21"/>
-      <c r="G585" s="101"/>
+      <c r="G585" s="100"/>
       <c r="H585" s="19"/>
       <c r="I585" s="19"/>
       <c r="J585" s="20"/>
@@ -24385,7 +24395,7 @@
       <c r="D586" s="19"/>
       <c r="E586" s="20"/>
       <c r="F586" s="21"/>
-      <c r="G586" s="101"/>
+      <c r="G586" s="100"/>
       <c r="H586" s="19"/>
       <c r="I586" s="19"/>
       <c r="J586" s="20"/>
@@ -24418,7 +24428,7 @@
       <c r="D587" s="19"/>
       <c r="E587" s="20"/>
       <c r="F587" s="21"/>
-      <c r="G587" s="101"/>
+      <c r="G587" s="100"/>
       <c r="H587" s="19"/>
       <c r="I587" s="19"/>
       <c r="J587" s="20"/>
@@ -24451,7 +24461,7 @@
       <c r="D588" s="19"/>
       <c r="E588" s="20"/>
       <c r="F588" s="21"/>
-      <c r="G588" s="101"/>
+      <c r="G588" s="100"/>
       <c r="H588" s="19"/>
       <c r="I588" s="19"/>
       <c r="J588" s="20"/>
@@ -24484,7 +24494,7 @@
       <c r="D589" s="19"/>
       <c r="E589" s="20"/>
       <c r="F589" s="21"/>
-      <c r="G589" s="101"/>
+      <c r="G589" s="100"/>
       <c r="H589" s="19"/>
       <c r="I589" s="19"/>
       <c r="J589" s="20"/>
@@ -24517,7 +24527,7 @@
       <c r="D590" s="19"/>
       <c r="E590" s="20"/>
       <c r="F590" s="21"/>
-      <c r="G590" s="101"/>
+      <c r="G590" s="100"/>
       <c r="H590" s="19"/>
       <c r="I590" s="19"/>
       <c r="J590" s="20"/>
@@ -24550,7 +24560,7 @@
       <c r="D591" s="19"/>
       <c r="E591" s="20"/>
       <c r="F591" s="21"/>
-      <c r="G591" s="101"/>
+      <c r="G591" s="100"/>
       <c r="H591" s="19"/>
       <c r="I591" s="19"/>
       <c r="J591" s="20"/>
@@ -24583,7 +24593,7 @@
       <c r="D592" s="19"/>
       <c r="E592" s="20"/>
       <c r="F592" s="21"/>
-      <c r="G592" s="101"/>
+      <c r="G592" s="100"/>
       <c r="H592" s="19"/>
       <c r="I592" s="19"/>
       <c r="J592" s="20"/>
@@ -24616,7 +24626,7 @@
       <c r="D593" s="19"/>
       <c r="E593" s="20"/>
       <c r="F593" s="21"/>
-      <c r="G593" s="101"/>
+      <c r="G593" s="100"/>
       <c r="H593" s="19"/>
       <c r="I593" s="19"/>
       <c r="J593" s="20"/>
@@ -24649,7 +24659,7 @@
       <c r="D594" s="19"/>
       <c r="E594" s="20"/>
       <c r="F594" s="21"/>
-      <c r="G594" s="101"/>
+      <c r="G594" s="100"/>
       <c r="H594" s="19"/>
       <c r="I594" s="19"/>
       <c r="J594" s="20"/>
@@ -24682,7 +24692,7 @@
       <c r="D595" s="19"/>
       <c r="E595" s="20"/>
       <c r="F595" s="21"/>
-      <c r="G595" s="101"/>
+      <c r="G595" s="100"/>
       <c r="H595" s="19"/>
       <c r="I595" s="19"/>
       <c r="J595" s="20"/>
@@ -24715,7 +24725,7 @@
       <c r="D596" s="19"/>
       <c r="E596" s="20"/>
       <c r="F596" s="21"/>
-      <c r="G596" s="101"/>
+      <c r="G596" s="100"/>
       <c r="H596" s="19"/>
       <c r="I596" s="19"/>
       <c r="J596" s="20"/>
@@ -24748,7 +24758,7 @@
       <c r="D597" s="19"/>
       <c r="E597" s="20"/>
       <c r="F597" s="21"/>
-      <c r="G597" s="101"/>
+      <c r="G597" s="100"/>
       <c r="H597" s="19"/>
       <c r="I597" s="19"/>
       <c r="J597" s="20"/>
@@ -24781,7 +24791,7 @@
       <c r="D598" s="19"/>
       <c r="E598" s="20"/>
       <c r="F598" s="21"/>
-      <c r="G598" s="101"/>
+      <c r="G598" s="100"/>
       <c r="H598" s="19"/>
       <c r="I598" s="19"/>
       <c r="J598" s="20"/>
@@ -24814,7 +24824,7 @@
       <c r="D599" s="19"/>
       <c r="E599" s="20"/>
       <c r="F599" s="21"/>
-      <c r="G599" s="101"/>
+      <c r="G599" s="100"/>
       <c r="H599" s="19"/>
       <c r="I599" s="19"/>
       <c r="J599" s="20"/>
@@ -24847,7 +24857,7 @@
       <c r="D600" s="19"/>
       <c r="E600" s="20"/>
       <c r="F600" s="21"/>
-      <c r="G600" s="101"/>
+      <c r="G600" s="100"/>
       <c r="H600" s="19"/>
       <c r="I600" s="19"/>
       <c r="J600" s="20"/>
@@ -24880,7 +24890,7 @@
       <c r="D601" s="19"/>
       <c r="E601" s="20"/>
       <c r="F601" s="21"/>
-      <c r="G601" s="101"/>
+      <c r="G601" s="100"/>
       <c r="H601" s="19"/>
       <c r="I601" s="19"/>
       <c r="J601" s="20"/>
@@ -24913,7 +24923,7 @@
       <c r="D602" s="19"/>
       <c r="E602" s="20"/>
       <c r="F602" s="21"/>
-      <c r="G602" s="101"/>
+      <c r="G602" s="100"/>
       <c r="H602" s="19"/>
       <c r="I602" s="19"/>
       <c r="J602" s="20"/>
@@ -24946,7 +24956,7 @@
       <c r="D603" s="19"/>
       <c r="E603" s="20"/>
       <c r="F603" s="21"/>
-      <c r="G603" s="101"/>
+      <c r="G603" s="100"/>
       <c r="H603" s="19"/>
       <c r="I603" s="19"/>
       <c r="J603" s="20"/>
@@ -24979,7 +24989,7 @@
       <c r="D604" s="19"/>
       <c r="E604" s="20"/>
       <c r="F604" s="21"/>
-      <c r="G604" s="101"/>
+      <c r="G604" s="100"/>
       <c r="H604" s="19"/>
       <c r="I604" s="19"/>
       <c r="J604" s="20"/>
@@ -25012,7 +25022,7 @@
       <c r="D605" s="19"/>
       <c r="E605" s="20"/>
       <c r="F605" s="21"/>
-      <c r="G605" s="101"/>
+      <c r="G605" s="100"/>
       <c r="H605" s="19"/>
       <c r="I605" s="19"/>
       <c r="J605" s="20"/>
@@ -25045,7 +25055,7 @@
       <c r="D606" s="19"/>
       <c r="E606" s="20"/>
       <c r="F606" s="21"/>
-      <c r="G606" s="101"/>
+      <c r="G606" s="100"/>
       <c r="H606" s="19"/>
       <c r="I606" s="19"/>
       <c r="J606" s="20"/>
@@ -25078,7 +25088,7 @@
       <c r="D607" s="19"/>
       <c r="E607" s="20"/>
       <c r="F607" s="21"/>
-      <c r="G607" s="101"/>
+      <c r="G607" s="100"/>
       <c r="H607" s="19"/>
       <c r="I607" s="19"/>
       <c r="J607" s="20"/>
@@ -25111,7 +25121,7 @@
       <c r="D608" s="19"/>
       <c r="E608" s="20"/>
       <c r="F608" s="21"/>
-      <c r="G608" s="101"/>
+      <c r="G608" s="100"/>
       <c r="H608" s="19"/>
       <c r="I608" s="19"/>
       <c r="J608" s="20"/>
@@ -25144,7 +25154,7 @@
       <c r="D609" s="19"/>
       <c r="E609" s="20"/>
       <c r="F609" s="21"/>
-      <c r="G609" s="101"/>
+      <c r="G609" s="100"/>
       <c r="H609" s="19"/>
       <c r="I609" s="19"/>
       <c r="J609" s="20"/>
@@ -25177,7 +25187,7 @@
       <c r="D610" s="19"/>
       <c r="E610" s="20"/>
       <c r="F610" s="21"/>
-      <c r="G610" s="101"/>
+      <c r="G610" s="100"/>
       <c r="H610" s="19"/>
       <c r="I610" s="19"/>
       <c r="J610" s="20"/>
@@ -25210,7 +25220,7 @@
       <c r="D611" s="19"/>
       <c r="E611" s="20"/>
       <c r="F611" s="21"/>
-      <c r="G611" s="101"/>
+      <c r="G611" s="100"/>
       <c r="H611" s="19"/>
       <c r="I611" s="19"/>
       <c r="J611" s="20"/>
@@ -25243,7 +25253,7 @@
       <c r="D612" s="19"/>
       <c r="E612" s="20"/>
       <c r="F612" s="21"/>
-      <c r="G612" s="101"/>
+      <c r="G612" s="100"/>
       <c r="H612" s="19"/>
       <c r="I612" s="19"/>
       <c r="J612" s="20"/>
@@ -25276,7 +25286,7 @@
       <c r="D613" s="19"/>
       <c r="E613" s="20"/>
       <c r="F613" s="21"/>
-      <c r="G613" s="101"/>
+      <c r="G613" s="100"/>
       <c r="H613" s="19"/>
       <c r="I613" s="19"/>
       <c r="J613" s="20"/>
@@ -25309,7 +25319,7 @@
       <c r="D614" s="19"/>
       <c r="E614" s="20"/>
       <c r="F614" s="21"/>
-      <c r="G614" s="101"/>
+      <c r="G614" s="100"/>
       <c r="H614" s="19"/>
       <c r="I614" s="19"/>
       <c r="J614" s="20"/>
@@ -25342,7 +25352,7 @@
       <c r="D615" s="19"/>
       <c r="E615" s="20"/>
       <c r="F615" s="21"/>
-      <c r="G615" s="101"/>
+      <c r="G615" s="100"/>
       <c r="H615" s="19"/>
       <c r="I615" s="19"/>
       <c r="J615" s="20"/>
@@ -25375,7 +25385,7 @@
       <c r="D616" s="19"/>
       <c r="E616" s="20"/>
       <c r="F616" s="21"/>
-      <c r="G616" s="101"/>
+      <c r="G616" s="100"/>
       <c r="H616" s="19"/>
       <c r="I616" s="19"/>
       <c r="J616" s="20"/>
@@ -25408,7 +25418,7 @@
       <c r="D617" s="19"/>
       <c r="E617" s="20"/>
       <c r="F617" s="21"/>
-      <c r="G617" s="101"/>
+      <c r="G617" s="100"/>
       <c r="H617" s="19"/>
       <c r="I617" s="19"/>
       <c r="J617" s="20"/>
@@ -25441,7 +25451,7 @@
       <c r="D618" s="19"/>
       <c r="E618" s="20"/>
       <c r="F618" s="21"/>
-      <c r="G618" s="101"/>
+      <c r="G618" s="100"/>
       <c r="H618" s="19"/>
       <c r="I618" s="19"/>
       <c r="J618" s="20"/>
@@ -25474,7 +25484,7 @@
       <c r="D619" s="19"/>
       <c r="E619" s="20"/>
       <c r="F619" s="21"/>
-      <c r="G619" s="101"/>
+      <c r="G619" s="100"/>
       <c r="H619" s="19"/>
       <c r="I619" s="19"/>
       <c r="J619" s="20"/>
@@ -25507,7 +25517,7 @@
       <c r="D620" s="19"/>
       <c r="E620" s="20"/>
       <c r="F620" s="21"/>
-      <c r="G620" s="101"/>
+      <c r="G620" s="100"/>
       <c r="H620" s="19"/>
       <c r="I620" s="19"/>
       <c r="J620" s="20"/>
@@ -25540,7 +25550,7 @@
       <c r="D621" s="19"/>
       <c r="E621" s="20"/>
       <c r="F621" s="21"/>
-      <c r="G621" s="101"/>
+      <c r="G621" s="100"/>
       <c r="H621" s="19"/>
       <c r="I621" s="19"/>
       <c r="J621" s="20"/>
@@ -25573,7 +25583,7 @@
       <c r="D622" s="19"/>
       <c r="E622" s="20"/>
       <c r="F622" s="21"/>
-      <c r="G622" s="101"/>
+      <c r="G622" s="100"/>
       <c r="H622" s="19"/>
       <c r="I622" s="19"/>
       <c r="J622" s="20"/>
@@ -25606,7 +25616,7 @@
       <c r="D623" s="19"/>
       <c r="E623" s="20"/>
       <c r="F623" s="21"/>
-      <c r="G623" s="101"/>
+      <c r="G623" s="100"/>
       <c r="H623" s="19"/>
       <c r="I623" s="19"/>
       <c r="J623" s="20"/>
@@ -25639,7 +25649,7 @@
       <c r="D624" s="19"/>
       <c r="E624" s="20"/>
       <c r="F624" s="21"/>
-      <c r="G624" s="101"/>
+      <c r="G624" s="100"/>
       <c r="H624" s="19"/>
       <c r="I624" s="19"/>
       <c r="J624" s="20"/>
@@ -25672,7 +25682,7 @@
       <c r="D625" s="19"/>
       <c r="E625" s="20"/>
       <c r="F625" s="21"/>
-      <c r="G625" s="101"/>
+      <c r="G625" s="100"/>
       <c r="H625" s="19"/>
       <c r="I625" s="19"/>
       <c r="J625" s="20"/>
@@ -25705,7 +25715,7 @@
       <c r="D626" s="19"/>
       <c r="E626" s="20"/>
       <c r="F626" s="21"/>
-      <c r="G626" s="101"/>
+      <c r="G626" s="100"/>
       <c r="H626" s="19"/>
       <c r="I626" s="19"/>
       <c r="J626" s="20"/>
@@ -25738,7 +25748,7 @@
       <c r="D627" s="19"/>
       <c r="E627" s="20"/>
       <c r="F627" s="21"/>
-      <c r="G627" s="101"/>
+      <c r="G627" s="100"/>
       <c r="H627" s="19"/>
       <c r="I627" s="19"/>
       <c r="J627" s="20"/>
@@ -25771,7 +25781,7 @@
       <c r="D628" s="19"/>
       <c r="E628" s="20"/>
       <c r="F628" s="21"/>
-      <c r="G628" s="101"/>
+      <c r="G628" s="100"/>
       <c r="H628" s="19"/>
       <c r="I628" s="19"/>
       <c r="J628" s="20"/>
@@ -25804,7 +25814,7 @@
       <c r="D629" s="19"/>
       <c r="E629" s="20"/>
       <c r="F629" s="21"/>
-      <c r="G629" s="101"/>
+      <c r="G629" s="100"/>
       <c r="H629" s="19"/>
       <c r="I629" s="19"/>
       <c r="J629" s="20"/>
@@ -25837,7 +25847,7 @@
       <c r="D630" s="19"/>
       <c r="E630" s="20"/>
       <c r="F630" s="21"/>
-      <c r="G630" s="101"/>
+      <c r="G630" s="100"/>
       <c r="H630" s="19"/>
       <c r="I630" s="19"/>
       <c r="J630" s="20"/>
@@ -25870,7 +25880,7 @@
       <c r="D631" s="19"/>
       <c r="E631" s="20"/>
       <c r="F631" s="21"/>
-      <c r="G631" s="101"/>
+      <c r="G631" s="100"/>
       <c r="H631" s="19"/>
       <c r="I631" s="19"/>
       <c r="J631" s="20"/>
@@ -25903,7 +25913,7 @@
       <c r="D632" s="19"/>
       <c r="E632" s="20"/>
       <c r="F632" s="21"/>
-      <c r="G632" s="101"/>
+      <c r="G632" s="100"/>
       <c r="H632" s="19"/>
       <c r="I632" s="19"/>
       <c r="J632" s="20"/>
@@ -25936,7 +25946,7 @@
       <c r="D633" s="19"/>
       <c r="E633" s="20"/>
       <c r="F633" s="21"/>
-      <c r="G633" s="101"/>
+      <c r="G633" s="100"/>
       <c r="H633" s="19"/>
       <c r="I633" s="19"/>
       <c r="J633" s="20"/>
@@ -25969,7 +25979,7 @@
       <c r="D634" s="19"/>
       <c r="E634" s="20"/>
       <c r="F634" s="21"/>
-      <c r="G634" s="101"/>
+      <c r="G634" s="100"/>
       <c r="H634" s="19"/>
       <c r="I634" s="19"/>
       <c r="J634" s="20"/>
@@ -26002,7 +26012,7 @@
       <c r="D635" s="19"/>
       <c r="E635" s="20"/>
       <c r="F635" s="21"/>
-      <c r="G635" s="101"/>
+      <c r="G635" s="100"/>
       <c r="H635" s="19"/>
       <c r="I635" s="19"/>
       <c r="J635" s="20"/>
@@ -26035,7 +26045,7 @@
       <c r="D636" s="19"/>
       <c r="E636" s="20"/>
       <c r="F636" s="21"/>
-      <c r="G636" s="101"/>
+      <c r="G636" s="100"/>
       <c r="H636" s="19"/>
       <c r="I636" s="19"/>
       <c r="J636" s="20"/>
@@ -26068,7 +26078,7 @@
       <c r="D637" s="19"/>
       <c r="E637" s="20"/>
       <c r="F637" s="21"/>
-      <c r="G637" s="101"/>
+      <c r="G637" s="100"/>
       <c r="H637" s="19"/>
       <c r="I637" s="19"/>
       <c r="J637" s="20"/>
@@ -26101,7 +26111,7 @@
       <c r="D638" s="19"/>
       <c r="E638" s="20"/>
       <c r="F638" s="21"/>
-      <c r="G638" s="101"/>
+      <c r="G638" s="100"/>
       <c r="H638" s="19"/>
       <c r="I638" s="19"/>
       <c r="J638" s="20"/>
@@ -26134,7 +26144,7 @@
       <c r="D639" s="19"/>
       <c r="E639" s="20"/>
       <c r="F639" s="21"/>
-      <c r="G639" s="101"/>
+      <c r="G639" s="100"/>
       <c r="H639" s="19"/>
       <c r="I639" s="19"/>
       <c r="J639" s="20"/>
@@ -26167,7 +26177,7 @@
       <c r="D640" s="19"/>
       <c r="E640" s="20"/>
       <c r="F640" s="21"/>
-      <c r="G640" s="101"/>
+      <c r="G640" s="100"/>
       <c r="H640" s="19"/>
       <c r="I640" s="19"/>
       <c r="J640" s="20"/>
@@ -26200,7 +26210,7 @@
       <c r="D641" s="19"/>
       <c r="E641" s="20"/>
       <c r="F641" s="21"/>
-      <c r="G641" s="101"/>
+      <c r="G641" s="100"/>
       <c r="H641" s="19"/>
       <c r="I641" s="19"/>
       <c r="J641" s="20"/>
@@ -26233,7 +26243,7 @@
       <c r="D642" s="19"/>
       <c r="E642" s="20"/>
       <c r="F642" s="21"/>
-      <c r="G642" s="101"/>
+      <c r="G642" s="100"/>
       <c r="H642" s="19"/>
       <c r="I642" s="19"/>
       <c r="J642" s="20"/>
@@ -26266,7 +26276,7 @@
       <c r="D643" s="19"/>
       <c r="E643" s="20"/>
       <c r="F643" s="21"/>
-      <c r="G643" s="101"/>
+      <c r="G643" s="100"/>
       <c r="H643" s="19"/>
       <c r="I643" s="19"/>
       <c r="J643" s="20"/>
@@ -26299,7 +26309,7 @@
       <c r="D644" s="19"/>
       <c r="E644" s="20"/>
       <c r="F644" s="21"/>
-      <c r="G644" s="101"/>
+      <c r="G644" s="100"/>
       <c r="H644" s="19"/>
       <c r="I644" s="19"/>
       <c r="J644" s="20"/>
@@ -26332,7 +26342,7 @@
       <c r="D645" s="19"/>
       <c r="E645" s="20"/>
       <c r="F645" s="21"/>
-      <c r="G645" s="101"/>
+      <c r="G645" s="100"/>
       <c r="H645" s="19"/>
       <c r="I645" s="19"/>
       <c r="J645" s="20"/>
@@ -26365,7 +26375,7 @@
       <c r="D646" s="19"/>
       <c r="E646" s="20"/>
       <c r="F646" s="21"/>
-      <c r="G646" s="101"/>
+      <c r="G646" s="100"/>
       <c r="H646" s="19"/>
       <c r="I646" s="19"/>
       <c r="J646" s="20"/>
@@ -26398,7 +26408,7 @@
       <c r="D647" s="19"/>
       <c r="E647" s="20"/>
       <c r="F647" s="21"/>
-      <c r="G647" s="101"/>
+      <c r="G647" s="100"/>
       <c r="H647" s="19"/>
       <c r="I647" s="19"/>
       <c r="J647" s="20"/>
@@ -26431,7 +26441,7 @@
       <c r="D648" s="19"/>
       <c r="E648" s="20"/>
       <c r="F648" s="21"/>
-      <c r="G648" s="101"/>
+      <c r="G648" s="100"/>
       <c r="H648" s="19"/>
       <c r="I648" s="19"/>
       <c r="J648" s="20"/>
@@ -26464,7 +26474,7 @@
       <c r="D649" s="19"/>
       <c r="E649" s="20"/>
       <c r="F649" s="21"/>
-      <c r="G649" s="101"/>
+      <c r="G649" s="100"/>
       <c r="H649" s="19"/>
       <c r="I649" s="19"/>
       <c r="J649" s="20"/>
@@ -26497,7 +26507,7 @@
       <c r="D650" s="19"/>
       <c r="E650" s="20"/>
       <c r="F650" s="21"/>
-      <c r="G650" s="101"/>
+      <c r="G650" s="100"/>
       <c r="H650" s="19"/>
       <c r="I650" s="19"/>
       <c r="J650" s="20"/>
@@ -26530,7 +26540,7 @@
       <c r="D651" s="19"/>
       <c r="E651" s="20"/>
       <c r="F651" s="21"/>
-      <c r="G651" s="101"/>
+      <c r="G651" s="100"/>
       <c r="H651" s="19"/>
       <c r="I651" s="19"/>
       <c r="J651" s="20"/>
@@ -26563,7 +26573,7 @@
       <c r="D652" s="19"/>
       <c r="E652" s="20"/>
       <c r="F652" s="21"/>
-      <c r="G652" s="101"/>
+      <c r="G652" s="100"/>
       <c r="H652" s="19"/>
       <c r="I652" s="19"/>
       <c r="J652" s="20"/>
@@ -26596,7 +26606,7 @@
       <c r="D653" s="19"/>
       <c r="E653" s="20"/>
       <c r="F653" s="21"/>
-      <c r="G653" s="101"/>
+      <c r="G653" s="100"/>
       <c r="H653" s="19"/>
       <c r="I653" s="19"/>
       <c r="J653" s="20"/>
@@ -26629,7 +26639,7 @@
       <c r="D654" s="19"/>
       <c r="E654" s="20"/>
       <c r="F654" s="21"/>
-      <c r="G654" s="101"/>
+      <c r="G654" s="100"/>
       <c r="H654" s="19"/>
       <c r="I654" s="19"/>
       <c r="J654" s="20"/>
@@ -26662,7 +26672,7 @@
       <c r="D655" s="19"/>
       <c r="E655" s="20"/>
       <c r="F655" s="21"/>
-      <c r="G655" s="101"/>
+      <c r="G655" s="100"/>
       <c r="H655" s="19"/>
       <c r="I655" s="19"/>
       <c r="J655" s="20"/>
@@ -26695,7 +26705,7 @@
       <c r="D656" s="19"/>
       <c r="E656" s="20"/>
       <c r="F656" s="21"/>
-      <c r="G656" s="101"/>
+      <c r="G656" s="100"/>
       <c r="H656" s="19"/>
       <c r="I656" s="19"/>
       <c r="J656" s="20"/>
@@ -26728,7 +26738,7 @@
       <c r="D657" s="19"/>
       <c r="E657" s="20"/>
       <c r="F657" s="21"/>
-      <c r="G657" s="101"/>
+      <c r="G657" s="100"/>
       <c r="H657" s="19"/>
       <c r="I657" s="19"/>
       <c r="J657" s="20"/>
@@ -26761,7 +26771,7 @@
       <c r="D658" s="19"/>
       <c r="E658" s="20"/>
       <c r="F658" s="21"/>
-      <c r="G658" s="101"/>
+      <c r="G658" s="100"/>
       <c r="H658" s="19"/>
       <c r="I658" s="19"/>
       <c r="J658" s="20"/>
@@ -26794,7 +26804,7 @@
       <c r="D659" s="19"/>
       <c r="E659" s="20"/>
       <c r="F659" s="21"/>
-      <c r="G659" s="101"/>
+      <c r="G659" s="100"/>
       <c r="H659" s="19"/>
       <c r="I659" s="19"/>
       <c r="J659" s="20"/>
@@ -26827,7 +26837,7 @@
       <c r="D660" s="19"/>
       <c r="E660" s="20"/>
       <c r="F660" s="21"/>
-      <c r="G660" s="101"/>
+      <c r="G660" s="100"/>
       <c r="H660" s="19"/>
       <c r="I660" s="19"/>
       <c r="J660" s="20"/>
@@ -26860,7 +26870,7 @@
       <c r="D661" s="19"/>
       <c r="E661" s="20"/>
       <c r="F661" s="21"/>
-      <c r="G661" s="101"/>
+      <c r="G661" s="100"/>
       <c r="H661" s="19"/>
       <c r="I661" s="19"/>
       <c r="J661" s="20"/>
@@ -26893,7 +26903,7 @@
       <c r="D662" s="19"/>
       <c r="E662" s="20"/>
       <c r="F662" s="21"/>
-      <c r="G662" s="101"/>
+      <c r="G662" s="100"/>
       <c r="H662" s="19"/>
       <c r="I662" s="19"/>
       <c r="J662" s="20"/>
@@ -26926,7 +26936,7 @@
       <c r="D663" s="19"/>
       <c r="E663" s="20"/>
       <c r="F663" s="21"/>
-      <c r="G663" s="101"/>
+      <c r="G663" s="100"/>
       <c r="H663" s="19"/>
       <c r="I663" s="19"/>
       <c r="J663" s="20"/>
@@ -26959,7 +26969,7 @@
       <c r="D664" s="19"/>
       <c r="E664" s="20"/>
       <c r="F664" s="21"/>
-      <c r="G664" s="101"/>
+      <c r="G664" s="100"/>
       <c r="H664" s="19"/>
       <c r="I664" s="19"/>
       <c r="J664" s="20"/>
@@ -26992,7 +27002,7 @@
       <c r="D665" s="19"/>
       <c r="E665" s="20"/>
       <c r="F665" s="21"/>
-      <c r="G665" s="101"/>
+      <c r="G665" s="100"/>
       <c r="H665" s="19"/>
       <c r="I665" s="19"/>
       <c r="J665" s="20"/>
@@ -27025,7 +27035,7 @@
       <c r="D666" s="19"/>
       <c r="E666" s="20"/>
       <c r="F666" s="21"/>
-      <c r="G666" s="101"/>
+      <c r="G666" s="100"/>
       <c r="H666" s="19"/>
       <c r="I666" s="19"/>
       <c r="J666" s="20"/>
@@ -27058,7 +27068,7 @@
       <c r="D667" s="19"/>
       <c r="E667" s="20"/>
       <c r="F667" s="21"/>
-      <c r="G667" s="101"/>
+      <c r="G667" s="100"/>
       <c r="H667" s="19"/>
       <c r="I667" s="19"/>
       <c r="J667" s="20"/>
@@ -27091,7 +27101,7 @@
       <c r="D668" s="19"/>
       <c r="E668" s="20"/>
       <c r="F668" s="21"/>
-      <c r="G668" s="101"/>
+      <c r="G668" s="100"/>
       <c r="H668" s="19"/>
       <c r="I668" s="19"/>
       <c r="J668" s="20"/>
@@ -27124,7 +27134,7 @@
       <c r="D669" s="19"/>
       <c r="E669" s="20"/>
       <c r="F669" s="21"/>
-      <c r="G669" s="101"/>
+      <c r="G669" s="100"/>
       <c r="H669" s="19"/>
       <c r="I669" s="19"/>
       <c r="J669" s="20"/>
@@ -27157,7 +27167,7 @@
       <c r="D670" s="19"/>
       <c r="E670" s="20"/>
       <c r="F670" s="21"/>
-      <c r="G670" s="101"/>
+      <c r="G670" s="100"/>
       <c r="H670" s="19"/>
       <c r="I670" s="19"/>
       <c r="J670" s="20"/>
@@ -27190,7 +27200,7 @@
       <c r="D671" s="19"/>
       <c r="E671" s="20"/>
       <c r="F671" s="21"/>
-      <c r="G671" s="101"/>
+      <c r="G671" s="100"/>
       <c r="H671" s="19"/>
       <c r="I671" s="19"/>
       <c r="J671" s="20"/>
@@ -27223,7 +27233,7 @@
       <c r="D672" s="19"/>
       <c r="E672" s="20"/>
       <c r="F672" s="21"/>
-      <c r="G672" s="101"/>
+      <c r="G672" s="100"/>
       <c r="H672" s="19"/>
       <c r="I672" s="19"/>
       <c r="J672" s="20"/>
@@ -27256,7 +27266,7 @@
       <c r="D673" s="19"/>
       <c r="E673" s="20"/>
       <c r="F673" s="21"/>
-      <c r="G673" s="101"/>
+      <c r="G673" s="100"/>
       <c r="H673" s="19"/>
       <c r="I673" s="19"/>
       <c r="J673" s="20"/>
@@ -27289,7 +27299,7 @@
       <c r="D674" s="19"/>
       <c r="E674" s="20"/>
       <c r="F674" s="21"/>
-      <c r="G674" s="101"/>
+      <c r="G674" s="100"/>
       <c r="H674" s="19"/>
       <c r="I674" s="19"/>
       <c r="J674" s="20"/>
@@ -27322,7 +27332,7 @@
       <c r="D675" s="19"/>
       <c r="E675" s="20"/>
       <c r="F675" s="21"/>
-      <c r="G675" s="101"/>
+      <c r="G675" s="100"/>
       <c r="H675" s="19"/>
       <c r="I675" s="19"/>
       <c r="J675" s="20"/>
@@ -27355,7 +27365,7 @@
       <c r="D676" s="19"/>
       <c r="E676" s="20"/>
       <c r="F676" s="21"/>
-      <c r="G676" s="101"/>
+      <c r="G676" s="100"/>
       <c r="H676" s="19"/>
       <c r="I676" s="19"/>
       <c r="J676" s="20"/>
@@ -27388,7 +27398,7 @@
       <c r="D677" s="19"/>
       <c r="E677" s="20"/>
       <c r="F677" s="21"/>
-      <c r="G677" s="101"/>
+      <c r="G677" s="100"/>
       <c r="H677" s="19"/>
       <c r="I677" s="19"/>
       <c r="J677" s="20"/>
@@ -27421,7 +27431,7 @@
       <c r="D678" s="19"/>
       <c r="E678" s="20"/>
       <c r="F678" s="21"/>
-      <c r="G678" s="101"/>
+      <c r="G678" s="100"/>
       <c r="H678" s="19"/>
       <c r="I678" s="19"/>
       <c r="J678" s="20"/>
@@ -27454,7 +27464,7 @@
       <c r="D679" s="19"/>
       <c r="E679" s="20"/>
       <c r="F679" s="21"/>
-      <c r="G679" s="101"/>
+      <c r="G679" s="100"/>
       <c r="H679" s="19"/>
       <c r="I679" s="19"/>
       <c r="J679" s="20"/>
@@ -27487,7 +27497,7 @@
       <c r="D680" s="19"/>
       <c r="E680" s="20"/>
       <c r="F680" s="21"/>
-      <c r="G680" s="101"/>
+      <c r="G680" s="100"/>
       <c r="H680" s="19"/>
       <c r="I680" s="19"/>
       <c r="J680" s="20"/>
@@ -27520,7 +27530,7 @@
       <c r="D681" s="19"/>
       <c r="E681" s="20"/>
       <c r="F681" s="21"/>
-      <c r="G681" s="101"/>
+      <c r="G681" s="100"/>
       <c r="H681" s="19"/>
       <c r="I681" s="19"/>
       <c r="J681" s="20"/>
@@ -27553,7 +27563,7 @@
       <c r="D682" s="19"/>
       <c r="E682" s="20"/>
       <c r="F682" s="21"/>
-      <c r="G682" s="101"/>
+      <c r="G682" s="100"/>
       <c r="H682" s="19"/>
       <c r="I682" s="19"/>
       <c r="J682" s="20"/>
@@ -27586,7 +27596,7 @@
       <c r="D683" s="19"/>
       <c r="E683" s="20"/>
       <c r="F683" s="21"/>
-      <c r="G683" s="101"/>
+      <c r="G683" s="100"/>
       <c r="H683" s="19"/>
       <c r="I683" s="19"/>
       <c r="J683" s="20"/>
@@ -27619,7 +27629,7 @@
       <c r="D684" s="19"/>
       <c r="E684" s="20"/>
       <c r="F684" s="21"/>
-      <c r="G684" s="101"/>
+      <c r="G684" s="100"/>
       <c r="H684" s="19"/>
       <c r="I684" s="19"/>
       <c r="J684" s="20"/>
@@ -27652,7 +27662,7 @@
       <c r="D685" s="19"/>
       <c r="E685" s="20"/>
       <c r="F685" s="21"/>
-      <c r="G685" s="101"/>
+      <c r="G685" s="100"/>
       <c r="H685" s="19"/>
       <c r="I685" s="19"/>
       <c r="J685" s="20"/>
@@ -27685,7 +27695,7 @@
       <c r="D686" s="19"/>
       <c r="E686" s="20"/>
       <c r="F686" s="21"/>
-      <c r="G686" s="101"/>
+      <c r="G686" s="100"/>
       <c r="H686" s="19"/>
       <c r="I686" s="19"/>
       <c r="J686" s="20"/>
@@ -27718,7 +27728,7 @@
       <c r="D687" s="19"/>
       <c r="E687" s="20"/>
       <c r="F687" s="21"/>
-      <c r="G687" s="101"/>
+      <c r="G687" s="100"/>
       <c r="H687" s="19"/>
       <c r="I687" s="19"/>
       <c r="J687" s="20"/>
@@ -27751,7 +27761,7 @@
       <c r="D688" s="19"/>
       <c r="E688" s="20"/>
       <c r="F688" s="21"/>
-      <c r="G688" s="101"/>
+      <c r="G688" s="100"/>
       <c r="H688" s="19"/>
       <c r="I688" s="19"/>
       <c r="J688" s="20"/>
@@ -27784,7 +27794,7 @@
       <c r="D689" s="19"/>
       <c r="E689" s="20"/>
       <c r="F689" s="21"/>
-      <c r="G689" s="101"/>
+      <c r="G689" s="100"/>
       <c r="H689" s="19"/>
       <c r="I689" s="19"/>
       <c r="J689" s="20"/>
@@ -27817,7 +27827,7 @@
       <c r="D690" s="19"/>
       <c r="E690" s="20"/>
       <c r="F690" s="21"/>
-      <c r="G690" s="101"/>
+      <c r="G690" s="100"/>
       <c r="H690" s="19"/>
       <c r="I690" s="19"/>
       <c r="J690" s="20"/>
@@ -27850,7 +27860,7 @@
       <c r="D691" s="19"/>
       <c r="E691" s="20"/>
       <c r="F691" s="21"/>
-      <c r="G691" s="101"/>
+      <c r="G691" s="100"/>
       <c r="H691" s="19"/>
       <c r="I691" s="19"/>
       <c r="J691" s="20"/>
@@ -27883,7 +27893,7 @@
       <c r="D692" s="19"/>
       <c r="E692" s="20"/>
       <c r="F692" s="21"/>
-      <c r="G692" s="101"/>
+      <c r="G692" s="100"/>
       <c r="H692" s="19"/>
       <c r="I692" s="19"/>
       <c r="J692" s="20"/>
@@ -27916,7 +27926,7 @@
       <c r="D693" s="19"/>
       <c r="E693" s="20"/>
       <c r="F693" s="21"/>
-      <c r="G693" s="101"/>
+      <c r="G693" s="100"/>
       <c r="H693" s="19"/>
       <c r="I693" s="19"/>
       <c r="J693" s="20"/>
@@ -27949,7 +27959,7 @@
       <c r="D694" s="19"/>
       <c r="E694" s="20"/>
       <c r="F694" s="21"/>
-      <c r="G694" s="101"/>
+      <c r="G694" s="100"/>
       <c r="H694" s="19"/>
       <c r="I694" s="19"/>
       <c r="J694" s="20"/>
@@ -27982,7 +27992,7 @@
       <c r="D695" s="19"/>
       <c r="E695" s="20"/>
       <c r="F695" s="21"/>
-      <c r="G695" s="101"/>
+      <c r="G695" s="100"/>
       <c r="H695" s="19"/>
       <c r="I695" s="19"/>
       <c r="J695" s="20"/>
@@ -28015,7 +28025,7 @@
       <c r="D696" s="19"/>
       <c r="E696" s="20"/>
       <c r="F696" s="21"/>
-      <c r="G696" s="101"/>
+      <c r="G696" s="100"/>
       <c r="H696" s="19"/>
       <c r="I696" s="19"/>
       <c r="J696" s="20"/>
@@ -28048,7 +28058,7 @@
       <c r="D697" s="19"/>
       <c r="E697" s="20"/>
       <c r="F697" s="21"/>
-      <c r="G697" s="101"/>
+      <c r="G697" s="100"/>
       <c r="H697" s="19"/>
       <c r="I697" s="19"/>
       <c r="J697" s="20"/>
@@ -28081,7 +28091,7 @@
       <c r="D698" s="19"/>
       <c r="E698" s="20"/>
       <c r="F698" s="21"/>
-      <c r="G698" s="101"/>
+      <c r="G698" s="100"/>
       <c r="H698" s="19"/>
       <c r="I698" s="19"/>
       <c r="J698" s="20"/>
@@ -28114,7 +28124,7 @@
       <c r="D699" s="19"/>
       <c r="E699" s="20"/>
       <c r="F699" s="21"/>
-      <c r="G699" s="101"/>
+      <c r="G699" s="100"/>
       <c r="H699" s="19"/>
       <c r="I699" s="19"/>
       <c r="J699" s="20"/>
@@ -28147,7 +28157,7 @@
       <c r="D700" s="19"/>
       <c r="E700" s="20"/>
       <c r="F700" s="21"/>
-      <c r="G700" s="101"/>
+      <c r="G700" s="100"/>
       <c r="H700" s="19"/>
       <c r="I700" s="19"/>
       <c r="J700" s="20"/>
@@ -28180,7 +28190,7 @@
       <c r="D701" s="19"/>
       <c r="E701" s="20"/>
       <c r="F701" s="21"/>
-      <c r="G701" s="101"/>
+      <c r="G701" s="100"/>
       <c r="H701" s="19"/>
       <c r="I701" s="19"/>
       <c r="J701" s="20"/>
@@ -28213,7 +28223,7 @@
       <c r="D702" s="19"/>
       <c r="E702" s="20"/>
       <c r="F702" s="21"/>
-      <c r="G702" s="101"/>
+      <c r="G702" s="100"/>
       <c r="H702" s="19"/>
       <c r="I702" s="19"/>
       <c r="J702" s="20"/>
@@ -28246,7 +28256,7 @@
       <c r="D703" s="19"/>
       <c r="E703" s="20"/>
       <c r="F703" s="21"/>
-      <c r="G703" s="101"/>
+      <c r="G703" s="100"/>
       <c r="H703" s="19"/>
       <c r="I703" s="19"/>
       <c r="J703" s="20"/>
@@ -28279,7 +28289,7 @@
       <c r="D704" s="19"/>
       <c r="E704" s="20"/>
       <c r="F704" s="21"/>
-      <c r="G704" s="101"/>
+      <c r="G704" s="100"/>
       <c r="H704" s="19"/>
       <c r="I704" s="19"/>
       <c r="J704" s="20"/>
@@ -28312,7 +28322,7 @@
       <c r="D705" s="19"/>
       <c r="E705" s="20"/>
       <c r="F705" s="21"/>
-      <c r="G705" s="101"/>
+      <c r="G705" s="100"/>
       <c r="H705" s="19"/>
       <c r="I705" s="19"/>
       <c r="J705" s="20"/>
@@ -28345,7 +28355,7 @@
       <c r="D706" s="19"/>
       <c r="E706" s="20"/>
       <c r="F706" s="21"/>
-      <c r="G706" s="101"/>
+      <c r="G706" s="100"/>
       <c r="H706" s="19"/>
       <c r="I706" s="19"/>
       <c r="J706" s="20"/>
@@ -28378,7 +28388,7 @@
       <c r="D707" s="19"/>
       <c r="E707" s="20"/>
       <c r="F707" s="21"/>
-      <c r="G707" s="101"/>
+      <c r="G707" s="100"/>
       <c r="H707" s="19"/>
       <c r="I707" s="19"/>
       <c r="J707" s="20"/>
@@ -28411,7 +28421,7 @@
       <c r="D708" s="19"/>
       <c r="E708" s="20"/>
       <c r="F708" s="21"/>
-      <c r="G708" s="101"/>
+      <c r="G708" s="100"/>
       <c r="H708" s="19"/>
       <c r="I708" s="19"/>
       <c r="J708" s="20"/>
@@ -28444,7 +28454,7 @@
       <c r="D709" s="19"/>
       <c r="E709" s="20"/>
       <c r="F709" s="21"/>
-      <c r="G709" s="101"/>
+      <c r="G709" s="100"/>
       <c r="H709" s="19"/>
       <c r="I709" s="19"/>
       <c r="J709" s="20"/>
@@ -28477,7 +28487,7 @@
       <c r="D710" s="19"/>
       <c r="E710" s="20"/>
       <c r="F710" s="21"/>
-      <c r="G710" s="101"/>
+      <c r="G710" s="100"/>
       <c r="H710" s="19"/>
       <c r="I710" s="19"/>
       <c r="J710" s="20"/>
@@ -28510,7 +28520,7 @@
       <c r="D711" s="19"/>
       <c r="E711" s="20"/>
       <c r="F711" s="21"/>
-      <c r="G711" s="101"/>
+      <c r="G711" s="100"/>
       <c r="H711" s="19"/>
       <c r="I711" s="19"/>
       <c r="J711" s="20"/>
@@ -28543,7 +28553,7 @@
       <c r="D712" s="19"/>
       <c r="E712" s="20"/>
       <c r="F712" s="21"/>
-      <c r="G712" s="101"/>
+      <c r="G712" s="100"/>
       <c r="H712" s="19"/>
       <c r="I712" s="19"/>
       <c r="J712" s="20"/>
@@ -28576,7 +28586,7 @@
       <c r="D713" s="19"/>
       <c r="E713" s="20"/>
       <c r="F713" s="21"/>
-      <c r="G713" s="101"/>
+      <c r="G713" s="100"/>
       <c r="H713" s="19"/>
       <c r="I713" s="19"/>
       <c r="J713" s="20"/>
@@ -28609,7 +28619,7 @@
       <c r="D714" s="19"/>
       <c r="E714" s="20"/>
       <c r="F714" s="21"/>
-      <c r="G714" s="101"/>
+      <c r="G714" s="100"/>
       <c r="H714" s="19"/>
       <c r="I714" s="19"/>
       <c r="J714" s="20"/>
@@ -28642,7 +28652,7 @@
       <c r="D715" s="19"/>
       <c r="E715" s="20"/>
       <c r="F715" s="21"/>
-      <c r="G715" s="101"/>
+      <c r="G715" s="100"/>
       <c r="H715" s="19"/>
       <c r="I715" s="19"/>
       <c r="J715" s="20"/>
@@ -28675,7 +28685,7 @@
       <c r="D716" s="19"/>
       <c r="E716" s="20"/>
       <c r="F716" s="21"/>
-      <c r="G716" s="101"/>
+      <c r="G716" s="100"/>
       <c r="H716" s="19"/>
       <c r="I716" s="19"/>
       <c r="J716" s="20"/>
@@ -28708,7 +28718,7 @@
       <c r="D717" s="19"/>
       <c r="E717" s="20"/>
       <c r="F717" s="21"/>
-      <c r="G717" s="101"/>
+      <c r="G717" s="100"/>
       <c r="H717" s="19"/>
       <c r="I717" s="19"/>
       <c r="J717" s="20"/>
@@ -28741,7 +28751,7 @@
       <c r="D718" s="19"/>
       <c r="E718" s="20"/>
       <c r="F718" s="21"/>
-      <c r="G718" s="101"/>
+      <c r="G718" s="100"/>
       <c r="H718" s="19"/>
       <c r="I718" s="19"/>
       <c r="J718" s="20"/>
@@ -28774,7 +28784,7 @@
       <c r="D719" s="19"/>
       <c r="E719" s="20"/>
       <c r="F719" s="21"/>
-      <c r="G719" s="101"/>
+      <c r="G719" s="100"/>
       <c r="H719" s="19"/>
       <c r="I719" s="19"/>
       <c r="J719" s="20"/>
@@ -28807,7 +28817,7 @@
       <c r="D720" s="19"/>
       <c r="E720" s="20"/>
       <c r="F720" s="21"/>
-      <c r="G720" s="101"/>
+      <c r="G720" s="100"/>
       <c r="H720" s="19"/>
       <c r="I720" s="19"/>
       <c r="J720" s="20"/>
@@ -28840,7 +28850,7 @@
       <c r="D721" s="19"/>
       <c r="E721" s="20"/>
       <c r="F721" s="21"/>
-      <c r="G721" s="101"/>
+      <c r="G721" s="100"/>
       <c r="H721" s="19"/>
       <c r="I721" s="19"/>
       <c r="J721" s="20"/>
@@ -28873,7 +28883,7 @@
       <c r="D722" s="19"/>
       <c r="E722" s="20"/>
       <c r="F722" s="21"/>
-      <c r="G722" s="101"/>
+      <c r="G722" s="100"/>
       <c r="H722" s="19"/>
       <c r="I722" s="19"/>
       <c r="J722" s="20"/>
@@ -28906,7 +28916,7 @@
       <c r="D723" s="19"/>
       <c r="E723" s="20"/>
       <c r="F723" s="21"/>
-      <c r="G723" s="101"/>
+      <c r="G723" s="100"/>
       <c r="H723" s="19"/>
       <c r="I723" s="19"/>
       <c r="J723" s="20"/>
@@ -28939,7 +28949,7 @@
       <c r="D724" s="19"/>
       <c r="E724" s="20"/>
       <c r="F724" s="21"/>
-      <c r="G724" s="101"/>
+      <c r="G724" s="100"/>
       <c r="H724" s="19"/>
       <c r="I724" s="19"/>
       <c r="J724" s="20"/>
@@ -28972,7 +28982,7 @@
       <c r="D725" s="19"/>
       <c r="E725" s="20"/>
       <c r="F725" s="21"/>
-      <c r="G725" s="101"/>
+      <c r="G725" s="100"/>
       <c r="H725" s="19"/>
       <c r="I725" s="19"/>
       <c r="J725" s="20"/>
@@ -29005,7 +29015,7 @@
       <c r="D726" s="19"/>
       <c r="E726" s="20"/>
       <c r="F726" s="21"/>
-      <c r="G726" s="101"/>
+      <c r="G726" s="100"/>
       <c r="H726" s="19"/>
       <c r="I726" s="19"/>
       <c r="J726" s="20"/>
@@ -29038,7 +29048,7 @@
       <c r="D727" s="19"/>
       <c r="E727" s="20"/>
       <c r="F727" s="21"/>
-      <c r="G727" s="101"/>
+      <c r="G727" s="100"/>
       <c r="H727" s="19"/>
       <c r="I727" s="19"/>
       <c r="J727" s="20"/>
@@ -29071,7 +29081,7 @@
       <c r="D728" s="19"/>
       <c r="E728" s="20"/>
       <c r="F728" s="21"/>
-      <c r="G728" s="101"/>
+      <c r="G728" s="100"/>
       <c r="H728" s="19"/>
       <c r="I728" s="19"/>
       <c r="J728" s="20"/>
@@ -29104,7 +29114,7 @@
       <c r="D729" s="19"/>
       <c r="E729" s="20"/>
       <c r="F729" s="21"/>
-      <c r="G729" s="101"/>
+      <c r="G729" s="100"/>
       <c r="H729" s="19"/>
       <c r="I729" s="19"/>
       <c r="J729" s="20"/>
@@ -29137,7 +29147,7 @@
       <c r="D730" s="19"/>
       <c r="E730" s="20"/>
       <c r="F730" s="21"/>
-      <c r="G730" s="101"/>
+      <c r="G730" s="100"/>
       <c r="H730" s="19"/>
       <c r="I730" s="19"/>
       <c r="J730" s="20"/>
@@ -29170,7 +29180,7 @@
       <c r="D731" s="19"/>
       <c r="E731" s="20"/>
       <c r="F731" s="21"/>
-      <c r="G731" s="101"/>
+      <c r="G731" s="100"/>
       <c r="H731" s="19"/>
       <c r="I731" s="19"/>
       <c r="J731" s="20"/>
@@ -29203,7 +29213,7 @@
       <c r="D732" s="19"/>
       <c r="E732" s="20"/>
       <c r="F732" s="21"/>
-      <c r="G732" s="101"/>
+      <c r="G732" s="100"/>
       <c r="H732" s="19"/>
       <c r="I732" s="19"/>
       <c r="J732" s="20"/>
@@ -29236,7 +29246,7 @@
       <c r="D733" s="19"/>
       <c r="E733" s="20"/>
       <c r="F733" s="21"/>
-      <c r="G733" s="101"/>
+      <c r="G733" s="100"/>
       <c r="H733" s="19"/>
       <c r="I733" s="19"/>
       <c r="J733" s="20"/>
@@ -29269,7 +29279,7 @@
       <c r="D734" s="19"/>
       <c r="E734" s="20"/>
       <c r="F734" s="21"/>
-      <c r="G734" s="101"/>
+      <c r="G734" s="100"/>
       <c r="H734" s="19"/>
       <c r="I734" s="19"/>
       <c r="J734" s="20"/>
@@ -29302,7 +29312,7 @@
       <c r="D735" s="19"/>
       <c r="E735" s="20"/>
       <c r="F735" s="21"/>
-      <c r="G735" s="101"/>
+      <c r="G735" s="100"/>
       <c r="H735" s="19"/>
       <c r="I735" s="19"/>
       <c r="J735" s="20"/>
@@ -29335,7 +29345,7 @@
       <c r="D736" s="19"/>
       <c r="E736" s="20"/>
       <c r="F736" s="21"/>
-      <c r="G736" s="101"/>
+      <c r="G736" s="100"/>
       <c r="H736" s="19"/>
       <c r="I736" s="19"/>
       <c r="J736" s="20"/>
@@ -29368,7 +29378,7 @@
       <c r="D737" s="19"/>
       <c r="E737" s="20"/>
       <c r="F737" s="21"/>
-      <c r="G737" s="101"/>
+      <c r="G737" s="100"/>
       <c r="H737" s="19"/>
       <c r="I737" s="19"/>
       <c r="J737" s="20"/>
@@ -29401,7 +29411,7 @@
       <c r="D738" s="19"/>
       <c r="E738" s="20"/>
       <c r="F738" s="21"/>
-      <c r="G738" s="101"/>
+      <c r="G738" s="100"/>
       <c r="H738" s="19"/>
       <c r="I738" s="19"/>
       <c r="J738" s="20"/>
@@ -29434,7 +29444,7 @@
       <c r="D739" s="19"/>
       <c r="E739" s="20"/>
       <c r="F739" s="21"/>
-      <c r="G739" s="101"/>
+      <c r="G739" s="100"/>
       <c r="H739" s="19"/>
       <c r="I739" s="19"/>
       <c r="J739" s="20"/>
@@ -29467,7 +29477,7 @@
       <c r="D740" s="19"/>
       <c r="E740" s="20"/>
       <c r="F740" s="21"/>
-      <c r="G740" s="101"/>
+      <c r="G740" s="100"/>
       <c r="H740" s="19"/>
       <c r="I740" s="19"/>
       <c r="J740" s="20"/>
@@ -29500,7 +29510,7 @@
       <c r="D741" s="19"/>
       <c r="E741" s="20"/>
       <c r="F741" s="21"/>
-      <c r="G741" s="101"/>
+      <c r="G741" s="100"/>
       <c r="H741" s="19"/>
       <c r="I741" s="19"/>
       <c r="J741" s="20"/>
@@ -29533,7 +29543,7 @@
       <c r="D742" s="19"/>
       <c r="E742" s="20"/>
       <c r="F742" s="21"/>
-      <c r="G742" s="101"/>
+      <c r="G742" s="100"/>
       <c r="H742" s="19"/>
       <c r="I742" s="19"/>
       <c r="J742" s="20"/>
@@ -29566,7 +29576,7 @@
       <c r="D743" s="19"/>
       <c r="E743" s="20"/>
       <c r="F743" s="21"/>
-      <c r="G743" s="101"/>
+      <c r="G743" s="100"/>
       <c r="H743" s="19"/>
       <c r="I743" s="19"/>
       <c r="J743" s="20"/>
@@ -29599,7 +29609,7 @@
       <c r="D744" s="19"/>
       <c r="E744" s="20"/>
       <c r="F744" s="21"/>
-      <c r="G744" s="101"/>
+      <c r="G744" s="100"/>
       <c r="H744" s="19"/>
       <c r="I744" s="19"/>
       <c r="J744" s="20"/>
@@ -29632,7 +29642,7 @@
       <c r="D745" s="19"/>
       <c r="E745" s="20"/>
       <c r="F745" s="21"/>
-      <c r="G745" s="101"/>
+      <c r="G745" s="100"/>
       <c r="H745" s="19"/>
       <c r="I745" s="19"/>
       <c r="J745" s="20"/>
@@ -29665,7 +29675,7 @@
       <c r="D746" s="19"/>
       <c r="E746" s="20"/>
       <c r="F746" s="21"/>
-      <c r="G746" s="101"/>
+      <c r="G746" s="100"/>
       <c r="H746" s="19"/>
       <c r="I746" s="19"/>
       <c r="J746" s="20"/>
@@ -29698,7 +29708,7 @@
       <c r="D747" s="19"/>
       <c r="E747" s="20"/>
       <c r="F747" s="21"/>
-      <c r="G747" s="101"/>
+      <c r="G747" s="100"/>
       <c r="H747" s="19"/>
       <c r="I747" s="19"/>
       <c r="J747" s="20"/>
@@ -29731,7 +29741,7 @@
       <c r="D748" s="19"/>
       <c r="E748" s="20"/>
       <c r="F748" s="21"/>
-      <c r="G748" s="101"/>
+      <c r="G748" s="100"/>
       <c r="H748" s="19"/>
       <c r="I748" s="19"/>
       <c r="J748" s="20"/>
@@ -29764,7 +29774,7 @@
       <c r="D749" s="19"/>
       <c r="E749" s="20"/>
       <c r="F749" s="21"/>
-      <c r="G749" s="101"/>
+      <c r="G749" s="100"/>
       <c r="H749" s="19"/>
       <c r="I749" s="19"/>
       <c r="J749" s="20"/>
@@ -29797,7 +29807,7 @@
       <c r="D750" s="19"/>
       <c r="E750" s="20"/>
       <c r="F750" s="21"/>
-      <c r="G750" s="101"/>
+      <c r="G750" s="100"/>
       <c r="H750" s="19"/>
       <c r="I750" s="19"/>
       <c r="J750" s="20"/>
@@ -29830,7 +29840,7 @@
       <c r="D751" s="19"/>
       <c r="E751" s="20"/>
       <c r="F751" s="21"/>
-      <c r="G751" s="101"/>
+      <c r="G751" s="100"/>
       <c r="H751" s="19"/>
       <c r="I751" s="19"/>
       <c r="J751" s="20"/>
@@ -29863,7 +29873,7 @@
       <c r="D752" s="19"/>
       <c r="E752" s="20"/>
       <c r="F752" s="21"/>
-      <c r="G752" s="101"/>
+      <c r="G752" s="100"/>
       <c r="H752" s="19"/>
       <c r="I752" s="19"/>
       <c r="J752" s="20"/>
@@ -29896,7 +29906,7 @@
       <c r="D753" s="19"/>
       <c r="E753" s="20"/>
       <c r="F753" s="21"/>
-      <c r="G753" s="101"/>
+      <c r="G753" s="100"/>
       <c r="H753" s="19"/>
       <c r="I753" s="19"/>
       <c r="J753" s="20"/>
@@ -29929,7 +29939,7 @@
       <c r="D754" s="19"/>
       <c r="E754" s="20"/>
       <c r="F754" s="21"/>
-      <c r="G754" s="101"/>
+      <c r="G754" s="100"/>
       <c r="H754" s="19"/>
       <c r="I754" s="19"/>
       <c r="J754" s="20"/>
@@ -29962,7 +29972,7 @@
       <c r="D755" s="19"/>
       <c r="E755" s="20"/>
       <c r="F755" s="21"/>
-      <c r="G755" s="101"/>
+      <c r="G755" s="100"/>
       <c r="H755" s="19"/>
       <c r="I755" s="19"/>
       <c r="J755" s="20"/>
@@ -29995,7 +30005,7 @@
       <c r="D756" s="19"/>
       <c r="E756" s="20"/>
       <c r="F756" s="21"/>
-      <c r="G756" s="101"/>
+      <c r="G756" s="100"/>
       <c r="H756" s="19"/>
       <c r="I756" s="19"/>
       <c r="J756" s="20"/>
@@ -30028,7 +30038,7 @@
       <c r="D757" s="19"/>
       <c r="E757" s="20"/>
       <c r="F757" s="21"/>
-      <c r="G757" s="101"/>
+      <c r="G757" s="100"/>
       <c r="H757" s="19"/>
       <c r="I757" s="19"/>
       <c r="J757" s="20"/>
@@ -30061,7 +30071,7 @@
       <c r="D758" s="19"/>
       <c r="E758" s="20"/>
       <c r="F758" s="21"/>
-      <c r="G758" s="101"/>
+      <c r="G758" s="100"/>
       <c r="H758" s="19"/>
       <c r="I758" s="19"/>
       <c r="J758" s="20"/>
@@ -30094,7 +30104,7 @@
       <c r="D759" s="19"/>
       <c r="E759" s="20"/>
       <c r="F759" s="21"/>
-      <c r="G759" s="101"/>
+      <c r="G759" s="100"/>
       <c r="H759" s="19"/>
       <c r="I759" s="19"/>
       <c r="J759" s="20"/>
@@ -30127,7 +30137,7 @@
       <c r="D760" s="19"/>
       <c r="E760" s="20"/>
       <c r="F760" s="21"/>
-      <c r="G760" s="101"/>
+      <c r="G760" s="100"/>
       <c r="H760" s="19"/>
       <c r="I760" s="19"/>
       <c r="J760" s="20"/>
@@ -30160,7 +30170,7 @@
       <c r="D761" s="19"/>
       <c r="E761" s="20"/>
       <c r="F761" s="21"/>
-      <c r="G761" s="101"/>
+      <c r="G761" s="100"/>
       <c r="H761" s="19"/>
       <c r="I761" s="19"/>
       <c r="J761" s="20"/>
@@ -30193,7 +30203,7 @@
       <c r="D762" s="19"/>
       <c r="E762" s="20"/>
       <c r="F762" s="21"/>
-      <c r="G762" s="101"/>
+      <c r="G762" s="100"/>
       <c r="H762" s="19"/>
       <c r="I762" s="19"/>
       <c r="J762" s="20"/>
@@ -30226,7 +30236,7 @@
       <c r="D763" s="19"/>
       <c r="E763" s="20"/>
       <c r="F763" s="21"/>
-      <c r="G763" s="101"/>
+      <c r="G763" s="100"/>
       <c r="H763" s="19"/>
       <c r="I763" s="19"/>
       <c r="J763" s="20"/>
@@ -30259,7 +30269,7 @@
       <c r="D764" s="19"/>
       <c r="E764" s="20"/>
       <c r="F764" s="21"/>
-      <c r="G764" s="101"/>
+      <c r="G764" s="100"/>
       <c r="H764" s="19"/>
       <c r="I764" s="19"/>
       <c r="J764" s="20"/>
@@ -30292,7 +30302,7 @@
       <c r="D765" s="19"/>
       <c r="E765" s="20"/>
       <c r="F765" s="21"/>
-      <c r="G765" s="101"/>
+      <c r="G765" s="100"/>
       <c r="H765" s="19"/>
       <c r="I765" s="19"/>
       <c r="J765" s="20"/>
@@ -30325,7 +30335,7 @@
       <c r="D766" s="19"/>
       <c r="E766" s="20"/>
       <c r="F766" s="21"/>
-      <c r="G766" s="101"/>
+      <c r="G766" s="100"/>
       <c r="H766" s="19"/>
       <c r="I766" s="19"/>
       <c r="J766" s="20"/>
@@ -30358,7 +30368,7 @@
       <c r="D767" s="19"/>
       <c r="E767" s="20"/>
       <c r="F767" s="21"/>
-      <c r="G767" s="101"/>
+      <c r="G767" s="100"/>
       <c r="H767" s="19"/>
       <c r="I767" s="19"/>
       <c r="J767" s="20"/>
@@ -30391,7 +30401,7 @@
       <c r="D768" s="19"/>
       <c r="E768" s="20"/>
       <c r="F768" s="21"/>
-      <c r="G768" s="101"/>
+      <c r="G768" s="100"/>
       <c r="H768" s="19"/>
       <c r="I768" s="19"/>
       <c r="J768" s="20"/>
@@ -30424,7 +30434,7 @@
       <c r="D769" s="19"/>
       <c r="E769" s="20"/>
       <c r="F769" s="21"/>
-      <c r="G769" s="101"/>
+      <c r="G769" s="100"/>
       <c r="H769" s="19"/>
       <c r="I769" s="19"/>
       <c r="J769" s="20"/>
@@ -30457,7 +30467,7 @@
       <c r="D770" s="19"/>
       <c r="E770" s="20"/>
       <c r="F770" s="21"/>
-      <c r="G770" s="101"/>
+      <c r="G770" s="100"/>
       <c r="H770" s="19"/>
       <c r="I770" s="19"/>
       <c r="J770" s="20"/>
@@ -30490,7 +30500,7 @@
       <c r="D771" s="19"/>
       <c r="E771" s="20"/>
       <c r="F771" s="21"/>
-      <c r="G771" s="101"/>
+      <c r="G771" s="100"/>
       <c r="H771" s="19"/>
       <c r="I771" s="19"/>
       <c r="J771" s="20"/>
@@ -30523,7 +30533,7 @@
       <c r="D772" s="19"/>
       <c r="E772" s="20"/>
       <c r="F772" s="21"/>
-      <c r="G772" s="101"/>
+      <c r="G772" s="100"/>
       <c r="H772" s="19"/>
       <c r="I772" s="19"/>
       <c r="J772" s="20"/>
@@ -30556,7 +30566,7 @@
       <c r="D773" s="19"/>
       <c r="E773" s="20"/>
       <c r="F773" s="21"/>
-      <c r="G773" s="101"/>
+      <c r="G773" s="100"/>
       <c r="H773" s="19"/>
       <c r="I773" s="19"/>
       <c r="J773" s="20"/>
@@ -30589,7 +30599,7 @@
       <c r="D774" s="19"/>
       <c r="E774" s="20"/>
       <c r="F774" s="21"/>
-      <c r="G774" s="101"/>
+      <c r="G774" s="100"/>
       <c r="H774" s="19"/>
       <c r="I774" s="19"/>
       <c r="J774" s="20"/>
@@ -30622,7 +30632,7 @@
       <c r="D775" s="19"/>
       <c r="E775" s="20"/>
       <c r="F775" s="21"/>
-      <c r="G775" s="101"/>
+      <c r="G775" s="100"/>
       <c r="H775" s="19"/>
       <c r="I775" s="19"/>
       <c r="J775" s="20"/>
@@ -30655,7 +30665,7 @@
       <c r="D776" s="19"/>
       <c r="E776" s="20"/>
       <c r="F776" s="21"/>
-      <c r="G776" s="101"/>
+      <c r="G776" s="100"/>
       <c r="H776" s="19"/>
       <c r="I776" s="19"/>
       <c r="J776" s="20"/>
@@ -30688,7 +30698,7 @@
       <c r="D777" s="19"/>
       <c r="E777" s="20"/>
       <c r="F777" s="21"/>
-      <c r="G777" s="101"/>
+      <c r="G777" s="100"/>
       <c r="H777" s="19"/>
       <c r="I777" s="19"/>
       <c r="J777" s="20"/>
@@ -30721,7 +30731,7 @@
       <c r="D778" s="19"/>
       <c r="E778" s="20"/>
       <c r="F778" s="21"/>
-      <c r="G778" s="101"/>
+      <c r="G778" s="100"/>
       <c r="H778" s="19"/>
       <c r="I778" s="19"/>
       <c r="J778" s="20"/>
@@ -30754,7 +30764,7 @@
       <c r="D779" s="19"/>
       <c r="E779" s="20"/>
       <c r="F779" s="21"/>
-      <c r="G779" s="101"/>
+      <c r="G779" s="100"/>
       <c r="H779" s="19"/>
       <c r="I779" s="19"/>
       <c r="J779" s="20"/>
@@ -30787,7 +30797,7 @@
       <c r="D780" s="19"/>
       <c r="E780" s="20"/>
       <c r="F780" s="21"/>
-      <c r="G780" s="101"/>
+      <c r="G780" s="100"/>
       <c r="H780" s="19"/>
       <c r="I780" s="19"/>
       <c r="J780" s="20"/>
@@ -30820,7 +30830,7 @@
       <c r="D781" s="19"/>
       <c r="E781" s="20"/>
       <c r="F781" s="21"/>
-      <c r="G781" s="101"/>
+      <c r="G781" s="100"/>
       <c r="H781" s="19"/>
       <c r="I781" s="19"/>
       <c r="J781" s="20"/>
@@ -30853,7 +30863,7 @@
       <c r="D782" s="19"/>
       <c r="E782" s="20"/>
       <c r="F782" s="21"/>
-      <c r="G782" s="101"/>
+      <c r="G782" s="100"/>
       <c r="H782" s="19"/>
       <c r="I782" s="19"/>
       <c r="J782" s="20"/>
@@ -30886,7 +30896,7 @@
       <c r="D783" s="19"/>
       <c r="E783" s="20"/>
       <c r="F783" s="21"/>
-      <c r="G783" s="101"/>
+      <c r="G783" s="100"/>
       <c r="H783" s="19"/>
       <c r="I783" s="19"/>
       <c r="J783" s="20"/>
@@ -30919,7 +30929,7 @@
       <c r="D784" s="19"/>
       <c r="E784" s="20"/>
       <c r="F784" s="21"/>
-      <c r="G784" s="101"/>
+      <c r="G784" s="100"/>
       <c r="H784" s="19"/>
       <c r="I784" s="19"/>
       <c r="J784" s="20"/>
@@ -30952,7 +30962,7 @@
       <c r="D785" s="19"/>
       <c r="E785" s="20"/>
       <c r="F785" s="21"/>
-      <c r="G785" s="101"/>
+      <c r="G785" s="100"/>
       <c r="H785" s="19"/>
       <c r="I785" s="19"/>
       <c r="J785" s="20"/>
@@ -30985,7 +30995,7 @@
       <c r="D786" s="19"/>
       <c r="E786" s="20"/>
       <c r="F786" s="21"/>
-      <c r="G786" s="101"/>
+      <c r="G786" s="100"/>
       <c r="H786" s="19"/>
       <c r="I786" s="19"/>
       <c r="J786" s="20"/>
@@ -31018,7 +31028,7 @@
       <c r="D787" s="19"/>
       <c r="E787" s="20"/>
       <c r="F787" s="21"/>
-      <c r="G787" s="101"/>
+      <c r="G787" s="100"/>
       <c r="H787" s="19"/>
       <c r="I787" s="19"/>
       <c r="J787" s="20"/>
@@ -31051,7 +31061,7 @@
       <c r="D788" s="19"/>
       <c r="E788" s="20"/>
       <c r="F788" s="21"/>
-      <c r="G788" s="101"/>
+      <c r="G788" s="100"/>
       <c r="H788" s="19"/>
       <c r="I788" s="19"/>
       <c r="J788" s="20"/>
@@ -31084,7 +31094,7 @@
       <c r="D789" s="19"/>
       <c r="E789" s="20"/>
       <c r="F789" s="21"/>
-      <c r="G789" s="101"/>
+      <c r="G789" s="100"/>
       <c r="H789" s="19"/>
       <c r="I789" s="19"/>
       <c r="J789" s="20"/>
@@ -31117,7 +31127,7 @@
       <c r="D790" s="19"/>
       <c r="E790" s="20"/>
       <c r="F790" s="21"/>
-      <c r="G790" s="101"/>
+      <c r="G790" s="100"/>
       <c r="H790" s="19"/>
       <c r="I790" s="19"/>
       <c r="J790" s="20"/>
@@ -31150,7 +31160,7 @@
       <c r="D791" s="19"/>
       <c r="E791" s="20"/>
       <c r="F791" s="21"/>
-      <c r="G791" s="101"/>
+      <c r="G791" s="100"/>
       <c r="H791" s="19"/>
       <c r="I791" s="19"/>
       <c r="J791" s="20"/>
@@ -31183,7 +31193,7 @@
       <c r="D792" s="19"/>
       <c r="E792" s="20"/>
       <c r="F792" s="21"/>
-      <c r="G792" s="101"/>
+      <c r="G792" s="100"/>
       <c r="H792" s="19"/>
       <c r="I792" s="19"/>
       <c r="J792" s="20"/>
@@ -31216,7 +31226,7 @@
       <c r="D793" s="19"/>
       <c r="E793" s="20"/>
       <c r="F793" s="21"/>
-      <c r="G793" s="101"/>
+      <c r="G793" s="100"/>
       <c r="H793" s="19"/>
       <c r="I793" s="19"/>
       <c r="J793" s="20"/>
@@ -31249,7 +31259,7 @@
       <c r="D794" s="19"/>
       <c r="E794" s="20"/>
       <c r="F794" s="21"/>
-      <c r="G794" s="101"/>
+      <c r="G794" s="100"/>
       <c r="H794" s="19"/>
       <c r="I794" s="19"/>
       <c r="J794" s="20"/>
@@ -31282,7 +31292,7 @@
       <c r="D795" s="19"/>
       <c r="E795" s="20"/>
       <c r="F795" s="21"/>
-      <c r="G795" s="101"/>
+      <c r="G795" s="100"/>
       <c r="H795" s="19"/>
       <c r="I795" s="19"/>
       <c r="J795" s="20"/>
@@ -31315,7 +31325,7 @@
       <c r="D796" s="19"/>
       <c r="E796" s="20"/>
       <c r="F796" s="21"/>
-      <c r="G796" s="101"/>
+      <c r="G796" s="100"/>
       <c r="H796" s="19"/>
       <c r="I796" s="19"/>
       <c r="J796" s="20"/>
@@ -31348,7 +31358,7 @@
       <c r="D797" s="19"/>
       <c r="E797" s="20"/>
       <c r="F797" s="21"/>
-      <c r="G797" s="101"/>
+      <c r="G797" s="100"/>
       <c r="H797" s="19"/>
       <c r="I797" s="19"/>
       <c r="J797" s="20"/>
@@ -31381,7 +31391,7 @@
       <c r="D798" s="19"/>
       <c r="E798" s="20"/>
       <c r="F798" s="21"/>
-      <c r="G798" s="101"/>
+      <c r="G798" s="100"/>
       <c r="H798" s="19"/>
       <c r="I798" s="19"/>
       <c r="J798" s="20"/>
@@ -31414,7 +31424,7 @@
       <c r="D799" s="19"/>
       <c r="E799" s="20"/>
       <c r="F799" s="21"/>
-      <c r="G799" s="101"/>
+      <c r="G799" s="100"/>
       <c r="H799" s="19"/>
       <c r="I799" s="19"/>
       <c r="J799" s="20"/>
@@ -31447,7 +31457,7 @@
       <c r="D800" s="19"/>
       <c r="E800" s="20"/>
       <c r="F800" s="21"/>
-      <c r="G800" s="101"/>
+      <c r="G800" s="100"/>
       <c r="H800" s="19"/>
       <c r="I800" s="19"/>
       <c r="J800" s="20"/>
@@ -31480,7 +31490,7 @@
       <c r="D801" s="19"/>
       <c r="E801" s="20"/>
       <c r="F801" s="21"/>
-      <c r="G801" s="101"/>
+      <c r="G801" s="100"/>
       <c r="H801" s="19"/>
       <c r="I801" s="19"/>
       <c r="J801" s="20"/>
@@ -31513,7 +31523,7 @@
       <c r="D802" s="19"/>
       <c r="E802" s="20"/>
       <c r="F802" s="21"/>
-      <c r="G802" s="101"/>
+      <c r="G802" s="100"/>
       <c r="H802" s="19"/>
       <c r="I802" s="19"/>
       <c r="J802" s="20"/>
@@ -31546,7 +31556,7 @@
       <c r="D803" s="19"/>
       <c r="E803" s="20"/>
       <c r="F803" s="21"/>
-      <c r="G803" s="101"/>
+      <c r="G803" s="100"/>
       <c r="H803" s="19"/>
       <c r="I803" s="19"/>
       <c r="J803" s="20"/>
@@ -31579,7 +31589,7 @@
       <c r="D804" s="19"/>
       <c r="E804" s="20"/>
       <c r="F804" s="21"/>
-      <c r="G804" s="101"/>
+      <c r="G804" s="100"/>
       <c r="H804" s="19"/>
       <c r="I804" s="19"/>
       <c r="J804" s="20"/>
@@ -31612,7 +31622,7 @@
       <c r="D805" s="19"/>
       <c r="E805" s="20"/>
       <c r="F805" s="21"/>
-      <c r="G805" s="101"/>
+      <c r="G805" s="100"/>
       <c r="H805" s="19"/>
       <c r="I805" s="19"/>
       <c r="J805" s="20"/>
@@ -31645,7 +31655,7 @@
       <c r="D806" s="19"/>
       <c r="E806" s="20"/>
       <c r="F806" s="21"/>
-      <c r="G806" s="101"/>
+      <c r="G806" s="100"/>
       <c r="H806" s="19"/>
       <c r="I806" s="19"/>
       <c r="J806" s="20"/>
@@ -31678,7 +31688,7 @@
       <c r="D807" s="19"/>
       <c r="E807" s="20"/>
       <c r="F807" s="21"/>
-      <c r="G807" s="101"/>
+      <c r="G807" s="100"/>
       <c r="H807" s="19"/>
       <c r="I807" s="19"/>
       <c r="J807" s="20"/>
@@ -31711,7 +31721,7 @@
       <c r="D808" s="19"/>
       <c r="E808" s="20"/>
       <c r="F808" s="21"/>
-      <c r="G808" s="101"/>
+      <c r="G808" s="100"/>
       <c r="H808" s="19"/>
       <c r="I808" s="19"/>
       <c r="J808" s="20"/>
@@ -31744,7 +31754,7 @@
       <c r="D809" s="19"/>
       <c r="E809" s="20"/>
       <c r="F809" s="21"/>
-      <c r="G809" s="101"/>
+      <c r="G809" s="100"/>
       <c r="H809" s="19"/>
       <c r="I809" s="19"/>
       <c r="J809" s="20"/>
@@ -31777,7 +31787,7 @@
       <c r="D810" s="19"/>
       <c r="E810" s="20"/>
       <c r="F810" s="21"/>
-      <c r="G810" s="101"/>
+      <c r="G810" s="100"/>
       <c r="H810" s="19"/>
       <c r="I810" s="19"/>
       <c r="J810" s="20"/>
@@ -31810,7 +31820,7 @@
       <c r="D811" s="19"/>
       <c r="E811" s="20"/>
       <c r="F811" s="21"/>
-      <c r="G811" s="101"/>
+      <c r="G811" s="100"/>
       <c r="H811" s="19"/>
       <c r="I811" s="19"/>
       <c r="J811" s="20"/>
@@ -31843,7 +31853,7 @@
       <c r="D812" s="19"/>
       <c r="E812" s="20"/>
       <c r="F812" s="21"/>
-      <c r="G812" s="101"/>
+      <c r="G812" s="100"/>
       <c r="H812" s="19"/>
       <c r="I812" s="19"/>
       <c r="J812" s="20"/>
@@ -31876,7 +31886,7 @@
       <c r="D813" s="19"/>
       <c r="E813" s="20"/>
       <c r="F813" s="21"/>
-      <c r="G813" s="101"/>
+      <c r="G813" s="100"/>
       <c r="H813" s="19"/>
       <c r="I813" s="19"/>
       <c r="J813" s="20"/>
@@ -31909,7 +31919,7 @@
       <c r="D814" s="19"/>
       <c r="E814" s="20"/>
       <c r="F814" s="21"/>
-      <c r="G814" s="101"/>
+      <c r="G814" s="100"/>
       <c r="H814" s="19"/>
       <c r="I814" s="19"/>
       <c r="J814" s="20"/>
@@ -31942,7 +31952,7 @@
       <c r="D815" s="19"/>
       <c r="E815" s="20"/>
       <c r="F815" s="21"/>
-      <c r="G815" s="101"/>
+      <c r="G815" s="100"/>
       <c r="H815" s="19"/>
       <c r="I815" s="19"/>
       <c r="J815" s="20"/>
@@ -31975,7 +31985,7 @@
       <c r="D816" s="19"/>
       <c r="E816" s="20"/>
       <c r="F816" s="21"/>
-      <c r="G816" s="101"/>
+      <c r="G816" s="100"/>
       <c r="H816" s="19"/>
       <c r="I816" s="19"/>
       <c r="J816" s="20"/>
@@ -32008,7 +32018,7 @@
       <c r="D817" s="19"/>
       <c r="E817" s="20"/>
       <c r="F817" s="21"/>
-      <c r="G817" s="101"/>
+      <c r="G817" s="100"/>
       <c r="H817" s="19"/>
       <c r="I817" s="19"/>
       <c r="J817" s="20"/>
@@ -32041,7 +32051,7 @@
       <c r="D818" s="19"/>
       <c r="E818" s="20"/>
       <c r="F818" s="21"/>
-      <c r="G818" s="101"/>
+      <c r="G818" s="100"/>
       <c r="H818" s="19"/>
       <c r="I818" s="19"/>
       <c r="J818" s="20"/>
@@ -32074,7 +32084,7 @@
       <c r="D819" s="19"/>
       <c r="E819" s="20"/>
       <c r="F819" s="21"/>
-      <c r="G819" s="101"/>
+      <c r="G819" s="100"/>
       <c r="H819" s="19"/>
       <c r="I819" s="19"/>
       <c r="J819" s="20"/>
@@ -32107,7 +32117,7 @@
       <c r="D820" s="19"/>
       <c r="E820" s="20"/>
       <c r="F820" s="21"/>
-      <c r="G820" s="101"/>
+      <c r="G820" s="100"/>
       <c r="H820" s="19"/>
       <c r="I820" s="19"/>
       <c r="J820" s="20"/>
@@ -32140,7 +32150,7 @@
       <c r="D821" s="19"/>
       <c r="E821" s="20"/>
       <c r="F821" s="21"/>
-      <c r="G821" s="101"/>
+      <c r="G821" s="100"/>
       <c r="H821" s="19"/>
       <c r="I821" s="19"/>
       <c r="J821" s="20"/>
@@ -32173,7 +32183,7 @@
       <c r="D822" s="19"/>
       <c r="E822" s="20"/>
       <c r="F822" s="21"/>
-      <c r="G822" s="101"/>
+      <c r="G822" s="100"/>
       <c r="H822" s="19"/>
       <c r="I822" s="19"/>
       <c r="J822" s="20"/>
@@ -32206,7 +32216,7 @@
       <c r="D823" s="19"/>
       <c r="E823" s="20"/>
       <c r="F823" s="21"/>
-      <c r="G823" s="101"/>
+      <c r="G823" s="100"/>
       <c r="H823" s="19"/>
       <c r="I823" s="19"/>
       <c r="J823" s="20"/>
@@ -32239,7 +32249,7 @@
       <c r="D824" s="19"/>
       <c r="E824" s="20"/>
       <c r="F824" s="21"/>
-      <c r="G824" s="101"/>
+      <c r="G824" s="100"/>
       <c r="H824" s="19"/>
       <c r="I824" s="19"/>
       <c r="J824" s="20"/>
@@ -32272,7 +32282,7 @@
       <c r="D825" s="19"/>
       <c r="E825" s="20"/>
       <c r="F825" s="21"/>
-      <c r="G825" s="101"/>
+      <c r="G825" s="100"/>
       <c r="H825" s="19"/>
       <c r="I825" s="19"/>
       <c r="J825" s="20"/>
@@ -32305,7 +32315,7 @@
       <c r="D826" s="19"/>
       <c r="E826" s="20"/>
       <c r="F826" s="21"/>
-      <c r="G826" s="101"/>
+      <c r="G826" s="100"/>
       <c r="H826" s="19"/>
       <c r="I826" s="19"/>
       <c r="J826" s="20"/>
@@ -32338,7 +32348,7 @@
       <c r="D827" s="19"/>
       <c r="E827" s="20"/>
       <c r="F827" s="21"/>
-      <c r="G827" s="101"/>
+      <c r="G827" s="100"/>
       <c r="H827" s="19"/>
       <c r="I827" s="19"/>
       <c r="J827" s="20"/>
@@ -32371,7 +32381,7 @@
       <c r="D828" s="19"/>
       <c r="E828" s="20"/>
       <c r="F828" s="21"/>
-      <c r="G828" s="101"/>
+      <c r="G828" s="100"/>
       <c r="H828" s="19"/>
       <c r="I828" s="19"/>
       <c r="J828" s="20"/>
@@ -32404,7 +32414,7 @@
       <c r="D829" s="19"/>
       <c r="E829" s="20"/>
       <c r="F829" s="21"/>
-      <c r="G829" s="101"/>
+      <c r="G829" s="100"/>
       <c r="H829" s="19"/>
       <c r="I829" s="19"/>
       <c r="J829" s="20"/>
@@ -32437,7 +32447,7 @@
       <c r="D830" s="19"/>
       <c r="E830" s="20"/>
       <c r="F830" s="21"/>
-      <c r="G830" s="101"/>
+      <c r="G830" s="100"/>
       <c r="H830" s="19"/>
       <c r="I830" s="19"/>
       <c r="J830" s="20"/>
@@ -32470,7 +32480,7 @@
       <c r="D831" s="19"/>
       <c r="E831" s="20"/>
       <c r="F831" s="21"/>
-      <c r="G831" s="101"/>
+      <c r="G831" s="100"/>
       <c r="H831" s="19"/>
       <c r="I831" s="19"/>
       <c r="J831" s="20"/>
@@ -32503,7 +32513,7 @@
       <c r="D832" s="19"/>
       <c r="E832" s="20"/>
       <c r="F832" s="21"/>
-      <c r="G832" s="101"/>
+      <c r="G832" s="100"/>
       <c r="H832" s="19"/>
       <c r="I832" s="19"/>
       <c r="J832" s="20"/>
@@ -32536,7 +32546,7 @@
       <c r="D833" s="19"/>
       <c r="E833" s="20"/>
       <c r="F833" s="21"/>
-      <c r="G833" s="101"/>
+      <c r="G833" s="100"/>
       <c r="H833" s="19"/>
       <c r="I833" s="19"/>
       <c r="J833" s="20"/>
@@ -32569,7 +32579,7 @@
       <c r="D834" s="19"/>
       <c r="E834" s="20"/>
       <c r="F834" s="21"/>
-      <c r="G834" s="101"/>
+      <c r="G834" s="100"/>
       <c r="H834" s="19"/>
       <c r="I834" s="19"/>
       <c r="J834" s="20"/>
@@ -32602,7 +32612,7 @@
       <c r="D835" s="19"/>
       <c r="E835" s="20"/>
       <c r="F835" s="21"/>
-      <c r="G835" s="101"/>
+      <c r="G835" s="100"/>
       <c r="H835" s="19"/>
       <c r="I835" s="19"/>
       <c r="J835" s="20"/>
@@ -32635,7 +32645,7 @@
       <c r="D836" s="19"/>
       <c r="E836" s="20"/>
       <c r="F836" s="21"/>
-      <c r="G836" s="101"/>
+      <c r="G836" s="100"/>
       <c r="H836" s="19"/>
       <c r="I836" s="19"/>
       <c r="J836" s="20"/>
@@ -32668,7 +32678,7 @@
       <c r="D837" s="19"/>
       <c r="E837" s="20"/>
       <c r="F837" s="21"/>
-      <c r="G837" s="101"/>
+      <c r="G837" s="100"/>
       <c r="H837" s="19"/>
       <c r="I837" s="19"/>
       <c r="J837" s="20"/>
@@ -32701,7 +32711,7 @@
       <c r="D838" s="19"/>
       <c r="E838" s="20"/>
       <c r="F838" s="21"/>
-      <c r="G838" s="101"/>
+      <c r="G838" s="100"/>
       <c r="H838" s="19"/>
       <c r="I838" s="19"/>
       <c r="J838" s="20"/>
@@ -32734,7 +32744,7 @@
       <c r="D839" s="19"/>
       <c r="E839" s="20"/>
       <c r="F839" s="21"/>
-      <c r="G839" s="101"/>
+      <c r="G839" s="100"/>
       <c r="H839" s="19"/>
       <c r="I839" s="19"/>
       <c r="J839" s="20"/>
@@ -32767,7 +32777,7 @@
       <c r="D840" s="19"/>
       <c r="E840" s="20"/>
       <c r="F840" s="21"/>
-      <c r="G840" s="101"/>
+      <c r="G840" s="100"/>
       <c r="H840" s="19"/>
       <c r="I840" s="19"/>
       <c r="J840" s="20"/>
@@ -32800,7 +32810,7 @@
       <c r="D841" s="19"/>
       <c r="E841" s="20"/>
       <c r="F841" s="21"/>
-      <c r="G841" s="101"/>
+      <c r="G841" s="100"/>
       <c r="H841" s="19"/>
       <c r="I841" s="19"/>
       <c r="J841" s="20"/>
@@ -32833,7 +32843,7 @@
       <c r="D842" s="19"/>
       <c r="E842" s="20"/>
       <c r="F842" s="21"/>
-      <c r="G842" s="101"/>
+      <c r="G842" s="100"/>
       <c r="H842" s="19"/>
       <c r="I842" s="19"/>
       <c r="J842" s="20"/>
@@ -32866,7 +32876,7 @@
       <c r="D843" s="19"/>
       <c r="E843" s="20"/>
       <c r="F843" s="21"/>
-      <c r="G843" s="101"/>
+      <c r="G843" s="100"/>
       <c r="H843" s="19"/>
       <c r="I843" s="19"/>
       <c r="J843" s="20"/>
@@ -32899,7 +32909,7 @@
       <c r="D844" s="19"/>
       <c r="E844" s="20"/>
       <c r="F844" s="21"/>
-      <c r="G844" s="101"/>
+      <c r="G844" s="100"/>
       <c r="H844" s="19"/>
       <c r="I844" s="19"/>
       <c r="J844" s="20"/>
@@ -32932,7 +32942,7 @@
       <c r="D845" s="19"/>
       <c r="E845" s="20"/>
       <c r="F845" s="21"/>
-      <c r="G845" s="101"/>
+      <c r="G845" s="100"/>
       <c r="H845" s="19"/>
       <c r="I845" s="19"/>
       <c r="J845" s="20"/>
@@ -32965,7 +32975,7 @@
       <c r="D846" s="19"/>
       <c r="E846" s="20"/>
       <c r="F846" s="21"/>
-      <c r="G846" s="101"/>
+      <c r="G846" s="100"/>
       <c r="H846" s="19"/>
       <c r="I846" s="19"/>
       <c r="J846" s="20"/>
@@ -32998,7 +33008,7 @@
       <c r="D847" s="19"/>
       <c r="E847" s="20"/>
       <c r="F847" s="21"/>
-      <c r="G847" s="101"/>
+      <c r="G847" s="100"/>
       <c r="H847" s="19"/>
       <c r="I847" s="19"/>
       <c r="J847" s="20"/>
@@ -33031,7 +33041,7 @@
       <c r="D848" s="19"/>
       <c r="E848" s="20"/>
       <c r="F848" s="21"/>
-      <c r="G848" s="101"/>
+      <c r="G848" s="100"/>
       <c r="H848" s="19"/>
       <c r="I848" s="19"/>
       <c r="J848" s="20"/>
@@ -33064,7 +33074,7 @@
       <c r="D849" s="19"/>
       <c r="E849" s="20"/>
       <c r="F849" s="21"/>
-      <c r="G849" s="101"/>
+      <c r="G849" s="100"/>
       <c r="H849" s="19"/>
       <c r="I849" s="19"/>
       <c r="J849" s="20"/>
@@ -33097,7 +33107,7 @@
       <c r="D850" s="19"/>
       <c r="E850" s="20"/>
       <c r="F850" s="21"/>
-      <c r="G850" s="101"/>
+      <c r="G850" s="100"/>
       <c r="H850" s="19"/>
       <c r="I850" s="19"/>
       <c r="J850" s="20"/>
@@ -33130,7 +33140,7 @@
       <c r="D851" s="19"/>
       <c r="E851" s="20"/>
       <c r="F851" s="21"/>
-      <c r="G851" s="101"/>
+      <c r="G851" s="100"/>
       <c r="H851" s="19"/>
       <c r="I851" s="19"/>
       <c r="J851" s="20"/>
@@ -33163,7 +33173,7 @@
       <c r="D852" s="19"/>
       <c r="E852" s="20"/>
       <c r="F852" s="21"/>
-      <c r="G852" s="101"/>
+      <c r="G852" s="100"/>
       <c r="H852" s="19"/>
       <c r="I852" s="19"/>
       <c r="J852" s="20"/>
@@ -33196,7 +33206,7 @@
       <c r="D853" s="19"/>
       <c r="E853" s="20"/>
       <c r="F853" s="21"/>
-      <c r="G853" s="101"/>
+      <c r="G853" s="100"/>
       <c r="H853" s="19"/>
       <c r="I853" s="19"/>
       <c r="J853" s="20"/>
@@ -33229,7 +33239,7 @@
       <c r="D854" s="19"/>
       <c r="E854" s="20"/>
       <c r="F854" s="21"/>
-      <c r="G854" s="101"/>
+      <c r="G854" s="100"/>
       <c r="H854" s="19"/>
       <c r="I854" s="19"/>
       <c r="J854" s="20"/>
@@ -33262,7 +33272,7 @@
       <c r="D855" s="19"/>
       <c r="E855" s="20"/>
       <c r="F855" s="21"/>
-      <c r="G855" s="101"/>
+      <c r="G855" s="100"/>
       <c r="H855" s="19"/>
       <c r="I855" s="19"/>
       <c r="J855" s="20"/>
@@ -33295,7 +33305,7 @@
       <c r="D856" s="19"/>
       <c r="E856" s="20"/>
       <c r="F856" s="21"/>
-      <c r="G856" s="101"/>
+      <c r="G856" s="100"/>
       <c r="H856" s="19"/>
       <c r="I856" s="19"/>
       <c r="J856" s="20"/>
@@ -33328,7 +33338,7 @@
       <c r="D857" s="19"/>
       <c r="E857" s="20"/>
       <c r="F857" s="21"/>
-      <c r="G857" s="101"/>
+      <c r="G857" s="100"/>
       <c r="H857" s="19"/>
       <c r="I857" s="19"/>
       <c r="J857" s="20"/>
@@ -33361,7 +33371,7 @@
       <c r="D858" s="19"/>
       <c r="E858" s="20"/>
       <c r="F858" s="21"/>
-      <c r="G858" s="101"/>
+      <c r="G858" s="100"/>
       <c r="H858" s="19"/>
       <c r="I858" s="19"/>
       <c r="J858" s="20"/>
@@ -33394,7 +33404,7 @@
       <c r="D859" s="19"/>
       <c r="E859" s="20"/>
       <c r="F859" s="21"/>
-      <c r="G859" s="101"/>
+      <c r="G859" s="100"/>
       <c r="H859" s="19"/>
       <c r="I859" s="19"/>
       <c r="J859" s="20"/>
@@ -33427,7 +33437,7 @@
       <c r="D860" s="19"/>
       <c r="E860" s="20"/>
       <c r="F860" s="21"/>
-      <c r="G860" s="101"/>
+      <c r="G860" s="100"/>
       <c r="H860" s="19"/>
       <c r="I860" s="19"/>
       <c r="J860" s="20"/>
@@ -33460,7 +33470,7 @@
       <c r="D861" s="19"/>
       <c r="E861" s="20"/>
       <c r="F861" s="21"/>
-      <c r="G861" s="101"/>
+      <c r="G861" s="100"/>
       <c r="H861" s="19"/>
       <c r="I861" s="19"/>
       <c r="J861" s="20"/>
@@ -33493,7 +33503,7 @@
       <c r="D862" s="19"/>
       <c r="E862" s="20"/>
       <c r="F862" s="21"/>
-      <c r="G862" s="101"/>
+      <c r="G862" s="100"/>
       <c r="H862" s="19"/>
       <c r="I862" s="19"/>
       <c r="J862" s="20"/>
@@ -33526,7 +33536,7 @@
       <c r="D863" s="19"/>
       <c r="E863" s="20"/>
       <c r="F863" s="21"/>
-      <c r="G863" s="101"/>
+      <c r="G863" s="100"/>
       <c r="H863" s="19"/>
       <c r="I863" s="19"/>
       <c r="J863" s="20"/>
@@ -33559,7 +33569,7 @@
       <c r="D864" s="19"/>
       <c r="E864" s="20"/>
       <c r="F864" s="21"/>
-      <c r="G864" s="101"/>
+      <c r="G864" s="100"/>
       <c r="H864" s="19"/>
       <c r="I864" s="19"/>
       <c r="J864" s="20"/>
@@ -33592,7 +33602,7 @@
       <c r="D865" s="19"/>
       <c r="E865" s="20"/>
       <c r="F865" s="21"/>
-      <c r="G865" s="101"/>
+      <c r="G865" s="100"/>
       <c r="H865" s="19"/>
       <c r="I865" s="19"/>
       <c r="J865" s="20"/>
@@ -33625,7 +33635,7 @@
       <c r="D866" s="19"/>
       <c r="E866" s="20"/>
       <c r="F866" s="21"/>
-      <c r="G866" s="101"/>
+      <c r="G866" s="100"/>
       <c r="H866" s="19"/>
       <c r="I866" s="19"/>
       <c r="J866" s="20"/>
@@ -33658,7 +33668,7 @@
       <c r="D867" s="19"/>
       <c r="E867" s="20"/>
       <c r="F867" s="21"/>
-      <c r="G867" s="101"/>
+      <c r="G867" s="100"/>
       <c r="H867" s="19"/>
       <c r="I867" s="19"/>
       <c r="J867" s="20"/>
@@ -33691,7 +33701,7 @@
       <c r="D868" s="19"/>
       <c r="E868" s="20"/>
       <c r="F868" s="21"/>
-      <c r="G868" s="101"/>
+      <c r="G868" s="100"/>
       <c r="H868" s="19"/>
       <c r="I868" s="19"/>
       <c r="J868" s="20"/>
@@ -33724,7 +33734,7 @@
       <c r="D869" s="19"/>
       <c r="E869" s="20"/>
       <c r="F869" s="21"/>
-      <c r="G869" s="101"/>
+      <c r="G869" s="100"/>
       <c r="H869" s="19"/>
       <c r="I869" s="19"/>
       <c r="J869" s="20"/>
@@ -33757,7 +33767,7 @@
       <c r="D870" s="19"/>
       <c r="E870" s="20"/>
       <c r="F870" s="21"/>
-      <c r="G870" s="101"/>
+      <c r="G870" s="100"/>
       <c r="H870" s="19"/>
       <c r="I870" s="19"/>
       <c r="J870" s="20"/>
@@ -33790,7 +33800,7 @@
       <c r="D871" s="19"/>
       <c r="E871" s="20"/>
       <c r="F871" s="21"/>
-      <c r="G871" s="101"/>
+      <c r="G871" s="100"/>
       <c r="H871" s="19"/>
       <c r="I871" s="19"/>
       <c r="J871" s="20"/>
@@ -33823,7 +33833,7 @@
       <c r="D872" s="19"/>
       <c r="E872" s="20"/>
       <c r="F872" s="21"/>
-      <c r="G872" s="101"/>
+      <c r="G872" s="100"/>
       <c r="H872" s="19"/>
       <c r="I872" s="19"/>
       <c r="J872" s="20"/>
@@ -33856,7 +33866,7 @@
       <c r="D873" s="19"/>
       <c r="E873" s="20"/>
       <c r="F873" s="21"/>
-      <c r="G873" s="101"/>
+      <c r="G873" s="100"/>
       <c r="H873" s="19"/>
       <c r="I873" s="19"/>
       <c r="J873" s="20"/>
@@ -33889,7 +33899,7 @@
       <c r="D874" s="19"/>
       <c r="E874" s="20"/>
       <c r="F874" s="21"/>
-      <c r="G874" s="101"/>
+      <c r="G874" s="100"/>
       <c r="H874" s="19"/>
       <c r="I874" s="19"/>
       <c r="J874" s="20"/>
@@ -33922,7 +33932,7 @@
       <c r="D875" s="19"/>
       <c r="E875" s="20"/>
       <c r="F875" s="21"/>
-      <c r="G875" s="101"/>
+      <c r="G875" s="100"/>
       <c r="H875" s="19"/>
       <c r="I875" s="19"/>
       <c r="J875" s="20"/>
@@ -33955,7 +33965,7 @@
       <c r="D876" s="19"/>
       <c r="E876" s="20"/>
       <c r="F876" s="21"/>
-      <c r="G876" s="101"/>
+      <c r="G876" s="100"/>
       <c r="H876" s="19"/>
       <c r="I876" s="19"/>
       <c r="J876" s="20"/>
@@ -33988,7 +33998,7 @@
       <c r="D877" s="19"/>
       <c r="E877" s="20"/>
       <c r="F877" s="21"/>
-      <c r="G877" s="101"/>
+      <c r="G877" s="100"/>
       <c r="H877" s="19"/>
       <c r="I877" s="19"/>
       <c r="J877" s="20"/>
@@ -34021,7 +34031,7 @@
       <c r="D878" s="19"/>
       <c r="E878" s="20"/>
       <c r="F878" s="21"/>
-      <c r="G878" s="101"/>
+      <c r="G878" s="100"/>
       <c r="H878" s="19"/>
       <c r="I878" s="19"/>
       <c r="J878" s="20"/>
@@ -34054,7 +34064,7 @@
       <c r="D879" s="19"/>
       <c r="E879" s="20"/>
       <c r="F879" s="21"/>
-      <c r="G879" s="101"/>
+      <c r="G879" s="100"/>
       <c r="H879" s="19"/>
       <c r="I879" s="19"/>
       <c r="J879" s="20"/>
@@ -34087,7 +34097,7 @@
       <c r="D880" s="19"/>
       <c r="E880" s="20"/>
       <c r="F880" s="21"/>
-      <c r="G880" s="101"/>
+      <c r="G880" s="100"/>
       <c r="H880" s="19"/>
       <c r="I880" s="19"/>
       <c r="J880" s="20"/>
@@ -34120,7 +34130,7 @@
       <c r="D881" s="19"/>
       <c r="E881" s="20"/>
       <c r="F881" s="21"/>
-      <c r="G881" s="101"/>
+      <c r="G881" s="100"/>
       <c r="H881" s="19"/>
       <c r="I881" s="19"/>
       <c r="J881" s="20"/>
@@ -34153,7 +34163,7 @@
       <c r="D882" s="19"/>
       <c r="E882" s="20"/>
       <c r="F882" s="21"/>
-      <c r="G882" s="101"/>
+      <c r="G882" s="100"/>
       <c r="H882" s="19"/>
       <c r="I882" s="19"/>
       <c r="J882" s="20"/>
@@ -34186,7 +34196,7 @@
       <c r="D883" s="19"/>
       <c r="E883" s="20"/>
       <c r="F883" s="21"/>
-      <c r="G883" s="101"/>
+      <c r="G883" s="100"/>
       <c r="H883" s="19"/>
       <c r="I883" s="19"/>
       <c r="J883" s="20"/>
@@ -34219,7 +34229,7 @@
       <c r="D884" s="19"/>
       <c r="E884" s="20"/>
       <c r="F884" s="21"/>
-      <c r="G884" s="101"/>
+      <c r="G884" s="100"/>
       <c r="H884" s="19"/>
       <c r="I884" s="19"/>
       <c r="J884" s="20"/>
@@ -34252,7 +34262,7 @@
       <c r="D885" s="19"/>
       <c r="E885" s="20"/>
       <c r="F885" s="21"/>
-      <c r="G885" s="101"/>
+      <c r="G885" s="100"/>
       <c r="H885" s="19"/>
       <c r="I885" s="19"/>
       <c r="J885" s="20"/>
@@ -34285,7 +34295,7 @@
       <c r="D886" s="19"/>
       <c r="E886" s="20"/>
       <c r="F886" s="21"/>
-      <c r="G886" s="101"/>
+      <c r="G886" s="100"/>
       <c r="H886" s="19"/>
       <c r="I886" s="19"/>
       <c r="J886" s="20"/>
@@ -34318,7 +34328,7 @@
       <c r="D887" s="19"/>
       <c r="E887" s="20"/>
       <c r="F887" s="21"/>
-      <c r="G887" s="101"/>
+      <c r="G887" s="100"/>
       <c r="H887" s="19"/>
       <c r="I887" s="19"/>
       <c r="J887" s="20"/>
@@ -34351,7 +34361,7 @@
       <c r="D888" s="19"/>
       <c r="E888" s="20"/>
       <c r="F888" s="21"/>
-      <c r="G888" s="101"/>
+      <c r="G888" s="100"/>
       <c r="H888" s="19"/>
       <c r="I888" s="19"/>
       <c r="J888" s="20"/>
@@ -34384,7 +34394,7 @@
       <c r="D889" s="19"/>
       <c r="E889" s="20"/>
       <c r="F889" s="21"/>
-      <c r="G889" s="101"/>
+      <c r="G889" s="100"/>
       <c r="H889" s="19"/>
       <c r="I889" s="19"/>
       <c r="J889" s="20"/>
@@ -34417,7 +34427,7 @@
       <c r="D890" s="19"/>
       <c r="E890" s="20"/>
       <c r="F890" s="21"/>
-      <c r="G890" s="101"/>
+      <c r="G890" s="100"/>
       <c r="H890" s="19"/>
       <c r="I890" s="19"/>
       <c r="J890" s="20"/>
@@ -34450,7 +34460,7 @@
       <c r="D891" s="19"/>
       <c r="E891" s="20"/>
       <c r="F891" s="21"/>
-      <c r="G891" s="101"/>
+      <c r="G891" s="100"/>
       <c r="H891" s="19"/>
       <c r="I891" s="19"/>
       <c r="J891" s="20"/>
@@ -34483,7 +34493,7 @@
       <c r="D892" s="19"/>
       <c r="E892" s="20"/>
       <c r="F892" s="21"/>
-      <c r="G892" s="101"/>
+      <c r="G892" s="100"/>
       <c r="H892" s="19"/>
       <c r="I892" s="19"/>
       <c r="J892" s="20"/>
@@ -34516,7 +34526,7 @@
       <c r="D893" s="19"/>
       <c r="E893" s="20"/>
       <c r="F893" s="21"/>
-      <c r="G893" s="101"/>
+      <c r="G893" s="100"/>
       <c r="H893" s="19"/>
       <c r="I893" s="19"/>
       <c r="J893" s="20"/>
@@ -34549,7 +34559,7 @@
       <c r="D894" s="19"/>
       <c r="E894" s="20"/>
       <c r="F894" s="21"/>
-      <c r="G894" s="101"/>
+      <c r="G894" s="100"/>
       <c r="H894" s="19"/>
       <c r="I894" s="19"/>
       <c r="J894" s="20"/>
@@ -34582,7 +34592,7 @@
       <c r="D895" s="19"/>
       <c r="E895" s="20"/>
       <c r="F895" s="21"/>
-      <c r="G895" s="101"/>
+      <c r="G895" s="100"/>
       <c r="H895" s="19"/>
       <c r="I895" s="19"/>
       <c r="J895" s="20"/>
@@ -34615,7 +34625,7 @@
       <c r="D896" s="19"/>
       <c r="E896" s="20"/>
       <c r="F896" s="21"/>
-      <c r="G896" s="101"/>
+      <c r="G896" s="100"/>
       <c r="H896" s="19"/>
       <c r="I896" s="19"/>
       <c r="J896" s="20"/>
@@ -34648,7 +34658,7 @@
       <c r="D897" s="19"/>
       <c r="E897" s="20"/>
       <c r="F897" s="21"/>
-      <c r="G897" s="101"/>
+      <c r="G897" s="100"/>
       <c r="H897" s="19"/>
       <c r="I897" s="19"/>
       <c r="J897" s="20"/>
@@ -34681,7 +34691,7 @@
       <c r="D898" s="19"/>
       <c r="E898" s="20"/>
       <c r="F898" s="21"/>
-      <c r="G898" s="101"/>
+      <c r="G898" s="100"/>
       <c r="H898" s="19"/>
       <c r="I898" s="19"/>
       <c r="J898" s="20"/>
@@ -34714,7 +34724,7 @@
       <c r="D899" s="19"/>
       <c r="E899" s="20"/>
       <c r="F899" s="21"/>
-      <c r="G899" s="101"/>
+      <c r="G899" s="100"/>
       <c r="H899" s="19"/>
       <c r="I899" s="19"/>
       <c r="J899" s="20"/>
@@ -34747,7 +34757,7 @@
       <c r="D900" s="19"/>
       <c r="E900" s="20"/>
       <c r="F900" s="21"/>
-      <c r="G900" s="101"/>
+      <c r="G900" s="100"/>
       <c r="H900" s="19"/>
       <c r="I900" s="19"/>
       <c r="J900" s="20"/>
@@ -34780,7 +34790,7 @@
       <c r="D901" s="19"/>
       <c r="E901" s="20"/>
       <c r="F901" s="21"/>
-      <c r="G901" s="101"/>
+      <c r="G901" s="100"/>
       <c r="H901" s="19"/>
       <c r="I901" s="19"/>
       <c r="J901" s="20"/>
@@ -34813,7 +34823,7 @@
       <c r="D902" s="19"/>
       <c r="E902" s="20"/>
       <c r="F902" s="21"/>
-      <c r="G902" s="101"/>
+      <c r="G902" s="100"/>
       <c r="H902" s="19"/>
       <c r="I902" s="19"/>
       <c r="J902" s="20"/>
@@ -34846,7 +34856,7 @@
       <c r="D903" s="19"/>
       <c r="E903" s="20"/>
       <c r="F903" s="21"/>
-      <c r="G903" s="101"/>
+      <c r="G903" s="100"/>
       <c r="H903" s="19"/>
       <c r="I903" s="19"/>
       <c r="J903" s="20"/>
@@ -34879,7 +34889,7 @@
       <c r="D904" s="19"/>
       <c r="E904" s="20"/>
       <c r="F904" s="21"/>
-      <c r="G904" s="101"/>
+      <c r="G904" s="100"/>
       <c r="H904" s="19"/>
       <c r="I904" s="19"/>
       <c r="J904" s="20"/>
@@ -34912,7 +34922,7 @@
       <c r="D905" s="19"/>
       <c r="E905" s="20"/>
       <c r="F905" s="21"/>
-      <c r="G905" s="101"/>
+      <c r="G905" s="100"/>
       <c r="H905" s="19"/>
       <c r="I905" s="19"/>
       <c r="J905" s="20"/>
@@ -34945,7 +34955,7 @@
       <c r="D906" s="19"/>
       <c r="E906" s="20"/>
       <c r="F906" s="21"/>
-      <c r="G906" s="101"/>
+      <c r="G906" s="100"/>
       <c r="H906" s="19"/>
       <c r="I906" s="19"/>
       <c r="J906" s="20"/>
@@ -34978,7 +34988,7 @@
       <c r="D907" s="19"/>
       <c r="E907" s="20"/>
       <c r="F907" s="21"/>
-      <c r="G907" s="101"/>
+      <c r="G907" s="100"/>
       <c r="H907" s="19"/>
       <c r="I907" s="19"/>
       <c r="J907" s="20"/>
@@ -35011,7 +35021,7 @@
       <c r="D908" s="19"/>
       <c r="E908" s="20"/>
       <c r="F908" s="21"/>
-      <c r="G908" s="101"/>
+      <c r="G908" s="100"/>
       <c r="H908" s="19"/>
       <c r="I908" s="19"/>
       <c r="J908" s="20"/>
@@ -35044,7 +35054,7 @@
       <c r="D909" s="19"/>
       <c r="E909" s="20"/>
       <c r="F909" s="21"/>
-      <c r="G909" s="101"/>
+      <c r="G909" s="100"/>
       <c r="H909" s="19"/>
       <c r="I909" s="19"/>
       <c r="J909" s="20"/>
@@ -35077,7 +35087,7 @@
       <c r="D910" s="19"/>
       <c r="E910" s="20"/>
       <c r="F910" s="21"/>
-      <c r="G910" s="101"/>
+      <c r="G910" s="100"/>
       <c r="H910" s="19"/>
       <c r="I910" s="19"/>
       <c r="J910" s="20"/>
@@ -35110,7 +35120,7 @@
       <c r="D911" s="19"/>
       <c r="E911" s="20"/>
       <c r="F911" s="21"/>
-      <c r="G911" s="101"/>
+      <c r="G911" s="100"/>
       <c r="H911" s="19"/>
       <c r="I911" s="19"/>
       <c r="J911" s="20"/>
@@ -35143,7 +35153,7 @@
       <c r="D912" s="19"/>
       <c r="E912" s="20"/>
       <c r="F912" s="21"/>
-      <c r="G912" s="101"/>
+      <c r="G912" s="100"/>
       <c r="H912" s="19"/>
       <c r="I912" s="19"/>
       <c r="J912" s="20"/>
@@ -35176,7 +35186,7 @@
       <c r="D913" s="19"/>
       <c r="E913" s="20"/>
       <c r="F913" s="21"/>
-      <c r="G913" s="101"/>
+      <c r="G913" s="100"/>
       <c r="H913" s="19"/>
       <c r="I913" s="19"/>
       <c r="J913" s="20"/>
@@ -35209,7 +35219,7 @@
       <c r="D914" s="19"/>
       <c r="E914" s="20"/>
       <c r="F914" s="21"/>
-      <c r="G914" s="101"/>
+      <c r="G914" s="100"/>
       <c r="H914" s="19"/>
       <c r="I914" s="19"/>
       <c r="J914" s="20"/>
@@ -35242,7 +35252,7 @@
       <c r="D915" s="19"/>
       <c r="E915" s="20"/>
       <c r="F915" s="21"/>
-      <c r="G915" s="101"/>
+      <c r="G915" s="100"/>
       <c r="H915" s="19"/>
       <c r="I915" s="19"/>
       <c r="J915" s="20"/>
@@ -35275,7 +35285,7 @@
       <c r="D916" s="19"/>
       <c r="E916" s="20"/>
       <c r="F916" s="21"/>
-      <c r="G916" s="101"/>
+      <c r="G916" s="100"/>
       <c r="H916" s="19"/>
       <c r="I916" s="19"/>
       <c r="J916" s="20"/>
@@ -35308,7 +35318,7 @@
       <c r="D917" s="19"/>
       <c r="E917" s="20"/>
       <c r="F917" s="21"/>
-      <c r="G917" s="101"/>
+      <c r="G917" s="100"/>
       <c r="H917" s="19"/>
       <c r="I917" s="19"/>
       <c r="J917" s="20"/>
@@ -35341,7 +35351,7 @@
       <c r="D918" s="19"/>
       <c r="E918" s="20"/>
       <c r="F918" s="21"/>
-      <c r="G918" s="101"/>
+      <c r="G918" s="100"/>
       <c r="H918" s="19"/>
       <c r="I918" s="19"/>
       <c r="J918" s="20"/>
@@ -35374,7 +35384,7 @@
       <c r="D919" s="19"/>
       <c r="E919" s="20"/>
       <c r="F919" s="21"/>
-      <c r="G919" s="101"/>
+      <c r="G919" s="100"/>
       <c r="H919" s="19"/>
       <c r="I919" s="19"/>
       <c r="J919" s="20"/>
@@ -35407,7 +35417,7 @@
       <c r="D920" s="19"/>
       <c r="E920" s="20"/>
       <c r="F920" s="21"/>
-      <c r="G920" s="101"/>
+      <c r="G920" s="100"/>
       <c r="H920" s="19"/>
       <c r="I920" s="19"/>
       <c r="J920" s="20"/>
@@ -35440,7 +35450,7 @@
       <c r="D921" s="19"/>
       <c r="E921" s="20"/>
       <c r="F921" s="21"/>
-      <c r="G921" s="101"/>
+      <c r="G921" s="100"/>
       <c r="H921" s="19"/>
       <c r="I921" s="19"/>
       <c r="J921" s="20"/>
@@ -35473,7 +35483,7 @@
       <c r="D922" s="19"/>
       <c r="E922" s="20"/>
       <c r="F922" s="21"/>
-      <c r="G922" s="101"/>
+      <c r="G922" s="100"/>
       <c r="H922" s="19"/>
       <c r="I922" s="19"/>
       <c r="J922" s="20"/>
@@ -35506,7 +35516,7 @@
       <c r="D923" s="19"/>
       <c r="E923" s="20"/>
       <c r="F923" s="21"/>
-      <c r="G923" s="101"/>
+      <c r="G923" s="100"/>
       <c r="H923" s="19"/>
       <c r="I923" s="19"/>
       <c r="J923" s="20"/>
@@ -35539,7 +35549,7 @@
       <c r="D924" s="19"/>
       <c r="E924" s="20"/>
       <c r="F924" s="21"/>
-      <c r="G924" s="101"/>
+      <c r="G924" s="100"/>
       <c r="H924" s="19"/>
       <c r="I924" s="19"/>
       <c r="J924" s="20"/>
@@ -35572,7 +35582,7 @@
       <c r="D925" s="19"/>
       <c r="E925" s="20"/>
       <c r="F925" s="21"/>
-      <c r="G925" s="101"/>
+      <c r="G925" s="100"/>
       <c r="H925" s="19"/>
       <c r="I925" s="19"/>
       <c r="J925" s="20"/>
@@ -35605,7 +35615,7 @@
       <c r="D926" s="19"/>
       <c r="E926" s="20"/>
       <c r="F926" s="21"/>
-      <c r="G926" s="101"/>
+      <c r="G926" s="100"/>
       <c r="H926" s="19"/>
       <c r="I926" s="19"/>
       <c r="J926" s="20"/>
@@ -35638,7 +35648,7 @@
       <c r="D927" s="19"/>
       <c r="E927" s="20"/>
       <c r="F927" s="21"/>
-      <c r="G927" s="101"/>
+      <c r="G927" s="100"/>
       <c r="H927" s="19"/>
       <c r="I927" s="19"/>
       <c r="J927" s="20"/>
@@ -35671,7 +35681,7 @@
       <c r="D928" s="19"/>
       <c r="E928" s="20"/>
       <c r="F928" s="21"/>
-      <c r="G928" s="101"/>
+      <c r="G928" s="100"/>
       <c r="H928" s="19"/>
       <c r="I928" s="19"/>
       <c r="J928" s="20"/>
@@ -35704,7 +35714,7 @@
       <c r="D929" s="19"/>
       <c r="E929" s="20"/>
       <c r="F929" s="21"/>
-      <c r="G929" s="101"/>
+      <c r="G929" s="100"/>
       <c r="H929" s="19"/>
       <c r="I929" s="19"/>
       <c r="J929" s="20"/>
@@ -35737,7 +35747,7 @@
       <c r="D930" s="19"/>
       <c r="E930" s="20"/>
       <c r="F930" s="21"/>
-      <c r="G930" s="101"/>
+      <c r="G930" s="100"/>
       <c r="H930" s="19"/>
       <c r="I930" s="19"/>
       <c r="J930" s="20"/>
@@ -35770,7 +35780,7 @@
       <c r="D931" s="19"/>
       <c r="E931" s="20"/>
       <c r="F931" s="21"/>
-      <c r="G931" s="101"/>
+      <c r="G931" s="100"/>
       <c r="H931" s="19"/>
       <c r="I931" s="19"/>
       <c r="J931" s="20"/>
@@ -35803,7 +35813,7 @@
       <c r="D932" s="19"/>
       <c r="E932" s="20"/>
       <c r="F932" s="21"/>
-      <c r="G932" s="101"/>
+      <c r="G932" s="100"/>
       <c r="H932" s="19"/>
       <c r="I932" s="19"/>
       <c r="J932" s="20"/>
@@ -35836,7 +35846,7 @@
       <c r="D933" s="19"/>
       <c r="E933" s="20"/>
       <c r="F933" s="21"/>
-      <c r="G933" s="101"/>
+      <c r="G933" s="100"/>
       <c r="H933" s="19"/>
       <c r="I933" s="19"/>
       <c r="J933" s="20"/>
@@ -35869,7 +35879,7 @@
       <c r="D934" s="19"/>
       <c r="E934" s="20"/>
       <c r="F934" s="21"/>
-      <c r="G934" s="101"/>
+      <c r="G934" s="100"/>
       <c r="H934" s="19"/>
       <c r="I934" s="19"/>
       <c r="J934" s="20"/>
@@ -35902,7 +35912,7 @@
       <c r="D935" s="19"/>
       <c r="E935" s="20"/>
       <c r="F935" s="21"/>
-      <c r="G935" s="101"/>
+      <c r="G935" s="100"/>
       <c r="H935" s="19"/>
       <c r="I935" s="19"/>
       <c r="J935" s="20"/>
@@ -35935,7 +35945,7 @@
       <c r="D936" s="19"/>
       <c r="E936" s="20"/>
       <c r="F936" s="21"/>
-      <c r="G936" s="101"/>
+      <c r="G936" s="100"/>
       <c r="H936" s="19"/>
       <c r="I936" s="19"/>
       <c r="J936" s="20"/>
@@ -35968,7 +35978,7 @@
       <c r="D937" s="19"/>
       <c r="E937" s="20"/>
       <c r="F937" s="21"/>
-      <c r="G937" s="101"/>
+      <c r="G937" s="100"/>
       <c r="H937" s="19"/>
       <c r="I937" s="19"/>
       <c r="J937" s="20"/>
@@ -36001,7 +36011,7 @@
       <c r="D938" s="19"/>
       <c r="E938" s="20"/>
       <c r="F938" s="21"/>
-      <c r="G938" s="101"/>
+      <c r="G938" s="100"/>
       <c r="H938" s="19"/>
       <c r="I938" s="19"/>
       <c r="J938" s="20"/>
@@ -36034,7 +36044,7 @@
       <c r="D939" s="19"/>
       <c r="E939" s="20"/>
       <c r="F939" s="21"/>
-      <c r="G939" s="101"/>
+      <c r="G939" s="100"/>
       <c r="H939" s="19"/>
       <c r="I939" s="19"/>
       <c r="J939" s="20"/>
@@ -36067,7 +36077,7 @@
       <c r="D940" s="19"/>
       <c r="E940" s="20"/>
       <c r="F940" s="21"/>
-      <c r="G940" s="101"/>
+      <c r="G940" s="100"/>
       <c r="H940" s="19"/>
       <c r="I940" s="19"/>
       <c r="J940" s="20"/>
@@ -36100,7 +36110,7 @@
       <c r="D941" s="19"/>
       <c r="E941" s="20"/>
       <c r="F941" s="21"/>
-      <c r="G941" s="101"/>
+      <c r="G941" s="100"/>
       <c r="H941" s="19"/>
       <c r="I941" s="19"/>
       <c r="J941" s="20"/>
@@ -36133,7 +36143,7 @@
       <c r="D942" s="19"/>
       <c r="E942" s="20"/>
       <c r="F942" s="21"/>
-      <c r="G942" s="101"/>
+      <c r="G942" s="100"/>
       <c r="H942" s="19"/>
       <c r="I942" s="19"/>
       <c r="J942" s="20"/>
@@ -36166,7 +36176,7 @@
       <c r="D943" s="19"/>
       <c r="E943" s="20"/>
       <c r="F943" s="21"/>
-      <c r="G943" s="101"/>
+      <c r="G943" s="100"/>
       <c r="H943" s="19"/>
       <c r="I943" s="19"/>
       <c r="J943" s="20"/>
@@ -36199,7 +36209,7 @@
       <c r="D944" s="19"/>
       <c r="E944" s="20"/>
       <c r="F944" s="21"/>
-      <c r="G944" s="101"/>
+      <c r="G944" s="100"/>
       <c r="H944" s="19"/>
       <c r="I944" s="19"/>
       <c r="J944" s="20"/>
@@ -36232,7 +36242,7 @@
       <c r="D945" s="19"/>
       <c r="E945" s="20"/>
       <c r="F945" s="21"/>
-      <c r="G945" s="101"/>
+      <c r="G945" s="100"/>
       <c r="H945" s="19"/>
       <c r="I945" s="19"/>
       <c r="J945" s="20"/>
@@ -36265,7 +36275,7 @@
       <c r="D946" s="19"/>
       <c r="E946" s="20"/>
       <c r="F946" s="21"/>
-      <c r="G946" s="101"/>
+      <c r="G946" s="100"/>
       <c r="H946" s="19"/>
       <c r="I946" s="19"/>
       <c r="J946" s="20"/>
@@ -36298,7 +36308,7 @@
       <c r="D947" s="19"/>
       <c r="E947" s="20"/>
       <c r="F947" s="21"/>
-      <c r="G947" s="101"/>
+      <c r="G947" s="100"/>
       <c r="H947" s="19"/>
       <c r="I947" s="19"/>
       <c r="J947" s="20"/>
@@ -36331,7 +36341,7 @@
       <c r="D948" s="19"/>
       <c r="E948" s="20"/>
       <c r="F948" s="21"/>
-      <c r="G948" s="101"/>
+      <c r="G948" s="100"/>
       <c r="H948" s="19"/>
       <c r="I948" s="19"/>
       <c r="J948" s="20"/>
@@ -36364,7 +36374,7 @@
       <c r="D949" s="19"/>
       <c r="E949" s="20"/>
       <c r="F949" s="21"/>
-      <c r="G949" s="101"/>
+      <c r="G949" s="100"/>
       <c r="H949" s="19"/>
       <c r="I949" s="19"/>
       <c r="J949" s="20"/>
@@ -36397,7 +36407,7 @@
       <c r="D950" s="19"/>
       <c r="E950" s="20"/>
       <c r="F950" s="21"/>
-      <c r="G950" s="101"/>
+      <c r="G950" s="100"/>
       <c r="H950" s="19"/>
       <c r="I950" s="19"/>
       <c r="J950" s="20"/>
@@ -36430,7 +36440,7 @@
       <c r="D951" s="19"/>
       <c r="E951" s="20"/>
       <c r="F951" s="21"/>
-      <c r="G951" s="101"/>
+      <c r="G951" s="100"/>
       <c r="H951" s="19"/>
       <c r="I951" s="19"/>
       <c r="J951" s="20"/>
@@ -36463,7 +36473,7 @@
       <c r="D952" s="19"/>
       <c r="E952" s="20"/>
       <c r="F952" s="21"/>
-      <c r="G952" s="101"/>
+      <c r="G952" s="100"/>
       <c r="H952" s="19"/>
       <c r="I952" s="19"/>
       <c r="J952" s="20"/>
@@ -36496,7 +36506,7 @@
       <c r="D953" s="19"/>
       <c r="E953" s="20"/>
       <c r="F953" s="21"/>
-      <c r="G953" s="101"/>
+      <c r="G953" s="100"/>
       <c r="H953" s="19"/>
       <c r="I953" s="19"/>
       <c r="J953" s="20"/>
@@ -36529,7 +36539,7 @@
       <c r="D954" s="19"/>
       <c r="E954" s="20"/>
       <c r="F954" s="21"/>
-      <c r="G954" s="101"/>
+      <c r="G954" s="100"/>
       <c r="H954" s="19"/>
       <c r="I954" s="19"/>
       <c r="J954" s="20"/>
@@ -36562,7 +36572,7 @@
       <c r="D955" s="19"/>
       <c r="E955" s="20"/>
       <c r="F955" s="21"/>
-      <c r="G955" s="101"/>
+      <c r="G955" s="100"/>
       <c r="H955" s="19"/>
       <c r="I955" s="19"/>
       <c r="J955" s="20"/>
@@ -36595,7 +36605,7 @@
       <c r="D956" s="19"/>
       <c r="E956" s="20"/>
       <c r="F956" s="21"/>
-      <c r="G956" s="101"/>
+      <c r="G956" s="100"/>
       <c r="H956" s="19"/>
       <c r="I956" s="19"/>
       <c r="J956" s="20"/>
@@ -36628,7 +36638,7 @@
       <c r="D957" s="19"/>
       <c r="E957" s="20"/>
       <c r="F957" s="21"/>
-      <c r="G957" s="101"/>
+      <c r="G957" s="100"/>
       <c r="H957" s="19"/>
       <c r="I957" s="19"/>
       <c r="J957" s="20"/>
@@ -36661,7 +36671,7 @@
       <c r="D958" s="19"/>
       <c r="E958" s="20"/>
       <c r="F958" s="21"/>
-      <c r="G958" s="101"/>
+      <c r="G958" s="100"/>
       <c r="H958" s="19"/>
       <c r="I958" s="19"/>
       <c r="J958" s="20"/>
@@ -36694,7 +36704,7 @@
       <c r="D959" s="19"/>
       <c r="E959" s="20"/>
       <c r="F959" s="21"/>
-      <c r="G959" s="101"/>
+      <c r="G959" s="100"/>
       <c r="H959" s="19"/>
       <c r="I959" s="19"/>
       <c r="J959" s="20"/>
@@ -36727,7 +36737,7 @@
       <c r="D960" s="19"/>
       <c r="E960" s="20"/>
       <c r="F960" s="21"/>
-      <c r="G960" s="101"/>
+      <c r="G960" s="100"/>
       <c r="H960" s="19"/>
       <c r="I960" s="19"/>
       <c r="J960" s="20"/>
@@ -36760,7 +36770,7 @@
       <c r="D961" s="19"/>
       <c r="E961" s="20"/>
       <c r="F961" s="21"/>
-      <c r="G961" s="101"/>
+      <c r="G961" s="100"/>
       <c r="H961" s="19"/>
       <c r="I961" s="19"/>
       <c r="J961" s="20"/>
@@ -36793,7 +36803,7 @@
       <c r="D962" s="19"/>
       <c r="E962" s="20"/>
       <c r="F962" s="21"/>
-      <c r="G962" s="101"/>
+      <c r="G962" s="100"/>
       <c r="H962" s="19"/>
       <c r="I962" s="19"/>
       <c r="J962" s="20"/>
@@ -36826,7 +36836,7 @@
       <c r="D963" s="19"/>
       <c r="E963" s="20"/>
       <c r="F963" s="21"/>
-      <c r="G963" s="101"/>
+      <c r="G963" s="100"/>
       <c r="H963" s="19"/>
       <c r="I963" s="19"/>
       <c r="J963" s="20"/>
@@ -36859,7 +36869,7 @@
       <c r="D964" s="19"/>
       <c r="E964" s="20"/>
       <c r="F964" s="21"/>
-      <c r="G964" s="101"/>
+      <c r="G964" s="100"/>
       <c r="H964" s="19"/>
       <c r="I964" s="19"/>
       <c r="J964" s="20"/>
@@ -36892,7 +36902,7 @@
       <c r="D965" s="19"/>
       <c r="E965" s="20"/>
       <c r="F965" s="21"/>
-      <c r="G965" s="101"/>
+      <c r="G965" s="100"/>
       <c r="H965" s="19"/>
       <c r="I965" s="19"/>
       <c r="J965" s="20"/>
@@ -36925,7 +36935,7 @@
       <c r="D966" s="19"/>
       <c r="E966" s="20"/>
       <c r="F966" s="21"/>
-      <c r="G966" s="101"/>
+      <c r="G966" s="100"/>
       <c r="H966" s="19"/>
       <c r="I966" s="19"/>
       <c r="J966" s="20"/>
@@ -36958,7 +36968,7 @@
       <c r="D967" s="19"/>
       <c r="E967" s="20"/>
       <c r="F967" s="21"/>
-      <c r="G967" s="101"/>
+      <c r="G967" s="100"/>
       <c r="H967" s="19"/>
       <c r="I967" s="19"/>
       <c r="J967" s="20"/>
@@ -36991,7 +37001,7 @@
       <c r="D968" s="19"/>
       <c r="E968" s="20"/>
       <c r="F968" s="21"/>
-      <c r="G968" s="101"/>
+      <c r="G968" s="100"/>
       <c r="H968" s="19"/>
       <c r="I968" s="19"/>
       <c r="J968" s="20"/>
@@ -37024,7 +37034,7 @@
       <c r="D969" s="19"/>
       <c r="E969" s="20"/>
       <c r="F969" s="21"/>
-      <c r="G969" s="101"/>
+      <c r="G969" s="100"/>
       <c r="H969" s="19"/>
       <c r="I969" s="19"/>
       <c r="J969" s="20"/>
@@ -37057,7 +37067,7 @@
       <c r="D970" s="19"/>
       <c r="E970" s="20"/>
       <c r="F970" s="21"/>
-      <c r="G970" s="101"/>
+      <c r="G970" s="100"/>
       <c r="H970" s="19"/>
       <c r="I970" s="19"/>
       <c r="J970" s="20"/>
@@ -37090,7 +37100,7 @@
       <c r="D971" s="19"/>
       <c r="E971" s="20"/>
       <c r="F971" s="21"/>
-      <c r="G971" s="101"/>
+      <c r="G971" s="100"/>
       <c r="H971" s="19"/>
       <c r="I971" s="19"/>
       <c r="J971" s="20"/>
@@ -37123,7 +37133,7 @@
       <c r="D972" s="19"/>
       <c r="E972" s="20"/>
       <c r="F972" s="21"/>
-      <c r="G972" s="101"/>
+      <c r="G972" s="100"/>
       <c r="H972" s="19"/>
       <c r="I972" s="19"/>
       <c r="J972" s="20"/>
@@ -37156,7 +37166,7 @@
       <c r="D973" s="19"/>
       <c r="E973" s="20"/>
       <c r="F973" s="21"/>
-      <c r="G973" s="101"/>
+      <c r="G973" s="100"/>
       <c r="H973" s="19"/>
       <c r="I973" s="19"/>
       <c r="J973" s="20"/>
@@ -37189,7 +37199,7 @@
       <c r="D974" s="19"/>
       <c r="E974" s="20"/>
       <c r="F974" s="21"/>
-      <c r="G974" s="101"/>
+      <c r="G974" s="100"/>
       <c r="H974" s="19"/>
       <c r="I974" s="19"/>
       <c r="J974" s="20"/>
@@ -37222,7 +37232,7 @@
       <c r="D975" s="19"/>
       <c r="E975" s="20"/>
       <c r="F975" s="21"/>
-      <c r="G975" s="101"/>
+      <c r="G975" s="100"/>
       <c r="H975" s="19"/>
       <c r="I975" s="19"/>
       <c r="J975" s="20"/>
@@ -37255,7 +37265,7 @@
       <c r="D976" s="19"/>
       <c r="E976" s="20"/>
       <c r="F976" s="21"/>
-      <c r="G976" s="101"/>
+      <c r="G976" s="100"/>
       <c r="H976" s="19"/>
       <c r="I976" s="19"/>
       <c r="J976" s="20"/>
@@ -37288,7 +37298,7 @@
       <c r="D977" s="19"/>
       <c r="E977" s="20"/>
       <c r="F977" s="21"/>
-      <c r="G977" s="101"/>
+      <c r="G977" s="100"/>
       <c r="H977" s="19"/>
       <c r="I977" s="19"/>
       <c r="J977" s="20"/>
@@ -37321,7 +37331,7 @@
       <c r="D978" s="19"/>
       <c r="E978" s="20"/>
       <c r="F978" s="21"/>
-      <c r="G978" s="101"/>
+      <c r="G978" s="100"/>
       <c r="H978" s="19"/>
       <c r="I978" s="19"/>
       <c r="J978" s="20"/>
@@ -37354,7 +37364,7 @@
       <c r="D979" s="19"/>
       <c r="E979" s="20"/>
       <c r="F979" s="21"/>
-      <c r="G979" s="101"/>
+      <c r="G979" s="100"/>
       <c r="H979" s="19"/>
       <c r="I979" s="19"/>
       <c r="J979" s="20"/>
@@ -37387,7 +37397,7 @@
       <c r="D980" s="19"/>
       <c r="E980" s="20"/>
       <c r="F980" s="21"/>
-      <c r="G980" s="101"/>
+      <c r="G980" s="100"/>
       <c r="H980" s="19"/>
       <c r="I980" s="19"/>
       <c r="J980" s="20"/>
@@ -37420,7 +37430,7 @@
       <c r="D981" s="19"/>
       <c r="E981" s="20"/>
       <c r="F981" s="21"/>
-      <c r="G981" s="101"/>
+      <c r="G981" s="100"/>
       <c r="H981" s="19"/>
       <c r="I981" s="19"/>
       <c r="J981" s="20"/>
@@ -37453,7 +37463,7 @@
       <c r="D982" s="19"/>
       <c r="E982" s="20"/>
       <c r="F982" s="21"/>
-      <c r="G982" s="101"/>
+      <c r="G982" s="100"/>
       <c r="H982" s="19"/>
       <c r="I982" s="19"/>
       <c r="J982" s="20"/>
@@ -37486,7 +37496,7 @@
       <c r="D983" s="19"/>
       <c r="E983" s="20"/>
       <c r="F983" s="21"/>
-      <c r="G983" s="101"/>
+      <c r="G983" s="100"/>
       <c r="H983" s="19"/>
       <c r="I983" s="19"/>
       <c r="J983" s="20"/>
@@ -37519,7 +37529,7 @@
       <c r="D984" s="19"/>
       <c r="E984" s="20"/>
       <c r="F984" s="21"/>
-      <c r="G984" s="101"/>
+      <c r="G984" s="100"/>
       <c r="H984" s="19"/>
       <c r="I984" s="19"/>
       <c r="J984" s="20"/>
@@ -37552,7 +37562,7 @@
       <c r="D985" s="19"/>
       <c r="E985" s="20"/>
       <c r="F985" s="21"/>
-      <c r="G985" s="101"/>
+      <c r="G985" s="100"/>
       <c r="H985" s="19"/>
       <c r="I985" s="19"/>
       <c r="J985" s="20"/>
@@ -37585,7 +37595,7 @@
       <c r="D986" s="19"/>
       <c r="E986" s="20"/>
       <c r="F986" s="21"/>
-      <c r="G986" s="101"/>
+      <c r="G986" s="100"/>
       <c r="H986" s="19"/>
       <c r="I986" s="19"/>
       <c r="J986" s="20"/>
@@ -37618,7 +37628,7 @@
       <c r="D987" s="19"/>
       <c r="E987" s="20"/>
       <c r="F987" s="21"/>
-      <c r="G987" s="101"/>
+      <c r="G987" s="100"/>
       <c r="H987" s="19"/>
       <c r="I987" s="19"/>
       <c r="J987" s="20"/>
@@ -37651,7 +37661,7 @@
       <c r="D988" s="19"/>
       <c r="E988" s="20"/>
       <c r="F988" s="21"/>
-      <c r="G988" s="101"/>
+      <c r="G988" s="100"/>
       <c r="H988" s="19"/>
       <c r="I988" s="19"/>
       <c r="J988" s="20"/>
@@ -37684,7 +37694,7 @@
       <c r="D989" s="19"/>
       <c r="E989" s="20"/>
       <c r="F989" s="21"/>
-      <c r="G989" s="101"/>
+      <c r="G989" s="100"/>
       <c r="H989" s="19"/>
       <c r="I989" s="19"/>
       <c r="J989" s="20"/>
@@ -37717,7 +37727,7 @@
       <c r="D990" s="19"/>
       <c r="E990" s="20"/>
       <c r="F990" s="21"/>
-      <c r="G990" s="101"/>
+      <c r="G990" s="100"/>
       <c r="H990" s="19"/>
       <c r="I990" s="19"/>
       <c r="J990" s="20"/>
@@ -37750,7 +37760,7 @@
       <c r="D991" s="19"/>
       <c r="E991" s="20"/>
       <c r="F991" s="21"/>
-      <c r="G991" s="101"/>
+      <c r="G991" s="100"/>
       <c r="H991" s="19"/>
       <c r="I991" s="19"/>
       <c r="J991" s="20"/>
@@ -37783,7 +37793,7 @@
       <c r="D992" s="19"/>
       <c r="E992" s="20"/>
       <c r="F992" s="21"/>
-      <c r="G992" s="101"/>
+      <c r="G992" s="100"/>
       <c r="H992" s="19"/>
       <c r="I992" s="19"/>
       <c r="J992" s="20"/>
@@ -37816,7 +37826,7 @@
       <c r="D993" s="19"/>
       <c r="E993" s="20"/>
       <c r="F993" s="21"/>
-      <c r="G993" s="101"/>
+      <c r="G993" s="100"/>
       <c r="H993" s="19"/>
       <c r="I993" s="19"/>
       <c r="J993" s="20"/>
@@ -37849,7 +37859,7 @@
       <c r="D994" s="19"/>
       <c r="E994" s="20"/>
       <c r="F994" s="21"/>
-      <c r="G994" s="101"/>
+      <c r="G994" s="100"/>
       <c r="H994" s="19"/>
       <c r="I994" s="19"/>
       <c r="J994" s="20"/>
@@ -37882,7 +37892,7 @@
       <c r="D995" s="19"/>
       <c r="E995" s="20"/>
       <c r="F995" s="21"/>
-      <c r="G995" s="101"/>
+      <c r="G995" s="100"/>
       <c r="H995" s="19"/>
       <c r="I995" s="19"/>
       <c r="J995" s="20"/>
@@ -37915,7 +37925,7 @@
       <c r="D996" s="19"/>
       <c r="E996" s="20"/>
       <c r="F996" s="21"/>
-      <c r="G996" s="101"/>
+      <c r="G996" s="100"/>
       <c r="H996" s="19"/>
       <c r="I996" s="19"/>
       <c r="J996" s="20"/>
@@ -37948,7 +37958,7 @@
       <c r="D997" s="19"/>
       <c r="E997" s="20"/>
       <c r="F997" s="21"/>
-      <c r="G997" s="101"/>
+      <c r="G997" s="100"/>
       <c r="H997" s="19"/>
       <c r="I997" s="19"/>
       <c r="J997" s="20"/>
@@ -37981,7 +37991,7 @@
       <c r="D998" s="19"/>
       <c r="E998" s="20"/>
       <c r="F998" s="21"/>
-      <c r="G998" s="101"/>
+      <c r="G998" s="100"/>
       <c r="H998" s="19"/>
       <c r="I998" s="19"/>
       <c r="J998" s="20"/>
@@ -38014,7 +38024,7 @@
       <c r="D999" s="19"/>
       <c r="E999" s="20"/>
       <c r="F999" s="21"/>
-      <c r="G999" s="101"/>
+      <c r="G999" s="100"/>
       <c r="H999" s="19"/>
       <c r="I999" s="19"/>
       <c r="J999" s="20"/>
@@ -38047,7 +38057,7 @@
       <c r="D1000" s="19"/>
       <c r="E1000" s="20"/>
       <c r="F1000" s="21"/>
-      <c r="G1000" s="101"/>
+      <c r="G1000" s="100"/>
       <c r="H1000" s="19"/>
       <c r="I1000" s="19"/>
       <c r="J1000" s="20"/>
@@ -38080,7 +38090,7 @@
       <c r="D1001" s="19"/>
       <c r="E1001" s="20"/>
       <c r="F1001" s="21"/>
-      <c r="G1001" s="101"/>
+      <c r="G1001" s="100"/>
       <c r="H1001" s="19"/>
       <c r="I1001" s="19"/>
       <c r="J1001" s="20"/>
@@ -38113,7 +38123,7 @@
       <c r="D1002" s="19"/>
       <c r="E1002" s="20"/>
       <c r="F1002" s="21"/>
-      <c r="G1002" s="101"/>
+      <c r="G1002" s="100"/>
       <c r="H1002" s="19"/>
       <c r="I1002" s="19"/>
       <c r="J1002" s="20"/>
@@ -38146,7 +38156,7 @@
       <c r="D1003" s="19"/>
       <c r="E1003" s="20"/>
       <c r="F1003" s="21"/>
-      <c r="G1003" s="101"/>
+      <c r="G1003" s="100"/>
       <c r="H1003" s="19"/>
       <c r="I1003" s="19"/>
       <c r="J1003" s="20"/>
@@ -38179,7 +38189,7 @@
       <c r="D1004" s="19"/>
       <c r="E1004" s="20"/>
       <c r="F1004" s="21"/>
-      <c r="G1004" s="101"/>
+      <c r="G1004" s="100"/>
       <c r="H1004" s="19"/>
       <c r="I1004" s="19"/>
       <c r="J1004" s="20"/>
@@ -38212,7 +38222,7 @@
       <c r="D1005" s="19"/>
       <c r="E1005" s="20"/>
       <c r="F1005" s="21"/>
-      <c r="G1005" s="101"/>
+      <c r="G1005" s="100"/>
       <c r="H1005" s="19"/>
       <c r="I1005" s="19"/>
       <c r="J1005" s="20"/>
@@ -38245,7 +38255,7 @@
       <c r="D1006" s="19"/>
       <c r="E1006" s="20"/>
       <c r="F1006" s="21"/>
-      <c r="G1006" s="101"/>
+      <c r="G1006" s="100"/>
       <c r="H1006" s="19"/>
       <c r="I1006" s="19"/>
       <c r="J1006" s="20"/>
@@ -48481,11 +48491,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="96" x14ac:dyDescent="0.2">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="110" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
       <c r="D1" s="9" t="s">
         <v>53</v>
       </c>
